--- a/Valores_maximos_P_meses.xlsx
+++ b/Valores_maximos_P_meses.xlsx
@@ -592,7 +592,7 @@
         <v>99.90000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         <v>33.71</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>100.79</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>63.62</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         <v>93.45999999999999</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1025,16 +1025,16 @@
         <v>5814</v>
       </c>
       <c r="P9" t="n">
-        <v>6093</v>
+        <v>6171</v>
       </c>
       <c r="Q9" t="n">
-        <v>6093</v>
+        <v>6171</v>
       </c>
       <c r="R9" t="n">
-        <v>97.48999999999999</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1095,16 +1095,16 @@
         <v>20912</v>
       </c>
       <c r="P10" t="n">
-        <v>20848</v>
+        <v>20934</v>
       </c>
       <c r="Q10" t="n">
-        <v>20912</v>
+        <v>20934</v>
       </c>
       <c r="R10" t="n">
-        <v>83.65000000000001</v>
+        <v>83.73999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>35.9</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
         <v>44.6</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         <v>105.95</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>12165</v>
       </c>
       <c r="P14" t="n">
-        <v>11584</v>
+        <v>13113</v>
       </c>
       <c r="Q14" t="n">
         <v>14496</v>
@@ -1384,7 +1384,7 @@
         <v>57.98</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="Q15" t="n">
         <v>4925</v>
@@ -1454,7 +1454,7 @@
         <v>39.4</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>14925</v>
       </c>
       <c r="P16" t="n">
-        <v>13690</v>
+        <v>14574</v>
       </c>
       <c r="Q16" t="n">
         <v>28370</v>
@@ -1524,7 +1524,7 @@
         <v>113.48</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
         <v>62.62</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>6.12</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -1841,16 +1841,16 @@
         <v>701</v>
       </c>
       <c r="P21" t="n">
-        <v>718</v>
+        <v>740</v>
       </c>
       <c r="Q21" t="n">
-        <v>718</v>
+        <v>740</v>
       </c>
       <c r="R21" t="n">
-        <v>23.93</v>
+        <v>24.67</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -1957,16 +1957,16 @@
         <v>1472</v>
       </c>
       <c r="P23" t="n">
-        <v>1519</v>
+        <v>1594</v>
       </c>
       <c r="Q23" t="n">
-        <v>1519</v>
+        <v>1594</v>
       </c>
       <c r="R23" t="n">
-        <v>75.95</v>
+        <v>79.7</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>9466</v>
       </c>
       <c r="P24" t="n">
-        <v>9039</v>
+        <v>9373</v>
       </c>
       <c r="Q24" t="n">
         <v>9466</v>
@@ -2036,7 +2036,7 @@
         <v>75.73</v>
       </c>
       <c r="S24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2176,7 +2176,7 @@
         <v>42.73</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -2222,7 +2222,7 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>12217</v>
       </c>
       <c r="P28" t="n">
-        <v>11414</v>
+        <v>12017</v>
       </c>
       <c r="Q28" t="n">
         <v>12217</v>
@@ -2292,7 +2292,7 @@
         <v>40.72</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>58.49</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -2524,7 +2524,7 @@
         <v>25.73</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>66.23</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -2710,7 +2710,7 @@
         <v>75.03</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>38.22</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -2850,7 +2850,7 @@
         <v>38.99</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>93</v>
       </c>
       <c r="S38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>14.4</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>94.44</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         <v>62.36</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>91.20999999999999</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>18</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -3377,16 +3377,16 @@
         <v>3477</v>
       </c>
       <c r="P45" t="n">
-        <v>4079</v>
+        <v>4333</v>
       </c>
       <c r="Q45" t="n">
-        <v>4079</v>
+        <v>4333</v>
       </c>
       <c r="R45" t="n">
-        <v>27.19</v>
+        <v>28.89</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -3447,16 +3447,16 @@
         <v>967</v>
       </c>
       <c r="P46" t="n">
-        <v>967</v>
+        <v>1200</v>
       </c>
       <c r="Q46" t="n">
-        <v>967</v>
+        <v>1200</v>
       </c>
       <c r="R46" t="n">
-        <v>15.47</v>
+        <v>19.2</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -3517,16 +3517,16 @@
         <v>1625</v>
       </c>
       <c r="P47" t="n">
-        <v>1649</v>
+        <v>1724</v>
       </c>
       <c r="Q47" t="n">
-        <v>1649</v>
+        <v>1724</v>
       </c>
       <c r="R47" t="n">
-        <v>54.97</v>
+        <v>57.47</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>67.7</v>
       </c>
       <c r="S48" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
         <v>2639</v>
       </c>
       <c r="P50" t="n">
-        <v>2564</v>
+        <v>2776</v>
       </c>
       <c r="Q50" t="n">
-        <v>2726</v>
+        <v>2776</v>
       </c>
       <c r="R50" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         <v>524.27</v>
       </c>
       <c r="S53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>57.11</v>
       </c>
       <c r="S54" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>70.65000000000001</v>
       </c>
       <c r="S55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>69.83</v>
       </c>
       <c r="S56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -4169,16 +4169,16 @@
         <v>707</v>
       </c>
       <c r="P57" t="n">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="Q57" t="n">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="R57" t="n">
-        <v>71.7</v>
+        <v>72.3</v>
       </c>
       <c r="S57" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>36</v>
       </c>
       <c r="S58" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>105.62</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="S61" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -4504,7 +4504,7 @@
         <v>98.48</v>
       </c>
       <c r="S62" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>96.95</v>
       </c>
       <c r="S63" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>52.97</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>77.69</v>
       </c>
       <c r="S65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>11393</v>
       </c>
       <c r="P67" t="n">
-        <v>11012</v>
+        <v>11429</v>
       </c>
       <c r="Q67" t="n">
         <v>12404</v>
@@ -4830,7 +4830,7 @@
         <v>99.23</v>
       </c>
       <c r="S67" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>12752</v>
       </c>
       <c r="P69" t="n">
-        <v>11980</v>
+        <v>11592</v>
       </c>
       <c r="Q69" t="n">
         <v>12752</v>
@@ -4946,7 +4946,7 @@
         <v>51.01</v>
       </c>
       <c r="S69" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -5016,7 +5016,7 @@
         <v>93.93000000000001</v>
       </c>
       <c r="S70" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         <v>110.42</v>
       </c>
       <c r="S71" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -5147,16 +5147,16 @@
         <v>25454</v>
       </c>
       <c r="P72" t="n">
-        <v>26363</v>
+        <v>27366</v>
       </c>
       <c r="Q72" t="n">
-        <v>26363</v>
+        <v>27366</v>
       </c>
       <c r="R72" t="n">
-        <v>58.58</v>
+        <v>60.81</v>
       </c>
       <c r="S72" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
       <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr"/>
       <c r="S73" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>59.94</v>
       </c>
       <c r="S74" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>104</v>
       </c>
       <c r="S75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>108.21</v>
       </c>
       <c r="S76" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -5473,16 +5473,16 @@
         <v>19559</v>
       </c>
       <c r="P77" t="n">
-        <v>17616</v>
+        <v>22207</v>
       </c>
       <c r="Q77" t="n">
-        <v>19559</v>
+        <v>22207</v>
       </c>
       <c r="R77" t="n">
-        <v>43.46</v>
+        <v>49.35</v>
       </c>
       <c r="S77" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>80.14</v>
       </c>
       <c r="S78" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -5622,7 +5622,7 @@
         <v>43.25</v>
       </c>
       <c r="S79" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -5683,16 +5683,16 @@
         <v>36867</v>
       </c>
       <c r="P80" t="n">
-        <v>38300</v>
+        <v>38755</v>
       </c>
       <c r="Q80" t="n">
-        <v>38300</v>
+        <v>38755</v>
       </c>
       <c r="R80" t="n">
-        <v>85.11</v>
+        <v>86.12</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>66.56999999999999</v>
       </c>
       <c r="S81" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -5832,7 +5832,7 @@
         <v>93.84</v>
       </c>
       <c r="S82" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>59.84</v>
       </c>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>48.39</v>
       </c>
       <c r="S84" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>106.75</v>
       </c>
       <c r="S85" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>58.65</v>
       </c>
       <c r="S86" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         <v>54.6</v>
       </c>
       <c r="S87" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>23857</v>
       </c>
       <c r="P88" t="n">
-        <v>18933</v>
+        <v>19317</v>
       </c>
       <c r="Q88" t="n">
         <v>23857</v>
@@ -6252,7 +6252,7 @@
         <v>95.43000000000001</v>
       </c>
       <c r="S88" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>56.23</v>
       </c>
       <c r="S89" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>79.76000000000001</v>
       </c>
       <c r="S90" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -6462,7 +6462,7 @@
         <v>73.36</v>
       </c>
       <c r="S91" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         <v>90.04000000000001</v>
       </c>
       <c r="S92" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
       <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>92</v>
       </c>
       <c r="S94" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -6709,16 +6709,16 @@
         <v>22630</v>
       </c>
       <c r="P95" t="n">
-        <v>23434</v>
+        <v>23706</v>
       </c>
       <c r="Q95" t="n">
-        <v>23434</v>
+        <v>23706</v>
       </c>
       <c r="R95" t="n">
-        <v>93.73999999999999</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="S95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>80.17</v>
       </c>
       <c r="S96" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         <v>108.33</v>
       </c>
       <c r="S97" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
       <c r="S98" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>71.52</v>
       </c>
       <c r="S99" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
       <c r="S100" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>89.53</v>
       </c>
       <c r="S101" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>65.48</v>
       </c>
       <c r="S102" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>70.98</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>40.29</v>
       </c>
       <c r="S104" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -7361,7 +7361,7 @@
         <v>27513</v>
       </c>
       <c r="P105" t="n">
-        <v>15393</v>
+        <v>13866</v>
       </c>
       <c r="Q105" t="n">
         <v>27513</v>
@@ -7370,7 +7370,7 @@
         <v>110.05</v>
       </c>
       <c r="S105" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>9607</v>
       </c>
       <c r="P106" t="n">
-        <v>3973</v>
+        <v>3616</v>
       </c>
       <c r="Q106" t="n">
         <v>9607</v>
@@ -7440,7 +7440,7 @@
         <v>102.47</v>
       </c>
       <c r="S106" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         <v>85.12</v>
       </c>
       <c r="S107" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
       <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr"/>
       <c r="S108" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -7626,7 +7626,7 @@
         <v>58.03</v>
       </c>
       <c r="S109" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
       <c r="Q110" t="inlineStr"/>
       <c r="R110" t="inlineStr"/>
       <c r="S110" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
       <c r="Q111" t="inlineStr"/>
       <c r="R111" t="inlineStr"/>
       <c r="S111" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -7779,16 +7779,16 @@
         <v>11434</v>
       </c>
       <c r="P112" t="n">
-        <v>11485</v>
+        <v>11521</v>
       </c>
       <c r="Q112" t="n">
-        <v>11485</v>
+        <v>11521</v>
       </c>
       <c r="R112" t="n">
-        <v>91.88</v>
+        <v>92.17</v>
       </c>
       <c r="S112" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>19.62</v>
       </c>
       <c r="S113" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
       <c r="Q114" t="inlineStr"/>
       <c r="R114" t="inlineStr"/>
       <c r="S114" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
       <c r="Q115" t="inlineStr"/>
       <c r="R115" t="inlineStr"/>
       <c r="S115" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>20122</v>
       </c>
       <c r="P116" t="n">
-        <v>19866</v>
+        <v>19937</v>
       </c>
       <c r="Q116" t="n">
         <v>20122</v>
@@ -8020,7 +8020,7 @@
         <v>80.48999999999999</v>
       </c>
       <c r="S116" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>95.56999999999999</v>
       </c>
       <c r="S117" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>58.46</v>
       </c>
       <c r="S118" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         <v>56.58</v>
       </c>
       <c r="S119" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>3.93</v>
       </c>
       <c r="S120" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
       <c r="Q121" t="inlineStr"/>
       <c r="R121" t="inlineStr"/>
       <c r="S121" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -8407,16 +8407,16 @@
         <v>16024</v>
       </c>
       <c r="P122" t="n">
-        <v>17836</v>
+        <v>17861</v>
       </c>
       <c r="Q122" t="n">
-        <v>17836</v>
+        <v>17861</v>
       </c>
       <c r="R122" t="n">
-        <v>59.45</v>
+        <v>59.54</v>
       </c>
       <c r="S122" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -8477,16 +8477,16 @@
         <v>10859</v>
       </c>
       <c r="P123" t="n">
-        <v>10764</v>
+        <v>12850</v>
       </c>
       <c r="Q123" t="n">
-        <v>10859</v>
+        <v>12850</v>
       </c>
       <c r="R123" t="n">
-        <v>86.87</v>
+        <v>102.8</v>
       </c>
       <c r="S123" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>102.76</v>
       </c>
       <c r="S124" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         <v>109.5</v>
       </c>
       <c r="S125" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -8696,7 +8696,7 @@
         <v>80.19</v>
       </c>
       <c r="S126" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>99.58</v>
       </c>
       <c r="S127" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>63.05</v>
       </c>
       <c r="S128" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>84.26000000000001</v>
       </c>
       <c r="S129" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -8976,7 +8976,7 @@
         <v>110.26</v>
       </c>
       <c r="S130" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -9037,16 +9037,16 @@
         <v>26362</v>
       </c>
       <c r="P131" t="n">
-        <v>27220</v>
+        <v>28323</v>
       </c>
       <c r="Q131" t="n">
-        <v>27220</v>
+        <v>28323</v>
       </c>
       <c r="R131" t="n">
-        <v>90.73</v>
+        <v>94.41</v>
       </c>
       <c r="S131" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         <v>92.59999999999999</v>
       </c>
       <c r="S132" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>32.86</v>
       </c>
       <c r="S133" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
       <c r="Q134" t="inlineStr"/>
       <c r="R134" t="inlineStr"/>
       <c r="S134" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>38.1</v>
       </c>
       <c r="S135" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
       <c r="S136" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>16.19</v>
       </c>
       <c r="S137" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         <v>93.81</v>
       </c>
       <c r="S139" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         <v>44.1</v>
       </c>
       <c r="S140" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>56.92</v>
       </c>
       <c r="S141" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>99.83</v>
       </c>
       <c r="S142" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>17803</v>
       </c>
       <c r="P143" t="n">
-        <v>14201</v>
+        <v>16445</v>
       </c>
       <c r="Q143" t="n">
         <v>19796</v>
@@ -9814,7 +9814,7 @@
         <v>79.18000000000001</v>
       </c>
       <c r="S143" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
       <c r="Q144" t="inlineStr"/>
       <c r="R144" t="inlineStr"/>
       <c r="S144" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>39.2</v>
       </c>
       <c r="S145" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>42.99</v>
       </c>
       <c r="S146" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -10070,7 +10070,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="S147" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>59.9</v>
       </c>
       <c r="S148" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -10204,7 +10204,7 @@
         <v>0</v>
       </c>
       <c r="S149" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>53.49</v>
       </c>
       <c r="S150" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -10344,7 +10344,7 @@
         <v>70.64</v>
       </c>
       <c r="S151" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
         <v>106.18</v>
       </c>
       <c r="S153" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -10530,7 +10530,7 @@
         <v>84.48</v>
       </c>
       <c r="S154" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>98.66</v>
       </c>
       <c r="S155" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -10661,7 +10661,7 @@
         <v>19750</v>
       </c>
       <c r="P156" t="n">
-        <v>18791</v>
+        <v>19637</v>
       </c>
       <c r="Q156" t="n">
         <v>19750</v>
@@ -10670,7 +10670,7 @@
         <v>65.83</v>
       </c>
       <c r="S156" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>3.87</v>
       </c>
       <c r="S157" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
       <c r="Q158" t="inlineStr"/>
       <c r="R158" t="inlineStr"/>
       <c r="S158" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>108.88</v>
       </c>
       <c r="S159" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -10917,16 +10917,16 @@
         <v>18776</v>
       </c>
       <c r="P160" t="n">
-        <v>19040</v>
+        <v>19135</v>
       </c>
       <c r="Q160" t="n">
-        <v>19040</v>
+        <v>19135</v>
       </c>
       <c r="R160" t="n">
-        <v>76.16</v>
+        <v>76.54000000000001</v>
       </c>
       <c r="S160" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
         <v>104.22</v>
       </c>
       <c r="S161" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>12269</v>
       </c>
       <c r="P162" t="n">
-        <v>10035</v>
+        <v>11682</v>
       </c>
       <c r="Q162" t="n">
         <v>12557</v>
@@ -11066,7 +11066,7 @@
         <v>62.78</v>
       </c>
       <c r="S162" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -11112,7 +11112,7 @@
       <c r="Q163" t="inlineStr"/>
       <c r="R163" t="inlineStr"/>
       <c r="S163" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -11173,7 +11173,7 @@
         <v>8322</v>
       </c>
       <c r="P164" t="n">
-        <v>8254</v>
+        <v>11042</v>
       </c>
       <c r="Q164" t="n">
         <v>11890</v>
@@ -11182,7 +11182,7 @@
         <v>59.45</v>
       </c>
       <c r="S164" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>23412</v>
       </c>
       <c r="P165" t="n">
-        <v>20190</v>
+        <v>20680</v>
       </c>
       <c r="Q165" t="n">
         <v>23412</v>
@@ -11252,7 +11252,7 @@
         <v>78.04000000000001</v>
       </c>
       <c r="S165" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>82.58</v>
       </c>
       <c r="S166" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -11392,7 +11392,7 @@
         <v>47.57</v>
       </c>
       <c r="S167" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>29.74</v>
       </c>
       <c r="S168" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -11508,7 +11508,7 @@
       <c r="Q169" t="inlineStr"/>
       <c r="R169" t="inlineStr"/>
       <c r="S169" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>43.76</v>
       </c>
       <c r="S170" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>66.22</v>
       </c>
       <c r="S171" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
       <c r="Q172" t="inlineStr"/>
       <c r="R172" t="inlineStr"/>
       <c r="S172" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>0</v>
       </c>
       <c r="S173" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
       <c r="Q174" t="inlineStr"/>
       <c r="R174" t="inlineStr"/>
       <c r="S174" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>48.54</v>
       </c>
       <c r="S175" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -11950,7 +11950,7 @@
         <v>90.65000000000001</v>
       </c>
       <c r="S176" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>19578</v>
       </c>
       <c r="P177" t="n">
-        <v>13531</v>
+        <v>15584</v>
       </c>
       <c r="Q177" t="n">
         <v>19578</v>
@@ -12020,7 +12020,7 @@
         <v>130.52</v>
       </c>
       <c r="S177" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T177" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>88.01000000000001</v>
       </c>
       <c r="S178" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>95.17</v>
       </c>
       <c r="S179" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>-10.65</v>
       </c>
       <c r="S180" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>79</v>
       </c>
       <c r="S181" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>97.13</v>
       </c>
       <c r="S182" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -12440,7 +12440,7 @@
         <v>105.32</v>
       </c>
       <c r="S183" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>0</v>
       </c>
       <c r="S184" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>13.8</v>
       </c>
       <c r="F185" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="G185" t="n">
         <v>119</v>
@@ -12577,10 +12577,10 @@
         <v>11432</v>
       </c>
       <c r="R185" t="n">
-        <v>45.73</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="S185" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -12641,7 +12641,7 @@
         <v>19286</v>
       </c>
       <c r="P186" t="n">
-        <v>15069</v>
+        <v>16782</v>
       </c>
       <c r="Q186" t="n">
         <v>23208</v>
@@ -12650,7 +12650,7 @@
         <v>92.83</v>
       </c>
       <c r="S186" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>56.31</v>
       </c>
       <c r="S187" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>26734</v>
       </c>
       <c r="P188" t="n">
-        <v>20523</v>
+        <v>24093</v>
       </c>
       <c r="Q188" t="n">
         <v>27359</v>
@@ -12790,7 +12790,7 @@
         <v>91.2</v>
       </c>
       <c r="S188" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -12860,7 +12860,7 @@
         <v>44.89</v>
       </c>
       <c r="S189" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T189" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>89.28</v>
       </c>
       <c r="S190" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T190" t="inlineStr">
         <is>
@@ -13000,7 +13000,7 @@
         <v>90.27</v>
       </c>
       <c r="S191" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T191" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>52.47</v>
       </c>
       <c r="S192" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T192" t="inlineStr">
         <is>
@@ -13131,16 +13131,16 @@
         <v>11271</v>
       </c>
       <c r="P193" t="n">
-        <v>10447</v>
+        <v>11823</v>
       </c>
       <c r="Q193" t="n">
-        <v>11271</v>
+        <v>11823</v>
       </c>
       <c r="R193" t="n">
-        <v>90.17</v>
+        <v>94.58</v>
       </c>
       <c r="S193" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T193" t="inlineStr">
         <is>
@@ -13186,7 +13186,7 @@
       <c r="Q194" t="inlineStr"/>
       <c r="R194" t="inlineStr"/>
       <c r="S194" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T194" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>51.91</v>
       </c>
       <c r="S195" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T195" t="inlineStr">
         <is>
@@ -13326,7 +13326,7 @@
         <v>61.17</v>
       </c>
       <c r="S196" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T196" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>64.98</v>
       </c>
       <c r="S197" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
         <v>50.06</v>
       </c>
       <c r="S198" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>10.98</v>
       </c>
       <c r="S199" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
       <c r="Q200" t="inlineStr"/>
       <c r="R200" t="inlineStr"/>
       <c r="S200" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>25463</v>
       </c>
       <c r="P201" t="n">
-        <v>22986</v>
+        <v>23020</v>
       </c>
       <c r="Q201" t="n">
         <v>25463</v>
@@ -13652,7 +13652,7 @@
         <v>101.85</v>
       </c>
       <c r="S201" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T201" t="inlineStr">
         <is>
@@ -13722,7 +13722,7 @@
         <v>18.95</v>
       </c>
       <c r="S202" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>58.47</v>
       </c>
       <c r="S203" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T203" t="inlineStr">
         <is>
@@ -13838,7 +13838,7 @@
       <c r="Q204" t="inlineStr"/>
       <c r="R204" t="inlineStr"/>
       <c r="S204" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>36.68</v>
       </c>
       <c r="S205" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>9.74</v>
       </c>
       <c r="S206" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T206" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>41.86</v>
       </c>
       <c r="S207" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
       <c r="Q208" t="inlineStr"/>
       <c r="R208" t="inlineStr"/>
       <c r="S208" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -14155,16 +14155,16 @@
         <v>22450</v>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>23928</v>
       </c>
       <c r="Q209" t="n">
-        <v>22789</v>
+        <v>23928</v>
       </c>
       <c r="R209" t="n">
-        <v>91.16</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="S209" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T209" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
       <c r="Q210" t="inlineStr"/>
       <c r="R210" t="inlineStr"/>
       <c r="S210" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
       <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -14317,16 +14317,16 @@
         <v>2584</v>
       </c>
       <c r="P212" t="n">
-        <v>2638</v>
+        <v>2828</v>
       </c>
       <c r="Q212" t="n">
-        <v>2638</v>
+        <v>2828</v>
       </c>
       <c r="R212" t="n">
-        <v>87.93000000000001</v>
+        <v>94.27</v>
       </c>
       <c r="S212" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T212" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>48.51</v>
       </c>
       <c r="S213" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T213" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>86.75</v>
       </c>
       <c r="S214" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T214" t="inlineStr">
         <is>
@@ -14536,7 +14536,7 @@
         <v>79.45999999999999</v>
       </c>
       <c r="S215" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T215" t="inlineStr">
         <is>
@@ -14606,7 +14606,7 @@
         <v>53.94</v>
       </c>
       <c r="S216" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T216" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>29.52</v>
       </c>
       <c r="S217" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T217" t="inlineStr">
         <is>
@@ -14737,16 +14737,16 @@
         <v>4639</v>
       </c>
       <c r="P218" t="n">
-        <v>4878</v>
+        <v>5240</v>
       </c>
       <c r="Q218" t="n">
-        <v>4878</v>
+        <v>5240</v>
       </c>
       <c r="R218" t="n">
-        <v>52.03</v>
+        <v>55.89</v>
       </c>
       <c r="S218" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T218" t="inlineStr">
         <is>
@@ -14792,7 +14792,7 @@
       <c r="Q219" t="inlineStr"/>
       <c r="R219" t="inlineStr"/>
       <c r="S219" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -14862,7 +14862,7 @@
         <v>46.12</v>
       </c>
       <c r="S220" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>21.77</v>
       </c>
       <c r="S221" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>96.52</v>
       </c>
       <c r="S222" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T222" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
       <c r="Q223" t="inlineStr"/>
       <c r="R223" t="inlineStr"/>
       <c r="S223" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T223" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>103.83</v>
       </c>
       <c r="S224" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T224" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>72.12</v>
       </c>
       <c r="S225" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>90.18000000000001</v>
       </c>
       <c r="S226" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>42.12</v>
       </c>
       <c r="S227" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>90.2</v>
       </c>
       <c r="S228" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -15459,16 +15459,16 @@
         <v>29585</v>
       </c>
       <c r="P229" t="n">
-        <v>29329</v>
+        <v>29745</v>
       </c>
       <c r="Q229" t="n">
-        <v>29585</v>
+        <v>29745</v>
       </c>
       <c r="R229" t="n">
-        <v>98.62</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="S229" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T229" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>7.17</v>
       </c>
       <c r="S230" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T230" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
       <c r="Q231" t="inlineStr"/>
       <c r="R231" t="inlineStr"/>
       <c r="S231" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T231" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>67.78</v>
       </c>
       <c r="S232" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T232" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>6622</v>
       </c>
       <c r="P233" t="n">
-        <v>5916</v>
+        <v>5941</v>
       </c>
       <c r="Q233" t="n">
         <v>6622</v>
@@ -15724,7 +15724,7 @@
         <v>65.95999999999999</v>
       </c>
       <c r="S233" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T233" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>75.01000000000001</v>
       </c>
       <c r="S234" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T234" t="inlineStr">
         <is>
@@ -15864,7 +15864,7 @@
         <v>42.74</v>
       </c>
       <c r="S235" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T235" t="inlineStr">
         <is>
@@ -15934,7 +15934,7 @@
         <v>15.48</v>
       </c>
       <c r="S236" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T236" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>46.39</v>
       </c>
       <c r="S237" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T237" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>69.8</v>
       </c>
       <c r="S238" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T238" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>1.26</v>
       </c>
       <c r="S239" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T239" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>1485</v>
       </c>
       <c r="P240" t="n">
-        <v>1317</v>
+        <v>1347</v>
       </c>
       <c r="Q240" t="n">
         <v>2389</v>
@@ -16214,7 +16214,7 @@
         <v>39.82</v>
       </c>
       <c r="S240" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T240" t="inlineStr">
         <is>
@@ -16284,7 +16284,7 @@
         <v>55.63</v>
       </c>
       <c r="S241" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T241" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>49.5</v>
       </c>
       <c r="S242" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T242" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>7330</v>
       </c>
       <c r="P243" t="n">
-        <v>6578</v>
+        <v>6332</v>
       </c>
       <c r="Q243" t="n">
         <v>7330</v>
@@ -16424,7 +16424,7 @@
         <v>73.3</v>
       </c>
       <c r="S243" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T243" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>43.38</v>
       </c>
       <c r="S244" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T244" t="inlineStr">
         <is>
@@ -16564,7 +16564,7 @@
         <v>43.32</v>
       </c>
       <c r="S245" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T245" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>61.67</v>
       </c>
       <c r="S246" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T246" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>50.13</v>
       </c>
       <c r="S247" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T247" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>50</v>
       </c>
       <c r="S248" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T248" t="inlineStr">
         <is>
@@ -16835,7 +16835,7 @@
         <v>6287</v>
       </c>
       <c r="P249" t="n">
-        <v>6082</v>
+        <v>6193</v>
       </c>
       <c r="Q249" t="n">
         <v>6287</v>
@@ -16844,7 +16844,7 @@
         <v>62.87</v>
       </c>
       <c r="S249" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T249" t="inlineStr">
         <is>
@@ -16905,16 +16905,16 @@
         <v>1432</v>
       </c>
       <c r="P250" t="n">
-        <v>1400</v>
+        <v>1695</v>
       </c>
       <c r="Q250" t="n">
-        <v>1432</v>
+        <v>1695</v>
       </c>
       <c r="R250" t="n">
-        <v>23.96</v>
+        <v>28.37</v>
       </c>
       <c r="S250" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T250" t="inlineStr">
         <is>
@@ -16984,7 +16984,7 @@
         <v>43.63</v>
       </c>
       <c r="S251" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T251" t="inlineStr">
         <is>
@@ -17054,7 +17054,7 @@
         <v>51.15</v>
       </c>
       <c r="S252" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T252" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>82.90000000000001</v>
       </c>
       <c r="S253" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T253" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>1797</v>
       </c>
       <c r="P254" t="n">
-        <v>1321</v>
+        <v>1215</v>
       </c>
       <c r="Q254" t="n">
         <v>1930</v>
@@ -17194,7 +17194,7 @@
         <v>48.25</v>
       </c>
       <c r="S254" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T254" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>101.59</v>
       </c>
       <c r="S255" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T255" t="inlineStr">
         <is>
@@ -17334,7 +17334,7 @@
         <v>62.55</v>
       </c>
       <c r="S256" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T256" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>45.85</v>
       </c>
       <c r="S257" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T257" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>78.44</v>
       </c>
       <c r="S258" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T258" t="inlineStr">
         <is>
@@ -17535,7 +17535,7 @@
         <v>5793</v>
       </c>
       <c r="P259" t="n">
-        <v>5365</v>
+        <v>5481</v>
       </c>
       <c r="Q259" t="n">
         <v>5793</v>
@@ -17544,7 +17544,7 @@
         <v>80.45999999999999</v>
       </c>
       <c r="S259" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T259" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>32.78</v>
       </c>
       <c r="S260" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T260" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>2164</v>
       </c>
       <c r="P261" t="n">
-        <v>1821</v>
+        <v>1838</v>
       </c>
       <c r="Q261" t="n">
         <v>3044</v>
@@ -17684,7 +17684,7 @@
         <v>50.73</v>
       </c>
       <c r="S261" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T261" t="inlineStr">
         <is>
@@ -17754,7 +17754,7 @@
         <v>89.41</v>
       </c>
       <c r="S262" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T262" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>69.42</v>
       </c>
       <c r="S263" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T263" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>67.26000000000001</v>
       </c>
       <c r="S264" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T264" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>78.86</v>
       </c>
       <c r="S265" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T265" t="inlineStr">
         <is>
@@ -18025,7 +18025,7 @@
         <v>5986</v>
       </c>
       <c r="P266" t="n">
-        <v>4716</v>
+        <v>5695</v>
       </c>
       <c r="Q266" t="n">
         <v>7429</v>
@@ -18034,7 +18034,7 @@
         <v>74.29000000000001</v>
       </c>
       <c r="S266" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T266" t="inlineStr">
         <is>
@@ -18095,16 +18095,16 @@
         <v>2312</v>
       </c>
       <c r="P267" t="n">
-        <v>2389</v>
+        <v>2398</v>
       </c>
       <c r="Q267" t="n">
-        <v>2389</v>
+        <v>2398</v>
       </c>
       <c r="R267" t="n">
-        <v>59.72</v>
+        <v>59.95</v>
       </c>
       <c r="S267" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T267" t="inlineStr">
         <is>
@@ -18174,7 +18174,7 @@
         <v>20.2</v>
       </c>
       <c r="S268" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T268" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>73.09999999999999</v>
       </c>
       <c r="S269" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T269" t="inlineStr">
         <is>
@@ -18314,7 +18314,7 @@
         <v>18.32</v>
       </c>
       <c r="S270" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T270" t="inlineStr">
         <is>
@@ -18375,16 +18375,16 @@
         <v>703</v>
       </c>
       <c r="P271" t="n">
-        <v>718</v>
+        <v>743</v>
       </c>
       <c r="Q271" t="n">
-        <v>718</v>
+        <v>743</v>
       </c>
       <c r="R271" t="n">
-        <v>14.36</v>
+        <v>14.86</v>
       </c>
       <c r="S271" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T271" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>4999</v>
       </c>
       <c r="P272" t="n">
-        <v>4904</v>
+        <v>5018</v>
       </c>
       <c r="Q272" t="n">
         <v>5324</v>
@@ -18454,7 +18454,7 @@
         <v>76.06</v>
       </c>
       <c r="S272" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T272" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>4413</v>
       </c>
       <c r="P273" t="n">
-        <v>4130</v>
+        <v>4307</v>
       </c>
       <c r="Q273" t="n">
         <v>4413</v>
@@ -18524,7 +18524,7 @@
         <v>63.04</v>
       </c>
       <c r="S273" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T273" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
         <v>4586</v>
       </c>
       <c r="P274" t="n">
-        <v>4804</v>
+        <v>5097</v>
       </c>
       <c r="Q274" t="n">
         <v>8427</v>
@@ -18594,7 +18594,7 @@
         <v>70.23</v>
       </c>
       <c r="S274" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T274" t="inlineStr">
         <is>
@@ -18664,7 +18664,7 @@
         <v>38.24</v>
       </c>
       <c r="S275" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T275" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>22.37</v>
       </c>
       <c r="S276" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T276" t="inlineStr">
         <is>
@@ -18795,16 +18795,16 @@
         <v>4863</v>
       </c>
       <c r="P277" t="n">
-        <v>4551</v>
+        <v>5083</v>
       </c>
       <c r="Q277" t="n">
-        <v>4974</v>
+        <v>5083</v>
       </c>
       <c r="R277" t="n">
-        <v>41.45</v>
+        <v>42.36</v>
       </c>
       <c r="S277" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T277" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
       <c r="Q278" t="inlineStr"/>
       <c r="R278" t="inlineStr"/>
       <c r="S278" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T278" t="inlineStr">
         <is>
@@ -18920,7 +18920,7 @@
         <v>75.59999999999999</v>
       </c>
       <c r="S279" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T279" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>42.2</v>
       </c>
       <c r="S280" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T280" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>81.67</v>
       </c>
       <c r="S281" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T281" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>79.63</v>
       </c>
       <c r="S282" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T282" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>4412</v>
       </c>
       <c r="P283" t="n">
-        <v>4135</v>
+        <v>4256</v>
       </c>
       <c r="Q283" t="n">
         <v>4502</v>
@@ -19200,7 +19200,7 @@
         <v>78.48</v>
       </c>
       <c r="S283" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T283" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>3273</v>
       </c>
       <c r="P284" t="n">
-        <v>2450</v>
+        <v>2569</v>
       </c>
       <c r="Q284" t="n">
         <v>4359</v>
@@ -19270,7 +19270,7 @@
         <v>75.98999999999999</v>
       </c>
       <c r="S284" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T284" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>83</v>
       </c>
       <c r="S285" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T285" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>8309</v>
       </c>
       <c r="P286" t="n">
-        <v>6389</v>
+        <v>6683</v>
       </c>
       <c r="Q286" t="n">
         <v>9318</v>
@@ -19410,7 +19410,7 @@
         <v>97.45999999999999</v>
       </c>
       <c r="S286" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T286" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>64.3</v>
       </c>
       <c r="S287" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T287" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
       <c r="Q288" t="inlineStr"/>
       <c r="R288" t="inlineStr"/>
       <c r="S288" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T288" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
       <c r="Q289" t="inlineStr"/>
       <c r="R289" t="inlineStr"/>
       <c r="S289" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T289" t="inlineStr">
         <is>
@@ -19642,7 +19642,7 @@
         <v>241.2</v>
       </c>
       <c r="S290" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T290" t="inlineStr">
         <is>
@@ -19712,7 +19712,7 @@
         <v>28.62</v>
       </c>
       <c r="S291" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T291" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>62.1</v>
       </c>
       <c r="S292" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T292" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>74.97</v>
       </c>
       <c r="S293" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T293" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>43.7</v>
       </c>
       <c r="S294" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T294" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>34.7</v>
       </c>
       <c r="S295" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T295" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>24.77</v>
       </c>
       <c r="S296" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T296" t="inlineStr">
         <is>
@@ -20132,7 +20132,7 @@
         <v>64.65000000000001</v>
       </c>
       <c r="S297" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T297" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>58.54</v>
       </c>
       <c r="S298" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T298" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>4617</v>
       </c>
       <c r="P299" t="n">
-        <v>4514</v>
+        <v>4602</v>
       </c>
       <c r="Q299" t="n">
         <v>4617</v>
@@ -20272,7 +20272,7 @@
         <v>65.95999999999999</v>
       </c>
       <c r="S299" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T299" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>47.6</v>
       </c>
       <c r="S300" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T300" t="inlineStr">
         <is>
@@ -20412,7 +20412,7 @@
         <v>51.04</v>
       </c>
       <c r="S301" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T301" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>50.87</v>
       </c>
       <c r="S302" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T302" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="S303" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T303" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>6.48</v>
       </c>
       <c r="S304" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T304" t="inlineStr">
         <is>
@@ -20692,7 +20692,7 @@
         <v>53.94</v>
       </c>
       <c r="S305" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T305" t="inlineStr">
         <is>
@@ -20762,7 +20762,7 @@
         <v>19.48</v>
       </c>
       <c r="S306" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T306" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>57.54</v>
       </c>
       <c r="S307" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T307" t="inlineStr">
         <is>
@@ -20893,16 +20893,16 @@
         <v>6140</v>
       </c>
       <c r="P308" t="n">
-        <v>6016</v>
+        <v>6267</v>
       </c>
       <c r="Q308" t="n">
-        <v>6140</v>
+        <v>6267</v>
       </c>
       <c r="R308" t="n">
-        <v>61.4</v>
+        <v>62.67</v>
       </c>
       <c r="S308" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T308" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>63.72</v>
       </c>
       <c r="S309" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T309" t="inlineStr">
         <is>
@@ -21033,16 +21033,16 @@
         <v>3754</v>
       </c>
       <c r="P310" t="n">
-        <v>3843</v>
+        <v>4124</v>
       </c>
       <c r="Q310" t="n">
-        <v>3843</v>
+        <v>4124</v>
       </c>
       <c r="R310" t="n">
-        <v>38.43</v>
+        <v>41.24</v>
       </c>
       <c r="S310" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T310" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>51.45</v>
       </c>
       <c r="S311" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T311" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>43.55</v>
       </c>
       <c r="S312" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T312" t="inlineStr">
         <is>
@@ -21252,7 +21252,7 @@
         <v>55.61</v>
       </c>
       <c r="S313" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T313" t="inlineStr">
         <is>
@@ -21322,7 +21322,7 @@
         <v>64.56</v>
       </c>
       <c r="S314" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T314" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>70.09</v>
       </c>
       <c r="S315" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T315" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>60.19</v>
       </c>
       <c r="S316" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T316" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
       <c r="Q317" t="inlineStr"/>
       <c r="R317" t="inlineStr"/>
       <c r="S317" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T317" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
       <c r="Q318" t="inlineStr"/>
       <c r="R318" t="inlineStr"/>
       <c r="S318" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -21624,7 +21624,7 @@
         <v>9</v>
       </c>
       <c r="S319" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
       <c r="Q320" t="inlineStr"/>
       <c r="R320" t="inlineStr"/>
       <c r="S320" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T320" t="inlineStr">
         <is>
@@ -21716,7 +21716,7 @@
       <c r="Q321" t="inlineStr"/>
       <c r="R321" t="inlineStr"/>
       <c r="S321" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>66.5</v>
       </c>
       <c r="S322" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
       <c r="Q323" t="inlineStr"/>
       <c r="R323" t="inlineStr"/>
       <c r="S323" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
       <c r="Q324" t="inlineStr"/>
       <c r="R324" t="inlineStr"/>
       <c r="S324" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>1176</v>
       </c>
       <c r="P325" t="n">
-        <v>1366</v>
+        <v>1450</v>
       </c>
       <c r="Q325" t="n">
         <v>1637</v>
@@ -21948,7 +21948,7 @@
         <v>11.69</v>
       </c>
       <c r="S325" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T325" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>96.7</v>
       </c>
       <c r="S326" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T326" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>68.95999999999999</v>
       </c>
       <c r="S327" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T327" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>6.4</v>
       </c>
       <c r="S328" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
       <c r="Q329" t="inlineStr"/>
       <c r="R329" t="inlineStr"/>
       <c r="S329" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T329" t="inlineStr">
         <is>
@@ -22274,7 +22274,7 @@
         <v>109.58</v>
       </c>
       <c r="S330" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -22344,7 +22344,7 @@
         <v>89.25</v>
       </c>
       <c r="S331" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T331" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>119.64</v>
       </c>
       <c r="S332" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T332" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>48.79</v>
       </c>
       <c r="S333" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T333" t="inlineStr">
         <is>
@@ -22545,16 +22545,16 @@
         <v>5311</v>
       </c>
       <c r="P334" t="n">
-        <v>4993</v>
+        <v>6185</v>
       </c>
       <c r="Q334" t="n">
-        <v>5311</v>
+        <v>6185</v>
       </c>
       <c r="R334" t="n">
-        <v>44.26</v>
+        <v>51.54</v>
       </c>
       <c r="S334" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T334" t="inlineStr">
         <is>
@@ -22615,16 +22615,16 @@
         <v>2975</v>
       </c>
       <c r="P335" t="n">
-        <v>3078</v>
+        <v>3127</v>
       </c>
       <c r="Q335" t="n">
-        <v>3078</v>
+        <v>3127</v>
       </c>
       <c r="R335" t="n">
-        <v>43.97</v>
+        <v>44.67</v>
       </c>
       <c r="S335" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T335" t="inlineStr">
         <is>
@@ -22694,7 +22694,7 @@
         <v>85.95999999999999</v>
       </c>
       <c r="S336" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T336" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>72.18000000000001</v>
       </c>
       <c r="S337" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>25.52</v>
       </c>
       <c r="S338" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T338" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>41.14</v>
       </c>
       <c r="S339" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>51.45</v>
       </c>
       <c r="S340" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>6.83</v>
       </c>
       <c r="S341" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>44.19</v>
       </c>
       <c r="S342" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>37.22</v>
       </c>
       <c r="S343" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T343" t="inlineStr">
         <is>
@@ -23230,7 +23230,7 @@
       <c r="Q344" t="inlineStr"/>
       <c r="R344" t="inlineStr"/>
       <c r="S344" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T344" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>47.5</v>
       </c>
       <c r="S345" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T345" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
       <c r="Q346" t="inlineStr"/>
       <c r="R346" t="inlineStr"/>
       <c r="S346" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -23416,7 +23416,7 @@
         <v>32.79</v>
       </c>
       <c r="S347" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
       <c r="Q348" t="inlineStr"/>
       <c r="R348" t="inlineStr"/>
       <c r="S348" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>90.66</v>
       </c>
       <c r="S349" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T349" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>3755</v>
       </c>
       <c r="P350" t="n">
-        <v>3672</v>
+        <v>3753</v>
       </c>
       <c r="Q350" t="n">
         <v>3782</v>
@@ -23602,7 +23602,7 @@
         <v>52.53</v>
       </c>
       <c r="S350" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T350" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>67.11</v>
       </c>
       <c r="S351" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T351" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>27.66</v>
       </c>
       <c r="S352" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>40.23</v>
       </c>
       <c r="S353" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>57.23</v>
       </c>
       <c r="S354" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -23943,16 +23943,16 @@
         <v>1958</v>
       </c>
       <c r="P355" t="n">
-        <v>2096</v>
+        <v>2270</v>
       </c>
       <c r="Q355" t="n">
-        <v>2096</v>
+        <v>2270</v>
       </c>
       <c r="R355" t="n">
-        <v>20.96</v>
+        <v>22.7</v>
       </c>
       <c r="S355" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -24022,7 +24022,7 @@
         <v>54.84</v>
       </c>
       <c r="S356" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T356" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>29.78</v>
       </c>
       <c r="S357" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T357" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>59.5</v>
       </c>
       <c r="S358" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T358" t="inlineStr">
         <is>
@@ -24223,16 +24223,16 @@
         <v>4348</v>
       </c>
       <c r="P359" t="n">
-        <v>4496</v>
+        <v>4644</v>
       </c>
       <c r="Q359" t="n">
-        <v>4496</v>
+        <v>4644</v>
       </c>
       <c r="R359" t="n">
-        <v>44.96</v>
+        <v>46.44</v>
       </c>
       <c r="S359" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T359" t="inlineStr">
         <is>
@@ -24293,16 +24293,16 @@
         <v>5726</v>
       </c>
       <c r="P360" t="n">
-        <v>6590</v>
+        <v>6043</v>
       </c>
       <c r="Q360" t="n">
-        <v>6590</v>
+        <v>6043</v>
       </c>
       <c r="R360" t="n">
-        <v>65.90000000000001</v>
+        <v>60.43</v>
       </c>
       <c r="S360" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T360" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>22.23</v>
       </c>
       <c r="S361" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T361" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>80.91</v>
       </c>
       <c r="S362" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T362" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>93.45</v>
       </c>
       <c r="S363" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T363" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>26.44</v>
       </c>
       <c r="S364" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T364" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>78.02</v>
       </c>
       <c r="S365" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T365" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>6493</v>
       </c>
       <c r="P366" t="n">
-        <v>6433</v>
+        <v>6490</v>
       </c>
       <c r="Q366" t="n">
         <v>6493</v>
@@ -24722,7 +24722,7 @@
         <v>64.93000000000001</v>
       </c>
       <c r="S366" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T366" t="inlineStr">
         <is>
@@ -24792,7 +24792,7 @@
         <v>71.02</v>
       </c>
       <c r="S367" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T367" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>60.37</v>
       </c>
       <c r="S368" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T368" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>58.84</v>
       </c>
       <c r="S369" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T369" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>79.70999999999999</v>
       </c>
       <c r="S370" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T370" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>72.97</v>
       </c>
       <c r="S371" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T371" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>67.77</v>
       </c>
       <c r="S372" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T372" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>53.1</v>
       </c>
       <c r="S373" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T373" t="inlineStr">
         <is>
@@ -25273,16 +25273,16 @@
         <v>3531</v>
       </c>
       <c r="P374" t="n">
-        <v>5489</v>
+        <v>5346</v>
       </c>
       <c r="Q374" t="n">
-        <v>5489</v>
+        <v>5346</v>
       </c>
       <c r="R374" t="n">
-        <v>54.89</v>
+        <v>53.46</v>
       </c>
       <c r="S374" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T374" t="inlineStr">
         <is>
@@ -25352,7 +25352,7 @@
         <v>40.25</v>
       </c>
       <c r="S375" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T375" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>43.67</v>
       </c>
       <c r="S376" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T376" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>53.52</v>
       </c>
       <c r="S377" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T377" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>58.98</v>
       </c>
       <c r="S378" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T378" t="inlineStr">
         <is>
@@ -25632,7 +25632,7 @@
         <v>49.25</v>
       </c>
       <c r="S379" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T379" t="inlineStr">
         <is>
@@ -25702,7 +25702,7 @@
         <v>35.43</v>
       </c>
       <c r="S380" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T380" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>30.64</v>
       </c>
       <c r="S381" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T381" t="inlineStr">
         <is>
@@ -25842,7 +25842,7 @@
         <v>39.4</v>
       </c>
       <c r="S382" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T382" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>78.03</v>
       </c>
       <c r="S383" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T383" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45.83</v>
       </c>
       <c r="S384" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T384" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>49.09</v>
       </c>
       <c r="S385" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T385" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>4569</v>
       </c>
       <c r="P386" t="n">
-        <v>4075</v>
+        <v>4132</v>
       </c>
       <c r="Q386" t="n">
         <v>4569</v>
@@ -26122,7 +26122,7 @@
         <v>63.72</v>
       </c>
       <c r="S386" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T386" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>37.9</v>
       </c>
       <c r="S387" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T387" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>2537</v>
       </c>
       <c r="P388" t="n">
-        <v>1643</v>
+        <v>2486</v>
       </c>
       <c r="Q388" t="n">
         <v>2537</v>
@@ -26262,7 +26262,7 @@
         <v>42.46</v>
       </c>
       <c r="S388" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T388" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>7403</v>
       </c>
       <c r="P389" t="n">
-        <v>6727</v>
+        <v>6105</v>
       </c>
       <c r="Q389" t="n">
         <v>7403</v>
@@ -26332,7 +26332,7 @@
         <v>74.03</v>
       </c>
       <c r="S389" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T389" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>28.86</v>
       </c>
       <c r="S390" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T390" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>11.33</v>
       </c>
       <c r="S391" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T391" t="inlineStr">
         <is>
@@ -26533,16 +26533,16 @@
         <v>2904</v>
       </c>
       <c r="P392" t="n">
-        <v>3536</v>
+        <v>3214</v>
       </c>
       <c r="Q392" t="n">
-        <v>3536</v>
+        <v>3214</v>
       </c>
       <c r="R392" t="n">
-        <v>35.36</v>
+        <v>32.14</v>
       </c>
       <c r="S392" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T392" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>59.81</v>
       </c>
       <c r="S393" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T393" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>14.86</v>
       </c>
       <c r="S394" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T394" t="inlineStr">
         <is>
@@ -26752,7 +26752,7 @@
         <v>98.11</v>
       </c>
       <c r="S395" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T395" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>39.61</v>
       </c>
       <c r="S396" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T396" t="inlineStr">
         <is>
@@ -26892,7 +26892,7 @@
         <v>52.12</v>
       </c>
       <c r="S397" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T397" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>73.36</v>
       </c>
       <c r="S398" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T398" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>85.94</v>
       </c>
       <c r="S399" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T399" t="inlineStr">
         <is>
@@ -27102,7 +27102,7 @@
         <v>80.94</v>
       </c>
       <c r="S400" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T400" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>52.75</v>
       </c>
       <c r="S401" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T401" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
       <c r="Q402" t="inlineStr"/>
       <c r="R402" t="inlineStr"/>
       <c r="S402" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T402" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>36.11</v>
       </c>
       <c r="S403" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T403" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>90.12</v>
       </c>
       <c r="S404" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T404" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>44.68</v>
       </c>
       <c r="S405" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T405" t="inlineStr">
         <is>
@@ -27489,16 +27489,16 @@
         <v>875</v>
       </c>
       <c r="P406" t="n">
-        <v>1516</v>
+        <v>1469</v>
       </c>
       <c r="Q406" t="n">
-        <v>1516</v>
+        <v>1469</v>
       </c>
       <c r="R406" t="n">
-        <v>8.92</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="S406" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T406" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>73.14</v>
       </c>
       <c r="S407" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T407" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45.9</v>
       </c>
       <c r="S408" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T408" t="inlineStr">
         <is>
@@ -27708,7 +27708,7 @@
         <v>32.99</v>
       </c>
       <c r="S409" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T409" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>42.95</v>
       </c>
       <c r="S410" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T410" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>37.11</v>
       </c>
       <c r="S411" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T411" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>93.17</v>
       </c>
       <c r="S412" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T412" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>0</v>
       </c>
       <c r="S413" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T413" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>7301</v>
       </c>
       <c r="P414" t="n">
-        <v>7004</v>
+        <v>7063</v>
       </c>
       <c r="Q414" t="n">
         <v>7501</v>
@@ -28058,7 +28058,7 @@
         <v>75.01000000000001</v>
       </c>
       <c r="S414" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T414" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>38.54</v>
       </c>
       <c r="S415" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T415" t="inlineStr">
         <is>
@@ -28198,7 +28198,7 @@
         <v>45.48</v>
       </c>
       <c r="S416" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T416" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>62.27</v>
       </c>
       <c r="S417" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T417" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>35.45</v>
       </c>
       <c r="S418" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T418" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>64.45999999999999</v>
       </c>
       <c r="S419" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T419" t="inlineStr">
         <is>
@@ -28478,7 +28478,7 @@
         <v>69.11</v>
       </c>
       <c r="S420" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T420" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>84.81999999999999</v>
       </c>
       <c r="S421" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T421" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>82.53</v>
       </c>
       <c r="S422" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T422" t="inlineStr">
         <is>
@@ -28688,7 +28688,7 @@
         <v>62.79</v>
       </c>
       <c r="S423" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T423" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>91.27</v>
       </c>
       <c r="S424" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T424" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>35.81</v>
       </c>
       <c r="S425" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T425" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>47.26</v>
       </c>
       <c r="S426" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T426" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>46.39</v>
       </c>
       <c r="S427" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T427" t="inlineStr">
         <is>
@@ -29029,16 +29029,16 @@
         <v>5628</v>
       </c>
       <c r="P428" t="n">
-        <v>5869</v>
+        <v>6049</v>
       </c>
       <c r="Q428" t="n">
-        <v>5869</v>
+        <v>6049</v>
       </c>
       <c r="R428" t="n">
-        <v>58.69</v>
+        <v>60.49</v>
       </c>
       <c r="S428" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T428" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>54.2</v>
       </c>
       <c r="S429" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T429" t="inlineStr">
         <is>
@@ -29178,7 +29178,7 @@
         <v>56.19</v>
       </c>
       <c r="S430" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T430" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         <v>49.2</v>
       </c>
       <c r="S431" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T431" t="inlineStr">
         <is>
@@ -29318,7 +29318,7 @@
         <v>48.76</v>
       </c>
       <c r="S432" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T432" t="inlineStr">
         <is>
@@ -29388,7 +29388,7 @@
         <v>48.45</v>
       </c>
       <c r="S433" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T433" t="inlineStr">
         <is>
@@ -29458,7 +29458,7 @@
         <v>43.96</v>
       </c>
       <c r="S434" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T434" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>80.65000000000001</v>
       </c>
       <c r="S435" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T435" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>26.62</v>
       </c>
       <c r="S436" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T436" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>70.72</v>
       </c>
       <c r="S437" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T437" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>63.3</v>
       </c>
       <c r="S438" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T438" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>27.75</v>
       </c>
       <c r="S439" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T439" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>20.53</v>
       </c>
       <c r="S440" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T440" t="inlineStr">
         <is>
@@ -29948,7 +29948,7 @@
         <v>31.63</v>
       </c>
       <c r="S441" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T441" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>1.96</v>
       </c>
       <c r="S442" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T442" t="inlineStr">
         <is>
@@ -30088,7 +30088,7 @@
         <v>71.98999999999999</v>
       </c>
       <c r="S443" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T443" t="inlineStr">
         <is>
@@ -30158,7 +30158,7 @@
         <v>64.19</v>
       </c>
       <c r="S444" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T444" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>31.08</v>
       </c>
       <c r="S445" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T445" t="inlineStr">
         <is>
@@ -30298,7 +30298,7 @@
         <v>30.87</v>
       </c>
       <c r="S446" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T446" t="inlineStr">
         <is>
@@ -30359,16 +30359,16 @@
         <v>4704</v>
       </c>
       <c r="P447" t="n">
-        <v>4876</v>
+        <v>5077</v>
       </c>
       <c r="Q447" t="n">
-        <v>4876</v>
+        <v>5077</v>
       </c>
       <c r="R447" t="n">
-        <v>48.57</v>
+        <v>50.57</v>
       </c>
       <c r="S447" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T447" t="inlineStr">
         <is>
@@ -30438,7 +30438,7 @@
         <v>92.89</v>
       </c>
       <c r="S448" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T448" t="inlineStr">
         <is>
@@ -30499,16 +30499,16 @@
         <v>4114</v>
       </c>
       <c r="P449" t="n">
-        <v>4027</v>
+        <v>5598</v>
       </c>
       <c r="Q449" t="n">
-        <v>4486</v>
+        <v>5598</v>
       </c>
       <c r="R449" t="n">
-        <v>44.86</v>
+        <v>55.98</v>
       </c>
       <c r="S449" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T449" t="inlineStr">
         <is>
@@ -30578,7 +30578,7 @@
         <v>77.15000000000001</v>
       </c>
       <c r="S450" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T450" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>87.08</v>
       </c>
       <c r="S451" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T451" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>43.67</v>
       </c>
       <c r="S452" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T452" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>77.44</v>
       </c>
       <c r="S453" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T453" t="inlineStr">
         <is>
@@ -30849,16 +30849,16 @@
         <v>6391</v>
       </c>
       <c r="P454" t="n">
-        <v>6249</v>
+        <v>7740</v>
       </c>
       <c r="Q454" t="n">
-        <v>6391</v>
+        <v>7740</v>
       </c>
       <c r="R454" t="n">
-        <v>63.91</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="S454" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T454" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>37.98</v>
       </c>
       <c r="S455" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T455" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>32.75</v>
       </c>
       <c r="S456" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T456" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>53.34</v>
       </c>
       <c r="S457" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T457" t="inlineStr">
         <is>
@@ -31138,7 +31138,7 @@
         <v>0</v>
       </c>
       <c r="S458" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T458" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>76.09</v>
       </c>
       <c r="S459" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T459" t="inlineStr">
         <is>
@@ -31269,16 +31269,16 @@
         <v>5133</v>
       </c>
       <c r="P460" t="n">
-        <v>5197</v>
+        <v>5293</v>
       </c>
       <c r="Q460" t="n">
-        <v>5197</v>
+        <v>5293</v>
       </c>
       <c r="R460" t="n">
-        <v>51.97</v>
+        <v>52.93</v>
       </c>
       <c r="S460" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T460" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>5366</v>
       </c>
       <c r="P461" t="n">
-        <v>3176</v>
+        <v>4367</v>
       </c>
       <c r="Q461" t="n">
         <v>5366</v>
@@ -31348,7 +31348,7 @@
         <v>29.98</v>
       </c>
       <c r="S461" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T461" t="inlineStr">
         <is>
@@ -31409,16 +31409,16 @@
         <v>525</v>
       </c>
       <c r="P462" t="n">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="Q462" t="n">
-        <v>576</v>
+        <v>586</v>
       </c>
       <c r="R462" t="n">
-        <v>28.8</v>
+        <v>29.3</v>
       </c>
       <c r="S462" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T462" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>61.26</v>
       </c>
       <c r="S463" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T463" t="inlineStr">
         <is>
@@ -31549,16 +31549,16 @@
         <v>4868</v>
       </c>
       <c r="P464" t="n">
-        <v>4848</v>
+        <v>4894</v>
       </c>
       <c r="Q464" t="n">
-        <v>4868</v>
+        <v>4894</v>
       </c>
       <c r="R464" t="n">
-        <v>67.89</v>
+        <v>68.25</v>
       </c>
       <c r="S464" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T464" t="inlineStr">
         <is>
@@ -31628,7 +31628,7 @@
         <v>69.64</v>
       </c>
       <c r="S465" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T465" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>78.83</v>
       </c>
       <c r="S466" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T466" t="inlineStr">
         <is>
@@ -31768,7 +31768,7 @@
         <v>86.27</v>
       </c>
       <c r="S467" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T467" t="inlineStr">
         <is>
@@ -31838,7 +31838,7 @@
         <v>74.13</v>
       </c>
       <c r="S468" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T468" t="inlineStr">
         <is>
@@ -31908,7 +31908,7 @@
         <v>42.79</v>
       </c>
       <c r="S469" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T469" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>73.84999999999999</v>
       </c>
       <c r="S470" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T470" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>70.69</v>
       </c>
       <c r="S471" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T471" t="inlineStr">
         <is>
@@ -32118,7 +32118,7 @@
         <v>61.32</v>
       </c>
       <c r="S472" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T472" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>76.45999999999999</v>
       </c>
       <c r="S473" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T473" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44.52</v>
       </c>
       <c r="S474" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T474" t="inlineStr">
         <is>
@@ -32328,7 +32328,7 @@
         <v>30.08</v>
       </c>
       <c r="S475" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T475" t="inlineStr">
         <is>
@@ -32398,7 +32398,7 @@
         <v>89.40000000000001</v>
       </c>
       <c r="S476" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T476" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>71.79000000000001</v>
       </c>
       <c r="S477" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T477" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>10.82</v>
       </c>
       <c r="S478" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T478" t="inlineStr">
         <is>
@@ -32608,7 +32608,7 @@
         <v>87.76000000000001</v>
       </c>
       <c r="S479" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T479" t="inlineStr">
         <is>
@@ -32669,7 +32669,7 @@
         <v>8975</v>
       </c>
       <c r="P480" t="n">
-        <v>8897</v>
+        <v>8942</v>
       </c>
       <c r="Q480" t="n">
         <v>8975</v>
@@ -32678,7 +32678,7 @@
         <v>89.75</v>
       </c>
       <c r="S480" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T480" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>50.52</v>
       </c>
       <c r="S481" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T481" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>38.41</v>
       </c>
       <c r="S482" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T482" t="inlineStr">
         <is>
@@ -32888,7 +32888,7 @@
         <v>78.08</v>
       </c>
       <c r="S483" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T483" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>22.72</v>
       </c>
       <c r="S484" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T484" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>29.41</v>
       </c>
       <c r="S485" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T485" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>51.04</v>
       </c>
       <c r="S486" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T486" t="inlineStr">
         <is>
@@ -33168,7 +33168,7 @@
         <v>40.37</v>
       </c>
       <c r="S487" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T487" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>40.08</v>
       </c>
       <c r="S488" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T488" t="inlineStr">
         <is>
@@ -33299,16 +33299,16 @@
         <v>4966</v>
       </c>
       <c r="P489" t="n">
-        <v>5269</v>
+        <v>5379</v>
       </c>
       <c r="Q489" t="n">
-        <v>5269</v>
+        <v>5379</v>
       </c>
       <c r="R489" t="n">
-        <v>52.69</v>
+        <v>53.79</v>
       </c>
       <c r="S489" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T489" t="inlineStr">
         <is>
@@ -33369,16 +33369,16 @@
         <v>9169</v>
       </c>
       <c r="P490" t="n">
-        <v>9210</v>
+        <v>9270</v>
       </c>
       <c r="Q490" t="n">
-        <v>9210</v>
+        <v>9270</v>
       </c>
       <c r="R490" t="n">
-        <v>70.84999999999999</v>
+        <v>71.31</v>
       </c>
       <c r="S490" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T490" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>44.36</v>
       </c>
       <c r="S491" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T491" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>51.76</v>
       </c>
       <c r="S492" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T492" t="inlineStr">
         <is>
@@ -33579,16 +33579,16 @@
         <v>4717</v>
       </c>
       <c r="P493" t="n">
-        <v>4727</v>
+        <v>4744</v>
       </c>
       <c r="Q493" t="n">
-        <v>4727</v>
+        <v>4744</v>
       </c>
       <c r="R493" t="n">
-        <v>47.09</v>
+        <v>47.26</v>
       </c>
       <c r="S493" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T493" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>41.12</v>
       </c>
       <c r="S494" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T494" t="inlineStr">
         <is>
@@ -33728,7 +33728,7 @@
         <v>57.66</v>
       </c>
       <c r="S495" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T495" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>52.9</v>
       </c>
       <c r="S496" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T496" t="inlineStr">
         <is>
@@ -33868,7 +33868,7 @@
         <v>44.09</v>
       </c>
       <c r="S497" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T497" t="inlineStr">
         <is>
@@ -33938,7 +33938,7 @@
         <v>41.87</v>
       </c>
       <c r="S498" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T498" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>81.84</v>
       </c>
       <c r="S499" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T499" t="inlineStr">
         <is>
@@ -34078,7 +34078,7 @@
         <v>39.72</v>
       </c>
       <c r="S500" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T500" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>3660</v>
       </c>
       <c r="P501" t="n">
-        <v>3555</v>
+        <v>3569</v>
       </c>
       <c r="Q501" t="n">
         <v>3660</v>
@@ -34148,7 +34148,7 @@
         <v>52.29</v>
       </c>
       <c r="S501" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T501" t="inlineStr">
         <is>
@@ -34218,7 +34218,7 @@
         <v>75.37</v>
       </c>
       <c r="S502" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T502" t="inlineStr">
         <is>
@@ -34288,7 +34288,7 @@
         <v>56.7</v>
       </c>
       <c r="S503" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T503" t="inlineStr">
         <is>
@@ -34358,7 +34358,7 @@
         <v>72.55</v>
       </c>
       <c r="S504" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T504" t="inlineStr">
         <is>
@@ -34428,7 +34428,7 @@
         <v>39.38</v>
       </c>
       <c r="S505" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T505" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>26.75</v>
       </c>
       <c r="S506" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T506" t="inlineStr">
         <is>
@@ -34559,16 +34559,16 @@
         <v>2776</v>
       </c>
       <c r="P507" t="n">
-        <v>3336</v>
+        <v>3344</v>
       </c>
       <c r="Q507" t="n">
-        <v>3336</v>
+        <v>3344</v>
       </c>
       <c r="R507" t="n">
-        <v>33.36</v>
+        <v>33.44</v>
       </c>
       <c r="S507" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T507" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>7115</v>
       </c>
       <c r="P508" t="n">
-        <v>7306</v>
+        <v>7358</v>
       </c>
       <c r="Q508" t="n">
         <v>8169</v>
@@ -34638,7 +34638,7 @@
         <v>81.69</v>
       </c>
       <c r="S508" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T508" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>44.63</v>
       </c>
       <c r="S509" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T509" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>58.63</v>
       </c>
       <c r="S510" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T510" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>39.58</v>
       </c>
       <c r="S511" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T511" t="inlineStr">
         <is>
@@ -34918,7 +34918,7 @@
         <v>76.65000000000001</v>
       </c>
       <c r="S512" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T512" t="inlineStr">
         <is>
@@ -34988,7 +34988,7 @@
         <v>63.35</v>
       </c>
       <c r="S513" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T513" t="inlineStr">
         <is>
@@ -35058,7 +35058,7 @@
         <v>0</v>
       </c>
       <c r="S514" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T514" t="inlineStr">
         <is>
@@ -35128,7 +35128,7 @@
         <v>91.55</v>
       </c>
       <c r="S515" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T515" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>5093</v>
       </c>
       <c r="P516" t="n">
-        <v>4820</v>
+        <v>4911</v>
       </c>
       <c r="Q516" t="n">
         <v>5093</v>
@@ -35198,7 +35198,7 @@
         <v>50.93</v>
       </c>
       <c r="S516" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T516" t="inlineStr">
         <is>
@@ -35268,7 +35268,7 @@
         <v>40.99</v>
       </c>
       <c r="S517" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T517" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>47.12</v>
       </c>
       <c r="S518" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T518" t="inlineStr">
         <is>
@@ -35408,7 +35408,7 @@
         <v>1.09</v>
       </c>
       <c r="S519" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T519" t="inlineStr">
         <is>
@@ -35478,7 +35478,7 @@
         <v>74.87</v>
       </c>
       <c r="S520" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T520" t="inlineStr">
         <is>
@@ -35548,7 +35548,7 @@
         <v>43.3</v>
       </c>
       <c r="S521" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T521" t="inlineStr">
         <is>
@@ -35609,16 +35609,16 @@
         <v>6020</v>
       </c>
       <c r="P522" t="n">
-        <v>5877</v>
+        <v>6033</v>
       </c>
       <c r="Q522" t="n">
-        <v>6020</v>
+        <v>6033</v>
       </c>
       <c r="R522" t="n">
-        <v>60.2</v>
+        <v>60.33</v>
       </c>
       <c r="S522" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T522" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>35.96</v>
       </c>
       <c r="S523" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T523" t="inlineStr">
         <is>
@@ -35758,7 +35758,7 @@
         <v>18.88</v>
       </c>
       <c r="S524" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T524" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>26.81</v>
       </c>
       <c r="S525" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T525" t="inlineStr">
         <is>
@@ -35898,7 +35898,7 @@
         <v>62.27</v>
       </c>
       <c r="S526" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T526" t="inlineStr">
         <is>
@@ -35968,7 +35968,7 @@
         <v>48.05</v>
       </c>
       <c r="S527" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T527" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>0</v>
       </c>
       <c r="S528" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T528" t="inlineStr">
         <is>
@@ -36099,7 +36099,7 @@
         <v>550</v>
       </c>
       <c r="P529" t="n">
-        <v>524</v>
+        <v>565</v>
       </c>
       <c r="Q529" t="n">
         <v>1035</v>
@@ -36108,7 +36108,7 @@
         <v>25.87</v>
       </c>
       <c r="S529" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T529" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>127.22</v>
       </c>
       <c r="S530" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T530" t="inlineStr">
         <is>
@@ -36248,7 +36248,7 @@
         <v>87.43000000000001</v>
       </c>
       <c r="S531" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T531" t="inlineStr">
         <is>
@@ -36318,7 +36318,7 @@
         <v>71.90000000000001</v>
       </c>
       <c r="S532" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T532" t="inlineStr">
         <is>
@@ -36379,16 +36379,16 @@
         <v>665</v>
       </c>
       <c r="P533" t="n">
-        <v>631</v>
+        <v>919</v>
       </c>
       <c r="Q533" t="n">
-        <v>707</v>
+        <v>919</v>
       </c>
       <c r="R533" t="n">
-        <v>35.35</v>
+        <v>45.95</v>
       </c>
       <c r="S533" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T533" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
       <c r="Q534" t="inlineStr"/>
       <c r="R534" t="inlineStr"/>
       <c r="S534" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T534" t="inlineStr">
         <is>
@@ -36504,7 +36504,7 @@
         <v>42.07</v>
       </c>
       <c r="S535" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T535" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>39.14</v>
       </c>
       <c r="S536" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T536" t="inlineStr">
         <is>
@@ -36644,7 +36644,7 @@
         <v>39.71</v>
       </c>
       <c r="S537" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T537" t="inlineStr">
         <is>
@@ -36705,16 +36705,16 @@
         <v>7893</v>
       </c>
       <c r="P538" t="n">
-        <v>7914</v>
+        <v>8199</v>
       </c>
       <c r="Q538" t="n">
-        <v>7914</v>
+        <v>8199</v>
       </c>
       <c r="R538" t="n">
-        <v>55.34</v>
+        <v>57.34</v>
       </c>
       <c r="S538" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T538" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
       <c r="Q539" t="inlineStr"/>
       <c r="R539" t="inlineStr"/>
       <c r="S539" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T539" t="inlineStr">
         <is>
@@ -36830,7 +36830,7 @@
         <v>39.61</v>
       </c>
       <c r="S540" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T540" t="inlineStr">
         <is>
@@ -36876,7 +36876,7 @@
       <c r="Q541" t="inlineStr"/>
       <c r="R541" t="inlineStr"/>
       <c r="S541" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T541" t="inlineStr">
         <is>
@@ -36937,7 +36937,7 @@
         <v>435</v>
       </c>
       <c r="P542" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="Q542" t="n">
         <v>3755</v>
@@ -36946,7 +36946,7 @@
         <v>37.55</v>
       </c>
       <c r="S542" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T542" t="inlineStr">
         <is>
@@ -37016,7 +37016,7 @@
         <v>50.12</v>
       </c>
       <c r="S543" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T543" t="inlineStr">
         <is>
@@ -37077,7 +37077,7 @@
         <v>5417</v>
       </c>
       <c r="P544" t="n">
-        <v>2881</v>
+        <v>2663</v>
       </c>
       <c r="Q544" t="n">
         <v>6510</v>
@@ -37086,7 +37086,7 @@
         <v>65.09999999999999</v>
       </c>
       <c r="S544" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T544" t="inlineStr">
         <is>
@@ -37147,7 +37147,7 @@
         <v>6861</v>
       </c>
       <c r="P545" t="n">
-        <v>2560</v>
+        <v>2427</v>
       </c>
       <c r="Q545" t="n">
         <v>6861</v>
@@ -37156,7 +37156,7 @@
         <v>62.37</v>
       </c>
       <c r="S545" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T545" t="inlineStr">
         <is>
@@ -37226,7 +37226,7 @@
         <v>90.11</v>
       </c>
       <c r="S546" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T546" t="inlineStr">
         <is>
@@ -37296,7 +37296,7 @@
         <v>77.02</v>
       </c>
       <c r="S547" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T547" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>34.11</v>
       </c>
       <c r="S548" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T548" t="inlineStr">
         <is>
@@ -37427,7 +37427,7 @@
         <v>3810</v>
       </c>
       <c r="P549" t="n">
-        <v>925</v>
+        <v>791</v>
       </c>
       <c r="Q549" t="n">
         <v>3847</v>
@@ -37436,7 +37436,7 @@
         <v>34.97</v>
       </c>
       <c r="S549" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T549" t="inlineStr">
         <is>
@@ -37506,7 +37506,7 @@
         <v>36.74</v>
       </c>
       <c r="S550" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T550" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>1.04</v>
       </c>
       <c r="S551" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T551" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
       <c r="Q552" t="inlineStr"/>
       <c r="R552" t="inlineStr"/>
       <c r="S552" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T552" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>57.14</v>
       </c>
       <c r="S553" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T553" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>529</v>
       </c>
       <c r="P554" t="n">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="Q554" t="n">
         <v>603</v>
@@ -37762,7 +37762,7 @@
         <v>6.03</v>
       </c>
       <c r="S554" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T554" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
       <c r="Q555" t="inlineStr"/>
       <c r="R555" t="inlineStr"/>
       <c r="S555" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T555" t="inlineStr">
         <is>
@@ -37854,7 +37854,7 @@
       <c r="Q556" t="inlineStr"/>
       <c r="R556" t="inlineStr"/>
       <c r="S556" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T556" t="inlineStr">
         <is>
@@ -37915,16 +37915,16 @@
         <v>1904</v>
       </c>
       <c r="P557" t="n">
-        <v>2157</v>
+        <v>2338</v>
       </c>
       <c r="Q557" t="n">
-        <v>2157</v>
+        <v>2338</v>
       </c>
       <c r="R557" t="n">
-        <v>10.78</v>
+        <v>11.69</v>
       </c>
       <c r="S557" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T557" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>16.72</v>
       </c>
       <c r="S558" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T558" t="inlineStr">
         <is>
@@ -38055,7 +38055,7 @@
         <v>5382</v>
       </c>
       <c r="P559" t="n">
-        <v>4279</v>
+        <v>4754</v>
       </c>
       <c r="Q559" t="n">
         <v>5382</v>
@@ -38064,7 +38064,7 @@
         <v>21.53</v>
       </c>
       <c r="S559" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T559" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
       <c r="Q560" t="inlineStr"/>
       <c r="R560" t="inlineStr"/>
       <c r="S560" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T560" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>74.3</v>
       </c>
       <c r="S561" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T561" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>4348</v>
       </c>
       <c r="P562" t="n">
-        <v>3824</v>
+        <v>4224</v>
       </c>
       <c r="Q562" t="n">
         <v>4348</v>
@@ -38250,7 +38250,7 @@
         <v>76.28</v>
       </c>
       <c r="S562" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T562" t="inlineStr">
         <is>
@@ -38320,7 +38320,7 @@
         <v>64.39</v>
       </c>
       <c r="S563" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T563" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>57.77</v>
       </c>
       <c r="S564" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T564" t="inlineStr">
         <is>
@@ -38436,7 +38436,7 @@
       <c r="Q565" t="inlineStr"/>
       <c r="R565" t="inlineStr"/>
       <c r="S565" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T565" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>99.09999999999999</v>
       </c>
       <c r="S566" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T566" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>58.07</v>
       </c>
       <c r="S567" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T567" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>43.67</v>
       </c>
       <c r="S568" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T568" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>40.04</v>
       </c>
       <c r="S569" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T569" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>40.12</v>
       </c>
       <c r="S570" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T570" t="inlineStr">
         <is>
@@ -38847,16 +38847,16 @@
         <v>5101</v>
       </c>
       <c r="P571" t="n">
-        <v>5939</v>
+        <v>6088</v>
       </c>
       <c r="Q571" t="n">
-        <v>5939</v>
+        <v>6088</v>
       </c>
       <c r="R571" t="n">
-        <v>84.84</v>
+        <v>86.97</v>
       </c>
       <c r="S571" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T571" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>25.93</v>
       </c>
       <c r="S572" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T572" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>67.55</v>
       </c>
       <c r="S573" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T573" t="inlineStr">
         <is>
@@ -39066,7 +39066,7 @@
         <v>71.06</v>
       </c>
       <c r="S574" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T574" t="inlineStr">
         <is>
@@ -39127,7 +39127,7 @@
         <v>4100</v>
       </c>
       <c r="P575" t="n">
-        <v>4193</v>
+        <v>4423</v>
       </c>
       <c r="Q575" t="n">
         <v>5088</v>
@@ -39136,7 +39136,7 @@
         <v>42.4</v>
       </c>
       <c r="S575" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T575" t="inlineStr">
         <is>
@@ -39206,7 +39206,7 @@
         <v>53.36</v>
       </c>
       <c r="S576" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T576" t="inlineStr">
         <is>
@@ -39276,7 +39276,7 @@
         <v>49.62</v>
       </c>
       <c r="S577" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T577" t="inlineStr">
         <is>
@@ -39322,7 +39322,7 @@
       <c r="Q578" t="inlineStr"/>
       <c r="R578" t="inlineStr"/>
       <c r="S578" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T578" t="inlineStr">
         <is>
@@ -39392,7 +39392,7 @@
         <v>46.67</v>
       </c>
       <c r="S579" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T579" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>97.56</v>
       </c>
       <c r="S580" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T580" t="inlineStr">
         <is>
@@ -39532,7 +39532,7 @@
         <v>72.59</v>
       </c>
       <c r="S581" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T581" t="inlineStr">
         <is>
@@ -39602,7 +39602,7 @@
         <v>87.81999999999999</v>
       </c>
       <c r="S582" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T582" t="inlineStr">
         <is>
@@ -39672,7 +39672,7 @@
         <v>59.79</v>
       </c>
       <c r="S583" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T583" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>59.72</v>
       </c>
       <c r="S584" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T584" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>39.59</v>
       </c>
       <c r="S585" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T585" t="inlineStr">
         <is>
@@ -39873,16 +39873,16 @@
         <v>2992</v>
       </c>
       <c r="P586" t="n">
-        <v>3005</v>
+        <v>3230</v>
       </c>
       <c r="Q586" t="n">
-        <v>3204</v>
+        <v>3230</v>
       </c>
       <c r="R586" t="n">
-        <v>29.79</v>
+        <v>30.03</v>
       </c>
       <c r="S586" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T586" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>2423</v>
       </c>
       <c r="P587" t="n">
-        <v>21</v>
+        <v>1970</v>
       </c>
       <c r="Q587" t="n">
         <v>3670</v>
@@ -39952,7 +39952,7 @@
         <v>36.7</v>
       </c>
       <c r="S587" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T587" t="inlineStr">
         <is>
@@ -40022,7 +40022,7 @@
         <v>93.7</v>
       </c>
       <c r="S588" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T588" t="inlineStr">
         <is>
@@ -40092,7 +40092,7 @@
         <v>15.24</v>
       </c>
       <c r="S589" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T589" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>34.74</v>
       </c>
       <c r="S590" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T590" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>62.45</v>
       </c>
       <c r="S591" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T591" t="inlineStr">
         <is>
@@ -40293,7 +40293,7 @@
         <v>398</v>
       </c>
       <c r="P592" t="n">
-        <v>398</v>
+        <v>349</v>
       </c>
       <c r="Q592" t="n">
         <v>398</v>
@@ -40302,7 +40302,7 @@
         <v>3.98</v>
       </c>
       <c r="S592" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T592" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>67.06</v>
       </c>
       <c r="S593" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T593" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>67.54000000000001</v>
       </c>
       <c r="S594" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
@@ -40512,7 +40512,7 @@
         <v>29.57</v>
       </c>
       <c r="S595" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T595" t="inlineStr">
         <is>
@@ -40582,7 +40582,7 @@
         <v>64</v>
       </c>
       <c r="S596" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T596" t="inlineStr">
         <is>
@@ -40652,7 +40652,7 @@
         <v>83.68000000000001</v>
       </c>
       <c r="S597" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T597" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>64.51000000000001</v>
       </c>
       <c r="S598" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T598" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>68.38</v>
       </c>
       <c r="S599" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T599" t="inlineStr">
         <is>
@@ -40853,16 +40853,16 @@
         <v>5124</v>
       </c>
       <c r="P600" t="n">
-        <v>7860</v>
+        <v>7646</v>
       </c>
       <c r="Q600" t="n">
-        <v>7860</v>
+        <v>7646</v>
       </c>
       <c r="R600" t="n">
-        <v>78.59999999999999</v>
+        <v>76.45999999999999</v>
       </c>
       <c r="S600" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T600" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>92.23999999999999</v>
       </c>
       <c r="S601" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T601" t="inlineStr">
         <is>
@@ -41002,7 +41002,7 @@
         <v>151.18</v>
       </c>
       <c r="S602" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T602" t="inlineStr">
         <is>
@@ -41072,7 +41072,7 @@
         <v>47.21</v>
       </c>
       <c r="S603" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T603" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>66.15000000000001</v>
       </c>
       <c r="S604" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T604" t="inlineStr">
         <is>
@@ -41212,7 +41212,7 @@
         <v>47.24</v>
       </c>
       <c r="S605" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T605" t="inlineStr">
         <is>
@@ -41282,7 +41282,7 @@
         <v>32.25</v>
       </c>
       <c r="S606" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T606" t="inlineStr">
         <is>
@@ -41343,16 +41343,16 @@
         <v>7934</v>
       </c>
       <c r="P607" t="n">
-        <v>7971</v>
+        <v>8200</v>
       </c>
       <c r="Q607" t="n">
-        <v>7971</v>
+        <v>8200</v>
       </c>
       <c r="R607" t="n">
-        <v>79.70999999999999</v>
+        <v>82</v>
       </c>
       <c r="S607" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T607" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>53.07</v>
       </c>
       <c r="S608" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T608" t="inlineStr">
         <is>
@@ -41483,16 +41483,16 @@
         <v>7250</v>
       </c>
       <c r="P609" t="n">
-        <v>7892</v>
+        <v>8964</v>
       </c>
       <c r="Q609" t="n">
-        <v>7892</v>
+        <v>8964</v>
       </c>
       <c r="R609" t="n">
-        <v>78.92</v>
+        <v>89.64</v>
       </c>
       <c r="S609" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T609" t="inlineStr">
         <is>
@@ -41553,7 +41553,7 @@
         <v>3274</v>
       </c>
       <c r="P610" t="n">
-        <v>2480</v>
+        <v>2933</v>
       </c>
       <c r="Q610" t="n">
         <v>3274</v>
@@ -41562,7 +41562,7 @@
         <v>36.53</v>
       </c>
       <c r="S610" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T610" t="inlineStr">
         <is>
@@ -41632,7 +41632,7 @@
         <v>67.58</v>
       </c>
       <c r="S611" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T611" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         <v>61.6</v>
       </c>
       <c r="S612" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T612" t="inlineStr">
         <is>
@@ -41772,7 +41772,7 @@
         <v>61.17</v>
       </c>
       <c r="S613" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T613" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>22.98</v>
       </c>
       <c r="S614" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T614" t="inlineStr">
         <is>
@@ -41912,7 +41912,7 @@
         <v>76.70999999999999</v>
       </c>
       <c r="S615" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T615" t="inlineStr">
         <is>
@@ -41982,7 +41982,7 @@
         <v>70.31</v>
       </c>
       <c r="S616" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T616" t="inlineStr">
         <is>
@@ -42052,7 +42052,7 @@
         <v>62.5</v>
       </c>
       <c r="S617" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T617" t="inlineStr">
         <is>
@@ -42122,7 +42122,7 @@
         <v>45.82</v>
       </c>
       <c r="S618" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T618" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
       <c r="Q619" t="inlineStr"/>
       <c r="R619" t="inlineStr"/>
       <c r="S619" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T619" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
         <v>56.39</v>
       </c>
       <c r="S620" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T620" t="inlineStr">
         <is>
@@ -42308,7 +42308,7 @@
         <v>24.2</v>
       </c>
       <c r="S621" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T621" t="inlineStr">
         <is>
@@ -42354,7 +42354,7 @@
       <c r="Q622" t="inlineStr"/>
       <c r="R622" t="inlineStr"/>
       <c r="S622" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T622" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>41.02</v>
       </c>
       <c r="S623" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T623" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>4097</v>
       </c>
       <c r="P624" t="n">
-        <v>3527</v>
+        <v>3993</v>
       </c>
       <c r="Q624" t="n">
         <v>5528</v>
@@ -42494,7 +42494,7 @@
         <v>92.51000000000001</v>
       </c>
       <c r="S624" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T624" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>41.16</v>
       </c>
       <c r="S625" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T625" t="inlineStr">
         <is>
@@ -42634,7 +42634,7 @@
         <v>55.8</v>
       </c>
       <c r="S626" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T626" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>55.53</v>
       </c>
       <c r="S627" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T627" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>66.77</v>
       </c>
       <c r="S628" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T628" t="inlineStr">
         <is>
@@ -42844,7 +42844,7 @@
         <v>49.87</v>
       </c>
       <c r="S629" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T629" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>1450</v>
       </c>
       <c r="P630" t="n">
-        <v>1353</v>
+        <v>1500</v>
       </c>
       <c r="Q630" t="n">
         <v>1722</v>
@@ -42914,7 +42914,7 @@
         <v>19.13</v>
       </c>
       <c r="S630" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T630" t="inlineStr">
         <is>
@@ -42984,7 +42984,7 @@
         <v>36.8</v>
       </c>
       <c r="S631" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T631" t="inlineStr">
         <is>
@@ -43054,7 +43054,7 @@
         <v>58.96</v>
       </c>
       <c r="S632" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T632" t="inlineStr">
         <is>
@@ -43124,7 +43124,7 @@
         <v>28.69</v>
       </c>
       <c r="S633" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T633" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>10.68</v>
       </c>
       <c r="S634" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T634" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>85.58</v>
       </c>
       <c r="S635" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T635" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>76.2</v>
       </c>
       <c r="S636" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T636" t="inlineStr">
         <is>
@@ -43404,7 +43404,7 @@
         <v>29.45</v>
       </c>
       <c r="S637" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T637" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>7248</v>
       </c>
       <c r="P638" t="n">
-        <v>4412</v>
+        <v>4823</v>
       </c>
       <c r="Q638" t="n">
         <v>9088</v>
@@ -43474,7 +43474,7 @@
         <v>95.05</v>
       </c>
       <c r="S638" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T638" t="inlineStr">
         <is>
@@ -43535,7 +43535,7 @@
         <v>7734</v>
       </c>
       <c r="P639" t="n">
-        <v>7157</v>
+        <v>7593</v>
       </c>
       <c r="Q639" t="n">
         <v>8193</v>
@@ -43544,7 +43544,7 @@
         <v>85.69</v>
       </c>
       <c r="S639" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T639" t="inlineStr">
         <is>
@@ -43614,7 +43614,7 @@
         <v>44.15</v>
       </c>
       <c r="S640" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T640" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>49.8</v>
       </c>
       <c r="S641" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T641" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>48.85</v>
       </c>
       <c r="S642" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T642" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>34.93</v>
       </c>
       <c r="S643" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T643" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>46.87</v>
       </c>
       <c r="S644" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T644" t="inlineStr">
         <is>
@@ -43964,7 +43964,7 @@
         <v>19.09</v>
       </c>
       <c r="S645" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T645" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>54.33</v>
       </c>
       <c r="S646" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T646" t="inlineStr">
         <is>
@@ -44104,7 +44104,7 @@
         <v>65.40000000000001</v>
       </c>
       <c r="S647" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T647" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>34.89</v>
       </c>
       <c r="S648" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T648" t="inlineStr">
         <is>
@@ -44244,7 +44244,7 @@
         <v>56.83</v>
       </c>
       <c r="S649" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T649" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>29.74</v>
       </c>
       <c r="S650" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T650" t="inlineStr">
         <is>
@@ -44384,7 +44384,7 @@
         <v>61.72</v>
       </c>
       <c r="S651" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T651" t="inlineStr">
         <is>
@@ -44454,7 +44454,7 @@
         <v>48.83</v>
       </c>
       <c r="S652" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T652" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>36.73</v>
       </c>
       <c r="S653" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T653" t="inlineStr">
         <is>
@@ -44585,7 +44585,7 @@
         <v>2005</v>
       </c>
       <c r="P654" t="n">
-        <v>2003</v>
+        <v>2146</v>
       </c>
       <c r="Q654" t="n">
         <v>2377</v>
@@ -44594,7 +44594,7 @@
         <v>33.96</v>
       </c>
       <c r="S654" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T654" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>74.06</v>
       </c>
       <c r="S655" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T655" t="inlineStr">
         <is>
@@ -44710,7 +44710,7 @@
       <c r="Q656" t="inlineStr"/>
       <c r="R656" t="inlineStr"/>
       <c r="S656" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T656" t="inlineStr">
         <is>
@@ -44780,7 +44780,7 @@
         <v>79.13</v>
       </c>
       <c r="S657" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T657" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>8291</v>
       </c>
       <c r="P658" t="n">
-        <v>6230</v>
+        <v>7026</v>
       </c>
       <c r="Q658" t="n">
         <v>9245</v>
@@ -44850,7 +44850,7 @@
         <v>92.45</v>
       </c>
       <c r="S658" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T658" t="inlineStr">
         <is>
@@ -44911,7 +44911,7 @@
         <v>5275</v>
       </c>
       <c r="P659" t="n">
-        <v>3434</v>
+        <v>3212</v>
       </c>
       <c r="Q659" t="n">
         <v>9224</v>
@@ -44920,7 +44920,7 @@
         <v>92.23999999999999</v>
       </c>
       <c r="S659" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T659" t="inlineStr">
         <is>
@@ -44981,7 +44981,7 @@
         <v>10585</v>
       </c>
       <c r="P660" t="n">
-        <v>6649</v>
+        <v>6978</v>
       </c>
       <c r="Q660" t="n">
         <v>10585</v>
@@ -44990,7 +44990,7 @@
         <v>105.85</v>
       </c>
       <c r="S660" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T660" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>111.93</v>
       </c>
       <c r="S661" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T661" t="inlineStr">
         <is>
@@ -45130,7 +45130,7 @@
         <v>8.59</v>
       </c>
       <c r="S662" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T662" t="inlineStr">
         <is>
@@ -45200,7 +45200,7 @@
         <v>85.81</v>
       </c>
       <c r="S663" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T663" t="inlineStr">
         <is>
@@ -45270,7 +45270,7 @@
         <v>92.91</v>
       </c>
       <c r="S664" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T664" t="inlineStr">
         <is>
@@ -45340,7 +45340,7 @@
         <v>94.81999999999999</v>
       </c>
       <c r="S665" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T665" t="inlineStr">
         <is>
@@ -45410,7 +45410,7 @@
         <v>69.70999999999999</v>
       </c>
       <c r="S666" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T666" t="inlineStr">
         <is>
@@ -45480,7 +45480,7 @@
         <v>10.57</v>
       </c>
       <c r="S667" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T667" t="inlineStr">
         <is>
@@ -45550,7 +45550,7 @@
         <v>92.61</v>
       </c>
       <c r="S668" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T668" t="inlineStr">
         <is>
@@ -45620,7 +45620,7 @@
         <v>79.34</v>
       </c>
       <c r="S669" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T669" t="inlineStr">
         <is>
@@ -45681,7 +45681,7 @@
         <v>8128</v>
       </c>
       <c r="P670" t="n">
-        <v>7073</v>
+        <v>7688</v>
       </c>
       <c r="Q670" t="n">
         <v>8128</v>
@@ -45690,7 +45690,7 @@
         <v>90.68000000000001</v>
       </c>
       <c r="S670" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T670" t="inlineStr">
         <is>
@@ -45760,7 +45760,7 @@
         <v>44.11</v>
       </c>
       <c r="S671" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T671" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>4216</v>
       </c>
       <c r="P672" t="n">
-        <v>2513</v>
+        <v>2632</v>
       </c>
       <c r="Q672" t="n">
         <v>5639</v>
@@ -45830,7 +45830,7 @@
         <v>78.64</v>
       </c>
       <c r="S672" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T672" t="inlineStr">
         <is>
@@ -45900,7 +45900,7 @@
         <v>25.82</v>
       </c>
       <c r="S673" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T673" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>4967</v>
       </c>
       <c r="P674" t="n">
-        <v>4421</v>
+        <v>4477</v>
       </c>
       <c r="Q674" t="n">
         <v>5957</v>
@@ -45970,7 +45970,7 @@
         <v>49.64</v>
       </c>
       <c r="S674" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T674" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>77.86</v>
       </c>
       <c r="S675" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T675" t="inlineStr">
         <is>
@@ -46110,7 +46110,7 @@
         <v>72.38</v>
       </c>
       <c r="S676" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T676" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>94.14</v>
       </c>
       <c r="S677" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T677" t="inlineStr">
         <is>
@@ -46250,7 +46250,7 @@
         <v>42.84</v>
       </c>
       <c r="S678" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T678" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>66.8</v>
       </c>
       <c r="S679" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T679" t="inlineStr">
         <is>
@@ -46390,7 +46390,7 @@
         <v>42.53</v>
       </c>
       <c r="S680" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T680" t="inlineStr">
         <is>
@@ -46460,7 +46460,7 @@
         <v>78.41</v>
       </c>
       <c r="S681" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T681" t="inlineStr">
         <is>
@@ -46530,7 +46530,7 @@
         <v>54.68</v>
       </c>
       <c r="S682" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T682" t="inlineStr">
         <is>
@@ -46600,7 +46600,7 @@
         <v>65.20999999999999</v>
       </c>
       <c r="S683" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T683" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>8124</v>
       </c>
       <c r="P684" t="n">
-        <v>0</v>
+        <v>901</v>
       </c>
       <c r="Q684" t="n">
         <v>13027</v>
@@ -46670,7 +46670,7 @@
         <v>81.42</v>
       </c>
       <c r="S684" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T684" t="inlineStr">
         <is>
@@ -46740,7 +46740,7 @@
         <v>56.07</v>
       </c>
       <c r="S685" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T685" t="inlineStr">
         <is>
@@ -46786,7 +46786,7 @@
       <c r="Q686" t="inlineStr"/>
       <c r="R686" t="inlineStr"/>
       <c r="S686" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T686" t="inlineStr">
         <is>
@@ -46832,7 +46832,7 @@
       <c r="Q687" t="inlineStr"/>
       <c r="R687" t="inlineStr"/>
       <c r="S687" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T687" t="inlineStr">
         <is>
@@ -46902,7 +46902,7 @@
         <v>8.949999999999999</v>
       </c>
       <c r="S688" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T688" t="inlineStr">
         <is>
@@ -46972,7 +46972,7 @@
         <v>51</v>
       </c>
       <c r="S689" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T689" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>8.65</v>
       </c>
       <c r="S690" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T690" t="inlineStr">
         <is>
@@ -47112,7 +47112,7 @@
         <v>50.79</v>
       </c>
       <c r="S691" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T691" t="inlineStr">
         <is>
@@ -47182,7 +47182,7 @@
         <v>78.69</v>
       </c>
       <c r="S692" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T692" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>92.51000000000001</v>
       </c>
       <c r="S693" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T693" t="inlineStr">
         <is>
@@ -47322,7 +47322,7 @@
         <v>91.09999999999999</v>
       </c>
       <c r="S694" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T694" t="inlineStr">
         <is>
@@ -47392,7 +47392,7 @@
         <v>79.7</v>
       </c>
       <c r="S695" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T695" t="inlineStr">
         <is>
@@ -47462,7 +47462,7 @@
         <v>85.40000000000001</v>
       </c>
       <c r="S696" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T696" t="inlineStr">
         <is>
@@ -47532,7 +47532,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="S697" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T697" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>68.45</v>
       </c>
       <c r="S698" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T698" t="inlineStr">
         <is>
@@ -47663,16 +47663,16 @@
         <v>6744</v>
       </c>
       <c r="P699" t="n">
-        <v>6642</v>
+        <v>6882</v>
       </c>
       <c r="Q699" t="n">
-        <v>6813</v>
+        <v>6882</v>
       </c>
       <c r="R699" t="n">
-        <v>68.13</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="S699" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T699" t="inlineStr">
         <is>
@@ -47742,7 +47742,7 @@
         <v>50.14</v>
       </c>
       <c r="S700" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T700" t="inlineStr">
         <is>
@@ -47812,7 +47812,7 @@
         <v>6.9</v>
       </c>
       <c r="S701" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T701" t="inlineStr">
         <is>
@@ -47873,16 +47873,16 @@
         <v>2843</v>
       </c>
       <c r="P702" t="n">
-        <v>2940</v>
+        <v>2632</v>
       </c>
       <c r="Q702" t="n">
-        <v>2940</v>
+        <v>2843</v>
       </c>
       <c r="R702" t="n">
-        <v>42</v>
+        <v>40.61</v>
       </c>
       <c r="S702" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T702" t="inlineStr">
         <is>
@@ -47952,7 +47952,7 @@
         <v>12.25</v>
       </c>
       <c r="S703" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T703" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>6.83</v>
       </c>
       <c r="S704" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T704" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>37.96</v>
       </c>
       <c r="S705" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T705" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>16.48</v>
       </c>
       <c r="S706" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T706" t="inlineStr">
         <is>
@@ -48232,7 +48232,7 @@
         <v>44.42</v>
       </c>
       <c r="S707" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T707" t="inlineStr">
         <is>
@@ -48302,7 +48302,7 @@
         <v>77.22</v>
       </c>
       <c r="S708" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T708" t="inlineStr">
         <is>
@@ -48372,7 +48372,7 @@
         <v>30.39</v>
       </c>
       <c r="S709" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T709" t="inlineStr">
         <is>
@@ -48442,7 +48442,7 @@
         <v>7.07</v>
       </c>
       <c r="S710" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T710" t="inlineStr">
         <is>
@@ -48512,7 +48512,7 @@
         <v>41.16</v>
       </c>
       <c r="S711" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T711" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>44.51</v>
       </c>
       <c r="S712" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T712" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>73.19</v>
       </c>
       <c r="S713" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T713" t="inlineStr">
         <is>
@@ -48713,7 +48713,7 @@
         <v>9341</v>
       </c>
       <c r="P714" t="n">
-        <v>5246</v>
+        <v>7740</v>
       </c>
       <c r="Q714" t="n">
         <v>9341</v>
@@ -48722,7 +48722,7 @@
         <v>87.3</v>
       </c>
       <c r="S714" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T714" t="inlineStr">
         <is>
@@ -48792,7 +48792,7 @@
         <v>55.91</v>
       </c>
       <c r="S715" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T715" t="inlineStr">
         <is>
@@ -48862,7 +48862,7 @@
         <v>51.57</v>
       </c>
       <c r="S716" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T716" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>14.8</v>
       </c>
       <c r="S717" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T717" t="inlineStr">
         <is>
@@ -49002,7 +49002,7 @@
         <v>55.84</v>
       </c>
       <c r="S718" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T718" t="inlineStr">
         <is>
@@ -49072,7 +49072,7 @@
         <v>73.54000000000001</v>
       </c>
       <c r="S719" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T719" t="inlineStr">
         <is>
@@ -49142,7 +49142,7 @@
         <v>60.96</v>
       </c>
       <c r="S720" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T720" t="inlineStr">
         <is>
@@ -49212,7 +49212,7 @@
         <v>0</v>
       </c>
       <c r="S721" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T721" t="inlineStr">
         <is>
@@ -49282,7 +49282,7 @@
         <v>46.25</v>
       </c>
       <c r="S722" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T722" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>85.61</v>
       </c>
       <c r="S723" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T723" t="inlineStr">
         <is>
@@ -49422,7 +49422,7 @@
         <v>92.39</v>
       </c>
       <c r="S724" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T724" t="inlineStr">
         <is>
@@ -49492,7 +49492,7 @@
         <v>55.49</v>
       </c>
       <c r="S725" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T725" t="inlineStr">
         <is>
@@ -49562,7 +49562,7 @@
         <v>58.49</v>
       </c>
       <c r="S726" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T726" t="inlineStr">
         <is>
@@ -49632,7 +49632,7 @@
         <v>69.05</v>
       </c>
       <c r="S727" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T727" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>89.18000000000001</v>
       </c>
       <c r="S728" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T728" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>0</v>
       </c>
       <c r="S729" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T729" t="inlineStr">
         <is>
@@ -49842,7 +49842,7 @@
         <v>66.40000000000001</v>
       </c>
       <c r="S730" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T730" t="inlineStr">
         <is>
@@ -49903,7 +49903,7 @@
         <v>6867</v>
       </c>
       <c r="P731" t="n">
-        <v>6273</v>
+        <v>6286</v>
       </c>
       <c r="Q731" t="n">
         <v>7742</v>
@@ -49912,7 +49912,7 @@
         <v>77.12</v>
       </c>
       <c r="S731" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T731" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>7052</v>
       </c>
       <c r="P732" t="n">
-        <v>4277</v>
+        <v>5351</v>
       </c>
       <c r="Q732" t="n">
         <v>7052</v>
@@ -49982,7 +49982,7 @@
         <v>70.25</v>
       </c>
       <c r="S732" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T732" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>73.23999999999999</v>
       </c>
       <c r="S733" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T733" t="inlineStr">
         <is>
@@ -50122,7 +50122,7 @@
         <v>94.12</v>
       </c>
       <c r="S734" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T734" t="inlineStr">
         <is>
@@ -50192,7 +50192,7 @@
         <v>76.28</v>
       </c>
       <c r="S735" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T735" t="inlineStr">
         <is>
@@ -50253,16 +50253,16 @@
         <v>7507</v>
       </c>
       <c r="P736" t="n">
-        <v>7521</v>
+        <v>7604</v>
       </c>
       <c r="Q736" t="n">
-        <v>7577</v>
+        <v>7604</v>
       </c>
       <c r="R736" t="n">
-        <v>75.48</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="S736" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T736" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         <v>67.38</v>
       </c>
       <c r="S737" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T737" t="inlineStr">
         <is>
@@ -50402,7 +50402,7 @@
         <v>58.21</v>
       </c>
       <c r="S738" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T738" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>28.85</v>
       </c>
       <c r="S739" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T739" t="inlineStr">
         <is>
@@ -50533,7 +50533,7 @@
         <v>8830</v>
       </c>
       <c r="P740" t="n">
-        <v>4692</v>
+        <v>6506</v>
       </c>
       <c r="Q740" t="n">
         <v>8830</v>
@@ -50542,7 +50542,7 @@
         <v>92.36</v>
       </c>
       <c r="S740" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T740" t="inlineStr">
         <is>
@@ -50603,7 +50603,7 @@
         <v>1267</v>
       </c>
       <c r="P741" t="n">
-        <v>1064</v>
+        <v>1400</v>
       </c>
       <c r="Q741" t="n">
         <v>1610</v>
@@ -50612,7 +50612,7 @@
         <v>13.42</v>
       </c>
       <c r="S741" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T741" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>6356</v>
       </c>
       <c r="P742" t="n">
-        <v>5058</v>
+        <v>7070</v>
       </c>
       <c r="Q742" t="n">
         <v>11079</v>
@@ -50682,7 +50682,7 @@
         <v>84.25</v>
       </c>
       <c r="S742" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T742" t="inlineStr">
         <is>
@@ -50752,7 +50752,7 @@
         <v>50.08</v>
       </c>
       <c r="S743" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T743" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>54.57</v>
       </c>
       <c r="S744" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T744" t="inlineStr">
         <is>
@@ -50883,7 +50883,7 @@
         <v>7046</v>
       </c>
       <c r="P745" t="n">
-        <v>5476</v>
+        <v>6620</v>
       </c>
       <c r="Q745" t="n">
         <v>7787</v>
@@ -50892,7 +50892,7 @@
         <v>70.79000000000001</v>
       </c>
       <c r="S745" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T745" t="inlineStr">
         <is>
@@ -50953,7 +50953,7 @@
         <v>2365</v>
       </c>
       <c r="P746" t="n">
-        <v>3116</v>
+        <v>2986</v>
       </c>
       <c r="Q746" t="n">
         <v>4293</v>
@@ -50962,7 +50962,7 @@
         <v>35.92</v>
       </c>
       <c r="S746" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T746" t="inlineStr">
         <is>
@@ -51023,7 +51023,7 @@
         <v>4170</v>
       </c>
       <c r="P747" t="n">
-        <v>3596</v>
+        <v>3820</v>
       </c>
       <c r="Q747" t="n">
         <v>5747</v>
@@ -51032,7 +51032,7 @@
         <v>73.98</v>
       </c>
       <c r="S747" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T747" t="inlineStr">
         <is>
@@ -51093,7 +51093,7 @@
         <v>5858</v>
       </c>
       <c r="P748" t="n">
-        <v>3576</v>
+        <v>4788</v>
       </c>
       <c r="Q748" t="n">
         <v>5858</v>
@@ -51102,7 +51102,7 @@
         <v>58.58</v>
       </c>
       <c r="S748" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T748" t="inlineStr">
         <is>
@@ -51163,7 +51163,7 @@
         <v>5114</v>
       </c>
       <c r="P749" t="n">
-        <v>2228</v>
+        <v>2143</v>
       </c>
       <c r="Q749" t="n">
         <v>5114</v>
@@ -51172,7 +51172,7 @@
         <v>71.03</v>
       </c>
       <c r="S749" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T749" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>20.44</v>
       </c>
       <c r="S750" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T750" t="inlineStr">
         <is>
@@ -51312,7 +51312,7 @@
         <v>30.18</v>
       </c>
       <c r="S751" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T751" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>78.09999999999999</v>
       </c>
       <c r="S752" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T752" t="inlineStr">
         <is>
@@ -51443,16 +51443,16 @@
         <v>1934</v>
       </c>
       <c r="P753" t="n">
-        <v>3593</v>
+        <v>3412</v>
       </c>
       <c r="Q753" t="n">
-        <v>3593</v>
+        <v>3412</v>
       </c>
       <c r="R753" t="n">
-        <v>44.91</v>
+        <v>42.65</v>
       </c>
       <c r="S753" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T753" t="inlineStr">
         <is>
@@ -51522,7 +51522,7 @@
         <v>44.5</v>
       </c>
       <c r="S754" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T754" t="inlineStr">
         <is>
@@ -51568,7 +51568,7 @@
       <c r="Q755" t="inlineStr"/>
       <c r="R755" t="inlineStr"/>
       <c r="S755" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T755" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>22.36</v>
       </c>
       <c r="S756" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T756" t="inlineStr">
         <is>
@@ -51708,7 +51708,7 @@
         <v>91.66</v>
       </c>
       <c r="S757" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T757" t="inlineStr">
         <is>
@@ -51769,7 +51769,7 @@
         <v>5661</v>
       </c>
       <c r="P758" t="n">
-        <v>4109</v>
+        <v>4835</v>
       </c>
       <c r="Q758" t="n">
         <v>5661</v>
@@ -51778,7 +51778,7 @@
         <v>80.87</v>
       </c>
       <c r="S758" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T758" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>90.94</v>
       </c>
       <c r="S759" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T759" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>38.96</v>
       </c>
       <c r="S760" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T760" t="inlineStr">
         <is>
@@ -51988,7 +51988,7 @@
         <v>91.44</v>
       </c>
       <c r="S761" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T761" t="inlineStr">
         <is>
@@ -52049,16 +52049,16 @@
         <v>1268</v>
       </c>
       <c r="P762" t="n">
-        <v>1343</v>
+        <v>1604</v>
       </c>
       <c r="Q762" t="n">
-        <v>1343</v>
+        <v>1604</v>
       </c>
       <c r="R762" t="n">
-        <v>27.98</v>
+        <v>33.42</v>
       </c>
       <c r="S762" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T762" t="inlineStr">
         <is>
@@ -52128,7 +52128,7 @@
         <v>79.34</v>
       </c>
       <c r="S763" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T763" t="inlineStr">
         <is>
@@ -52198,7 +52198,7 @@
         <v>30.49</v>
       </c>
       <c r="S764" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T764" t="inlineStr">
         <is>
@@ -52268,7 +52268,7 @@
         <v>75.7</v>
       </c>
       <c r="S765" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T765" t="inlineStr">
         <is>
@@ -52338,7 +52338,7 @@
         <v>16.58</v>
       </c>
       <c r="S766" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T766" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>43.87</v>
       </c>
       <c r="S767" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T767" t="inlineStr">
         <is>
@@ -52478,7 +52478,7 @@
         <v>35.92</v>
       </c>
       <c r="S768" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T768" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>28.25</v>
       </c>
       <c r="S769" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T769" t="inlineStr">
         <is>
@@ -52618,7 +52618,7 @@
         <v>32.36</v>
       </c>
       <c r="S770" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T770" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>5878</v>
       </c>
       <c r="P771" t="n">
-        <v>4901</v>
+        <v>4947</v>
       </c>
       <c r="Q771" t="n">
         <v>5878</v>
@@ -52688,7 +52688,7 @@
         <v>49.81</v>
       </c>
       <c r="S771" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T771" t="inlineStr">
         <is>
@@ -52758,7 +52758,7 @@
         <v>129.83</v>
       </c>
       <c r="S772" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T772" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45.47</v>
       </c>
       <c r="S773" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T773" t="inlineStr">
         <is>
@@ -52874,7 +52874,7 @@
       <c r="Q774" t="inlineStr"/>
       <c r="R774" t="inlineStr"/>
       <c r="S774" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T774" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>158824.8</v>
       </c>
       <c r="S775" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T775" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>52.98</v>
       </c>
       <c r="S776" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T776" t="inlineStr">
         <is>
@@ -53060,7 +53060,7 @@
       <c r="Q777" t="inlineStr"/>
       <c r="R777" t="inlineStr"/>
       <c r="S777" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T777" t="inlineStr">
         <is>
@@ -53106,7 +53106,7 @@
       <c r="Q778" t="inlineStr"/>
       <c r="R778" t="inlineStr"/>
       <c r="S778" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T778" t="inlineStr">
         <is>
@@ -53167,16 +53167,16 @@
         <v>961</v>
       </c>
       <c r="P779" t="n">
-        <v>969</v>
+        <v>1217</v>
       </c>
       <c r="Q779" t="n">
-        <v>969</v>
+        <v>1217</v>
       </c>
       <c r="R779" t="n">
-        <v>13.84</v>
+        <v>17.39</v>
       </c>
       <c r="S779" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T779" t="inlineStr">
         <is>
@@ -53246,7 +53246,7 @@
         <v>25.9</v>
       </c>
       <c r="S780" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T780" t="inlineStr">
         <is>
@@ -53316,7 +53316,7 @@
         <v>36.4</v>
       </c>
       <c r="S781" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T781" t="inlineStr">
         <is>
@@ -53386,7 +53386,7 @@
         <v>41.5</v>
       </c>
       <c r="S782" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T782" t="inlineStr">
         <is>
@@ -53456,7 +53456,7 @@
         <v>19.42</v>
       </c>
       <c r="S783" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T783" t="inlineStr">
         <is>
@@ -53517,16 +53517,16 @@
         <v>4422</v>
       </c>
       <c r="P784" t="n">
-        <v>4516</v>
+        <v>5739</v>
       </c>
       <c r="Q784" t="n">
-        <v>5679</v>
+        <v>5739</v>
       </c>
       <c r="R784" t="n">
-        <v>78.88</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="S784" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T784" t="inlineStr">
         <is>
@@ -53587,7 +53587,7 @@
         <v>4507</v>
       </c>
       <c r="P785" t="n">
-        <v>4335</v>
+        <v>4506</v>
       </c>
       <c r="Q785" t="n">
         <v>4507</v>
@@ -53596,7 +53596,7 @@
         <v>64.39</v>
       </c>
       <c r="S785" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T785" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>4.04</v>
       </c>
       <c r="S786" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T786" t="inlineStr">
         <is>
@@ -53736,7 +53736,7 @@
         <v>57.14</v>
       </c>
       <c r="S787" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T787" t="inlineStr">
         <is>
@@ -53782,7 +53782,7 @@
       <c r="Q788" t="inlineStr"/>
       <c r="R788" t="inlineStr"/>
       <c r="S788" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T788" t="inlineStr">
         <is>
@@ -53828,7 +53828,7 @@
       <c r="Q789" t="inlineStr"/>
       <c r="R789" t="inlineStr"/>
       <c r="S789" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T789" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>3176</v>
       </c>
       <c r="P790" t="n">
-        <v>0</v>
+        <v>3083</v>
       </c>
       <c r="Q790" t="n">
         <v>3176</v>
@@ -53898,7 +53898,7 @@
         <v>52.93</v>
       </c>
       <c r="S790" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T790" t="inlineStr">
         <is>
@@ -53959,7 +53959,7 @@
         <v>7184</v>
       </c>
       <c r="P791" t="n">
-        <v>1068</v>
+        <v>6765</v>
       </c>
       <c r="Q791" t="n">
         <v>7184</v>
@@ -53968,7 +53968,7 @@
         <v>71.84</v>
       </c>
       <c r="S791" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T791" t="inlineStr">
         <is>
@@ -54029,7 +54029,7 @@
         <v>1241</v>
       </c>
       <c r="P792" t="n">
-        <v>0</v>
+        <v>325</v>
       </c>
       <c r="Q792" t="n">
         <v>1907</v>
@@ -54038,7 +54038,7 @@
         <v>15.89</v>
       </c>
       <c r="S792" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T792" t="inlineStr">
         <is>
@@ -54099,7 +54099,7 @@
         <v>1972</v>
       </c>
       <c r="P793" t="n">
-        <v>0</v>
+        <v>1990</v>
       </c>
       <c r="Q793" t="n">
         <v>2531</v>
@@ -54108,7 +54108,7 @@
         <v>28.12</v>
       </c>
       <c r="S793" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T793" t="inlineStr">
         <is>
@@ -54178,7 +54178,7 @@
         <v>35.26</v>
       </c>
       <c r="S794" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T794" t="inlineStr">
         <is>
@@ -54248,7 +54248,7 @@
         <v>54.36</v>
       </c>
       <c r="S795" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T795" t="inlineStr">
         <is>
@@ -54318,7 +54318,7 @@
         <v>40.57</v>
       </c>
       <c r="S796" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T796" t="inlineStr">
         <is>
@@ -54388,7 +54388,7 @@
         <v>6.54</v>
       </c>
       <c r="S797" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T797" t="inlineStr">
         <is>
@@ -54449,7 +54449,7 @@
         <v>7168</v>
       </c>
       <c r="P798" t="n">
-        <v>5432</v>
+        <v>5629</v>
       </c>
       <c r="Q798" t="n">
         <v>7168</v>
@@ -54458,7 +54458,7 @@
         <v>71.68000000000001</v>
       </c>
       <c r="S798" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T798" t="inlineStr">
         <is>
@@ -54528,7 +54528,7 @@
         <v>88.14</v>
       </c>
       <c r="S799" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T799" t="inlineStr">
         <is>
@@ -54598,7 +54598,7 @@
         <v>59.54</v>
       </c>
       <c r="S800" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T800" t="inlineStr">
         <is>
@@ -54668,7 +54668,7 @@
         <v>66.66</v>
       </c>
       <c r="S801" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T801" t="inlineStr">
         <is>
@@ -54738,7 +54738,7 @@
         <v>49.63</v>
       </c>
       <c r="S802" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T802" t="inlineStr">
         <is>
@@ -54808,7 +54808,7 @@
         <v>53.29</v>
       </c>
       <c r="S803" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T803" t="inlineStr">
         <is>
@@ -54869,7 +54869,7 @@
         <v>2103</v>
       </c>
       <c r="P804" t="n">
-        <v>2161</v>
+        <v>2167</v>
       </c>
       <c r="Q804" t="n">
         <v>2316</v>
@@ -54878,7 +54878,7 @@
         <v>49.28</v>
       </c>
       <c r="S804" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T804" t="inlineStr">
         <is>
@@ -54939,16 +54939,16 @@
         <v>2696</v>
       </c>
       <c r="P805" t="n">
-        <v>2860</v>
+        <v>3008</v>
       </c>
       <c r="Q805" t="n">
-        <v>2860</v>
+        <v>3008</v>
       </c>
       <c r="R805" t="n">
-        <v>71.5</v>
+        <v>75.2</v>
       </c>
       <c r="S805" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T805" t="inlineStr">
         <is>
@@ -55018,7 +55018,7 @@
         <v>32.5</v>
       </c>
       <c r="S806" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T806" t="inlineStr">
         <is>
@@ -55079,16 +55079,16 @@
         <v>1586</v>
       </c>
       <c r="P807" t="n">
-        <v>1602</v>
+        <v>1660</v>
       </c>
       <c r="Q807" t="n">
-        <v>1602</v>
+        <v>1660</v>
       </c>
       <c r="R807" t="n">
-        <v>80.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="S807" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T807" t="inlineStr">
         <is>
@@ -55149,16 +55149,16 @@
         <v>5289</v>
       </c>
       <c r="P808" t="n">
-        <v>5571</v>
+        <v>5579</v>
       </c>
       <c r="Q808" t="n">
-        <v>5571</v>
+        <v>5579</v>
       </c>
       <c r="R808" t="n">
-        <v>77.38</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="S808" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T808" t="inlineStr">
         <is>
@@ -55228,7 +55228,7 @@
         <v>52.48</v>
       </c>
       <c r="S809" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T809" t="inlineStr">
         <is>
@@ -55274,7 +55274,7 @@
       <c r="Q810" t="inlineStr"/>
       <c r="R810" t="inlineStr"/>
       <c r="S810" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T810" t="inlineStr">
         <is>
@@ -55335,7 +55335,7 @@
         <v>128</v>
       </c>
       <c r="P811" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="Q811" t="n">
         <v>4173</v>
@@ -55344,7 +55344,7 @@
         <v>59.61</v>
       </c>
       <c r="S811" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T811" t="inlineStr">
         <is>
@@ -55414,7 +55414,7 @@
         <v>45.92</v>
       </c>
       <c r="S812" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T812" t="inlineStr">
         <is>
@@ -55460,7 +55460,7 @@
       <c r="Q813" t="inlineStr"/>
       <c r="R813" t="inlineStr"/>
       <c r="S813" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T813" t="inlineStr">
         <is>
@@ -55530,7 +55530,7 @@
         <v>99.81999999999999</v>
       </c>
       <c r="S814" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T814" t="inlineStr">
         <is>
@@ -55576,7 +55576,7 @@
       <c r="Q815" t="inlineStr"/>
       <c r="R815" t="inlineStr"/>
       <c r="S815" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T815" t="inlineStr">
         <is>
@@ -55622,7 +55622,7 @@
       <c r="Q816" t="inlineStr"/>
       <c r="R816" t="inlineStr"/>
       <c r="S816" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T816" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
         <v>77.84999999999999</v>
       </c>
       <c r="S817" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T817" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
       <c r="Q818" t="inlineStr"/>
       <c r="R818" t="inlineStr"/>
       <c r="S818" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T818" t="inlineStr">
         <is>
@@ -55784,7 +55784,7 @@
       <c r="Q819" t="inlineStr"/>
       <c r="R819" t="inlineStr"/>
       <c r="S819" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T819" t="inlineStr">
         <is>
@@ -55830,7 +55830,7 @@
       <c r="Q820" t="inlineStr"/>
       <c r="R820" t="inlineStr"/>
       <c r="S820" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T820" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
       <c r="Q821" t="inlineStr"/>
       <c r="R821" t="inlineStr"/>
       <c r="S821" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T821" t="inlineStr">
         <is>
@@ -55946,7 +55946,7 @@
         <v>88.38</v>
       </c>
       <c r="S822" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T822" t="inlineStr">
         <is>
@@ -56016,7 +56016,7 @@
         <v>62.57</v>
       </c>
       <c r="S823" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T823" t="inlineStr">
         <is>
@@ -56086,7 +56086,7 @@
         <v>95.19</v>
       </c>
       <c r="S824" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T824" t="inlineStr">
         <is>
@@ -56156,7 +56156,7 @@
         <v>57.71</v>
       </c>
       <c r="S825" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T825" t="inlineStr">
         <is>
@@ -56217,7 +56217,7 @@
         <v>3235</v>
       </c>
       <c r="P826" t="n">
-        <v>3276</v>
+        <v>3384</v>
       </c>
       <c r="Q826" t="n">
         <v>3976</v>
@@ -56226,7 +56226,7 @@
         <v>55.45</v>
       </c>
       <c r="S826" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T826" t="inlineStr">
         <is>
@@ -56296,7 +56296,7 @@
         <v>88.20999999999999</v>
       </c>
       <c r="S827" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T827" t="inlineStr">
         <is>
@@ -56366,7 +56366,7 @@
         <v>50.06</v>
       </c>
       <c r="S828" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T828" t="inlineStr">
         <is>
@@ -56436,7 +56436,7 @@
         <v>65.05</v>
       </c>
       <c r="S829" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T829" t="inlineStr">
         <is>
@@ -56506,7 +56506,7 @@
         <v>88.55</v>
       </c>
       <c r="S830" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T830" t="inlineStr">
         <is>
@@ -56576,7 +56576,7 @@
         <v>55.58</v>
       </c>
       <c r="S831" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T831" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         <v>19.13</v>
       </c>
       <c r="S832" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T832" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>1111</v>
       </c>
       <c r="P833" t="n">
-        <v>1083</v>
+        <v>1093</v>
       </c>
       <c r="Q833" t="n">
         <v>1510</v>
@@ -56716,7 +56716,7 @@
         <v>12.58</v>
       </c>
       <c r="S833" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T833" t="inlineStr">
         <is>
@@ -56786,7 +56786,7 @@
         <v>23.98</v>
       </c>
       <c r="S834" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T834" t="inlineStr">
         <is>
@@ -56856,7 +56856,7 @@
         <v>69.83</v>
       </c>
       <c r="S835" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T835" t="inlineStr">
         <is>
@@ -56926,7 +56926,7 @@
         <v>36.59</v>
       </c>
       <c r="S836" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T836" t="inlineStr">
         <is>
@@ -56996,7 +56996,7 @@
         <v>70.2</v>
       </c>
       <c r="S837" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T837" t="inlineStr">
         <is>
@@ -57066,7 +57066,7 @@
         <v>86.86</v>
       </c>
       <c r="S838" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T838" t="inlineStr">
         <is>
@@ -57127,7 +57127,7 @@
         <v>75</v>
       </c>
       <c r="P839" t="n">
-        <v>-266</v>
+        <v>0</v>
       </c>
       <c r="Q839" t="n">
         <v>75</v>
@@ -57136,7 +57136,7 @@
         <v>0.75</v>
       </c>
       <c r="S839" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T839" t="inlineStr">
         <is>
@@ -57197,16 +57197,16 @@
         <v>4051</v>
       </c>
       <c r="P840" t="n">
-        <v>4762</v>
+        <v>5805</v>
       </c>
       <c r="Q840" t="n">
-        <v>4762</v>
+        <v>5805</v>
       </c>
       <c r="R840" t="n">
-        <v>47.62</v>
+        <v>58.05</v>
       </c>
       <c r="S840" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T840" t="inlineStr">
         <is>
@@ -57267,7 +57267,7 @@
         <v>4910</v>
       </c>
       <c r="P841" t="n">
-        <v>4526</v>
+        <v>4716</v>
       </c>
       <c r="Q841" t="n">
         <v>5470</v>
@@ -57276,7 +57276,7 @@
         <v>54.7</v>
       </c>
       <c r="S841" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T841" t="inlineStr">
         <is>
@@ -57337,16 +57337,16 @@
         <v>5954</v>
       </c>
       <c r="P842" t="n">
-        <v>6060</v>
+        <v>7005</v>
       </c>
       <c r="Q842" t="n">
-        <v>6060</v>
+        <v>7005</v>
       </c>
       <c r="R842" t="n">
-        <v>60.6</v>
+        <v>70.05</v>
       </c>
       <c r="S842" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T842" t="inlineStr">
         <is>
@@ -57416,7 +57416,7 @@
         <v>61.72</v>
       </c>
       <c r="S843" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T843" t="inlineStr">
         <is>
@@ -57486,7 +57486,7 @@
         <v>16.17</v>
       </c>
       <c r="S844" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T844" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>80.77</v>
       </c>
       <c r="S845" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T845" t="inlineStr">
         <is>
@@ -57617,7 +57617,7 @@
         <v>1355</v>
       </c>
       <c r="P846" t="n">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="Q846" t="n">
         <v>1355</v>
@@ -57626,7 +57626,7 @@
         <v>18.9</v>
       </c>
       <c r="S846" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T846" t="inlineStr">
         <is>
@@ -57687,16 +57687,16 @@
         <v>1486</v>
       </c>
       <c r="P847" t="n">
-        <v>1327</v>
+        <v>1782</v>
       </c>
       <c r="Q847" t="n">
-        <v>1486</v>
+        <v>1782</v>
       </c>
       <c r="R847" t="n">
-        <v>16.58</v>
+        <v>19.88</v>
       </c>
       <c r="S847" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T847" t="inlineStr">
         <is>
@@ -57757,16 +57757,16 @@
         <v>2169</v>
       </c>
       <c r="P848" t="n">
-        <v>2165</v>
+        <v>2171</v>
       </c>
       <c r="Q848" t="n">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="R848" t="n">
-        <v>25.21</v>
+        <v>25.23</v>
       </c>
       <c r="S848" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T848" t="inlineStr">
         <is>
@@ -57827,7 +57827,7 @@
         <v>4278</v>
       </c>
       <c r="P849" t="n">
-        <v>4051</v>
+        <v>4169</v>
       </c>
       <c r="Q849" t="n">
         <v>4278</v>
@@ -57836,7 +57836,7 @@
         <v>49.72</v>
       </c>
       <c r="S849" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T849" t="inlineStr">
         <is>
@@ -57906,7 +57906,7 @@
         <v>17.91</v>
       </c>
       <c r="S850" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T850" t="inlineStr">
         <is>
@@ -57976,7 +57976,7 @@
         <v>2.86</v>
       </c>
       <c r="S851" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T851" t="inlineStr">
         <is>
@@ -58046,7 +58046,7 @@
         <v>0.87</v>
       </c>
       <c r="S852" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T852" t="inlineStr">
         <is>
@@ -58116,7 +58116,7 @@
         <v>64.98</v>
       </c>
       <c r="S853" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T853" t="inlineStr">
         <is>
@@ -58186,7 +58186,7 @@
         <v>71.93000000000001</v>
       </c>
       <c r="S854" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T854" t="inlineStr">
         <is>
@@ -58256,7 +58256,7 @@
         <v>62.87</v>
       </c>
       <c r="S855" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T855" t="inlineStr">
         <is>
@@ -58326,7 +58326,7 @@
         <v>86.63</v>
       </c>
       <c r="S856" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T856" t="inlineStr">
         <is>
@@ -58396,7 +58396,7 @@
         <v>44.85</v>
       </c>
       <c r="S857" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T857" t="inlineStr">
         <is>
@@ -58466,7 +58466,7 @@
         <v>96.76000000000001</v>
       </c>
       <c r="S858" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T858" t="inlineStr">
         <is>
@@ -58512,7 +58512,7 @@
       <c r="Q859" t="inlineStr"/>
       <c r="R859" t="inlineStr"/>
       <c r="S859" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T859" t="inlineStr">
         <is>
@@ -58573,16 +58573,16 @@
         <v>10771</v>
       </c>
       <c r="P860" t="n">
-        <v>11480</v>
+        <v>12764</v>
       </c>
       <c r="Q860" t="n">
-        <v>11480</v>
+        <v>12764</v>
       </c>
       <c r="R860" t="n">
-        <v>57.4</v>
+        <v>63.82</v>
       </c>
       <c r="S860" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T860" t="inlineStr">
         <is>
@@ -58652,7 +58652,7 @@
         <v>0.02</v>
       </c>
       <c r="S861" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T861" t="inlineStr">
         <is>
@@ -58698,7 +58698,7 @@
       <c r="Q862" t="inlineStr"/>
       <c r="R862" t="inlineStr"/>
       <c r="S862" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T862" t="inlineStr">
         <is>
@@ -58744,7 +58744,7 @@
       <c r="Q863" t="inlineStr"/>
       <c r="R863" t="inlineStr"/>
       <c r="S863" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T863" t="inlineStr">
         <is>
@@ -58805,7 +58805,7 @@
         <v>6268</v>
       </c>
       <c r="P864" t="n">
-        <v>4715</v>
+        <v>4927</v>
       </c>
       <c r="Q864" t="n">
         <v>6268</v>
@@ -58814,7 +58814,7 @@
         <v>52.23</v>
       </c>
       <c r="S864" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T864" t="inlineStr">
         <is>
@@ -58875,16 +58875,16 @@
         <v>4559</v>
       </c>
       <c r="P865" t="n">
-        <v>6351</v>
+        <v>5966</v>
       </c>
       <c r="Q865" t="n">
-        <v>6351</v>
+        <v>5966</v>
       </c>
       <c r="R865" t="n">
-        <v>52.92</v>
+        <v>49.72</v>
       </c>
       <c r="S865" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T865" t="inlineStr">
         <is>
@@ -58954,7 +58954,7 @@
         <v>50.62</v>
       </c>
       <c r="S866" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T866" t="inlineStr">
         <is>
@@ -59024,7 +59024,7 @@
         <v>52.58</v>
       </c>
       <c r="S867" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T867" t="inlineStr">
         <is>
@@ -59094,7 +59094,7 @@
         <v>69.53</v>
       </c>
       <c r="S868" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T868" t="inlineStr">
         <is>
@@ -59164,7 +59164,7 @@
         <v>72.03</v>
       </c>
       <c r="S869" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T869" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>12918</v>
       </c>
       <c r="P870" t="n">
-        <v>10859</v>
+        <v>10949</v>
       </c>
       <c r="Q870" t="n">
         <v>12918</v>
@@ -59234,7 +59234,7 @@
         <v>129.18</v>
       </c>
       <c r="S870" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T870" t="inlineStr">
         <is>
@@ -59304,7 +59304,7 @@
         <v>106.2</v>
       </c>
       <c r="S871" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T871" t="inlineStr">
         <is>

--- a/Valores_maximos_P_meses.xlsx
+++ b/Valores_maximos_P_meses.xlsx
@@ -1165,13 +1165,13 @@
         <v>1036</v>
       </c>
       <c r="P11" t="n">
-        <v>1077</v>
+        <v>1366</v>
       </c>
       <c r="Q11" t="n">
-        <v>1077</v>
+        <v>1366</v>
       </c>
       <c r="R11" t="n">
-        <v>35.9</v>
+        <v>45.53</v>
       </c>
       <c r="S11" t="n">
         <v>8</v>
@@ -1375,13 +1375,13 @@
         <v>12165</v>
       </c>
       <c r="P14" t="n">
-        <v>13113</v>
+        <v>14796</v>
       </c>
       <c r="Q14" t="n">
-        <v>14496</v>
+        <v>14796</v>
       </c>
       <c r="R14" t="n">
-        <v>57.98</v>
+        <v>59.18</v>
       </c>
       <c r="S14" t="n">
         <v>8</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>299</v>
+        <v>1377</v>
       </c>
       <c r="Q15" t="n">
         <v>4925</v>
@@ -1515,7 +1515,7 @@
         <v>14925</v>
       </c>
       <c r="P16" t="n">
-        <v>14574</v>
+        <v>15662</v>
       </c>
       <c r="Q16" t="n">
         <v>28370</v>
@@ -2283,7 +2283,7 @@
         <v>12217</v>
       </c>
       <c r="P28" t="n">
-        <v>12017</v>
+        <v>12085</v>
       </c>
       <c r="Q28" t="n">
         <v>12217</v>
@@ -4937,7 +4937,7 @@
         <v>12752</v>
       </c>
       <c r="P69" t="n">
-        <v>11592</v>
+        <v>11260</v>
       </c>
       <c r="Q69" t="n">
         <v>12752</v>
@@ -5473,13 +5473,13 @@
         <v>19559</v>
       </c>
       <c r="P77" t="n">
-        <v>22207</v>
+        <v>24841</v>
       </c>
       <c r="Q77" t="n">
-        <v>22207</v>
+        <v>24841</v>
       </c>
       <c r="R77" t="n">
-        <v>49.35</v>
+        <v>55.2</v>
       </c>
       <c r="S77" t="n">
         <v>8</v>
@@ -6173,13 +6173,13 @@
         <v>3914</v>
       </c>
       <c r="P87" t="n">
-        <v>4095</v>
+        <v>3534</v>
       </c>
       <c r="Q87" t="n">
-        <v>4095</v>
+        <v>3914</v>
       </c>
       <c r="R87" t="n">
-        <v>54.6</v>
+        <v>52.19</v>
       </c>
       <c r="S87" t="n">
         <v>8</v>
@@ -7361,7 +7361,7 @@
         <v>27513</v>
       </c>
       <c r="P105" t="n">
-        <v>13866</v>
+        <v>12812</v>
       </c>
       <c r="Q105" t="n">
         <v>27513</v>
@@ -7431,7 +7431,7 @@
         <v>9607</v>
       </c>
       <c r="P106" t="n">
-        <v>3616</v>
+        <v>3269</v>
       </c>
       <c r="Q106" t="n">
         <v>9607</v>
@@ -7617,7 +7617,7 @@
         <v>14456</v>
       </c>
       <c r="P109" t="n">
-        <v>13449</v>
+        <v>14217</v>
       </c>
       <c r="Q109" t="n">
         <v>14508</v>
@@ -8221,13 +8221,13 @@
         <v>12244</v>
       </c>
       <c r="P119" t="n">
-        <v>14144</v>
+        <v>11188</v>
       </c>
       <c r="Q119" t="n">
-        <v>14144</v>
+        <v>14086</v>
       </c>
       <c r="R119" t="n">
-        <v>56.58</v>
+        <v>56.34</v>
       </c>
       <c r="S119" t="n">
         <v>8</v>
@@ -8617,13 +8617,13 @@
         <v>26571</v>
       </c>
       <c r="P125" t="n">
-        <v>27375</v>
+        <v>28173</v>
       </c>
       <c r="Q125" t="n">
-        <v>27375</v>
+        <v>28173</v>
       </c>
       <c r="R125" t="n">
-        <v>109.5</v>
+        <v>112.69</v>
       </c>
       <c r="S125" t="n">
         <v>8</v>
@@ -9293,7 +9293,7 @@
         <v>6372</v>
       </c>
       <c r="P135" t="n">
-        <v>1643</v>
+        <v>1801</v>
       </c>
       <c r="Q135" t="n">
         <v>9526</v>
@@ -9665,7 +9665,7 @@
         <v>4729</v>
       </c>
       <c r="P141" t="n">
-        <v>4977</v>
+        <v>5067</v>
       </c>
       <c r="Q141" t="n">
         <v>5336</v>
@@ -10335,7 +10335,7 @@
         <v>4276</v>
       </c>
       <c r="P151" t="n">
-        <v>4046</v>
+        <v>4144</v>
       </c>
       <c r="Q151" t="n">
         <v>4768</v>
@@ -11383,13 +11383,13 @@
         <v>11635</v>
       </c>
       <c r="P167" t="n">
-        <v>11893</v>
+        <v>11975</v>
       </c>
       <c r="Q167" t="n">
-        <v>11893</v>
+        <v>11975</v>
       </c>
       <c r="R167" t="n">
-        <v>47.57</v>
+        <v>47.9</v>
       </c>
       <c r="S167" t="n">
         <v>8</v>
@@ -11453,13 +11453,13 @@
         <v>2788</v>
       </c>
       <c r="P168" t="n">
-        <v>2764</v>
+        <v>3495</v>
       </c>
       <c r="Q168" t="n">
-        <v>2788</v>
+        <v>3495</v>
       </c>
       <c r="R168" t="n">
-        <v>29.74</v>
+        <v>37.28</v>
       </c>
       <c r="S168" t="n">
         <v>8</v>
@@ -11871,7 +11871,7 @@
         <v>6068</v>
       </c>
       <c r="P175" t="n">
-        <v>3247</v>
+        <v>2859</v>
       </c>
       <c r="Q175" t="n">
         <v>6068</v>
@@ -12011,7 +12011,7 @@
         <v>19578</v>
       </c>
       <c r="P177" t="n">
-        <v>15584</v>
+        <v>16659</v>
       </c>
       <c r="Q177" t="n">
         <v>19578</v>
@@ -12641,7 +12641,7 @@
         <v>19286</v>
       </c>
       <c r="P186" t="n">
-        <v>16782</v>
+        <v>17525</v>
       </c>
       <c r="Q186" t="n">
         <v>23208</v>
@@ -12781,7 +12781,7 @@
         <v>26734</v>
       </c>
       <c r="P188" t="n">
-        <v>24093</v>
+        <v>27216</v>
       </c>
       <c r="Q188" t="n">
         <v>27359</v>
@@ -14387,7 +14387,7 @@
         <v>12128</v>
       </c>
       <c r="P213" t="n">
-        <v>11874</v>
+        <v>11883</v>
       </c>
       <c r="Q213" t="n">
         <v>12128</v>
@@ -14853,7 +14853,7 @@
         <v>2047</v>
       </c>
       <c r="P220" t="n">
-        <v>1876</v>
+        <v>1927</v>
       </c>
       <c r="Q220" t="n">
         <v>2306</v>
@@ -15249,7 +15249,7 @@
         <v>27054</v>
       </c>
       <c r="P226" t="n">
-        <v>23057</v>
+        <v>23717</v>
       </c>
       <c r="Q226" t="n">
         <v>27054</v>
@@ -16345,7 +16345,7 @@
         <v>7078</v>
       </c>
       <c r="P242" t="n">
-        <v>6784</v>
+        <v>6131</v>
       </c>
       <c r="Q242" t="n">
         <v>7078</v>
@@ -16415,7 +16415,7 @@
         <v>7330</v>
       </c>
       <c r="P243" t="n">
-        <v>6332</v>
+        <v>5759</v>
       </c>
       <c r="Q243" t="n">
         <v>7330</v>
@@ -16485,7 +16485,7 @@
         <v>3733</v>
       </c>
       <c r="P244" t="n">
-        <v>3226</v>
+        <v>2660</v>
       </c>
       <c r="Q244" t="n">
         <v>3733</v>
@@ -16555,7 +16555,7 @@
         <v>3899</v>
       </c>
       <c r="P245" t="n">
-        <v>3379</v>
+        <v>2946</v>
       </c>
       <c r="Q245" t="n">
         <v>3899</v>
@@ -16695,13 +16695,13 @@
         <v>4579</v>
       </c>
       <c r="P247" t="n">
-        <v>5033</v>
+        <v>4327</v>
       </c>
       <c r="Q247" t="n">
-        <v>5033</v>
+        <v>4579</v>
       </c>
       <c r="R247" t="n">
-        <v>50.13</v>
+        <v>45.61</v>
       </c>
       <c r="S247" t="n">
         <v>8</v>
@@ -17045,13 +17045,13 @@
         <v>2187</v>
       </c>
       <c r="P252" t="n">
-        <v>2445</v>
+        <v>2499</v>
       </c>
       <c r="Q252" t="n">
-        <v>2445</v>
+        <v>2499</v>
       </c>
       <c r="R252" t="n">
-        <v>51.15</v>
+        <v>52.28</v>
       </c>
       <c r="S252" t="n">
         <v>8</v>
@@ -17185,7 +17185,7 @@
         <v>1797</v>
       </c>
       <c r="P254" t="n">
-        <v>1215</v>
+        <v>1051</v>
       </c>
       <c r="Q254" t="n">
         <v>1930</v>
@@ -17465,7 +17465,7 @@
         <v>5648</v>
       </c>
       <c r="P258" t="n">
-        <v>5424</v>
+        <v>5437</v>
       </c>
       <c r="Q258" t="n">
         <v>5648</v>
@@ -17675,7 +17675,7 @@
         <v>2164</v>
       </c>
       <c r="P261" t="n">
-        <v>1838</v>
+        <v>1993</v>
       </c>
       <c r="Q261" t="n">
         <v>3044</v>
@@ -18025,7 +18025,7 @@
         <v>5986</v>
       </c>
       <c r="P266" t="n">
-        <v>5695</v>
+        <v>6519</v>
       </c>
       <c r="Q266" t="n">
         <v>7429</v>
@@ -18585,7 +18585,7 @@
         <v>4586</v>
       </c>
       <c r="P274" t="n">
-        <v>5097</v>
+        <v>4991</v>
       </c>
       <c r="Q274" t="n">
         <v>8427</v>
@@ -18981,7 +18981,7 @@
         <v>84</v>
       </c>
       <c r="P280" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="Q280" t="n">
         <v>807</v>
@@ -19121,13 +19121,13 @@
         <v>5453</v>
       </c>
       <c r="P282" t="n">
-        <v>5710</v>
+        <v>5717</v>
       </c>
       <c r="Q282" t="n">
-        <v>5710</v>
+        <v>5717</v>
       </c>
       <c r="R282" t="n">
-        <v>79.63</v>
+        <v>79.73</v>
       </c>
       <c r="S282" t="n">
         <v>8</v>
@@ -19471,7 +19471,7 @@
         <v>3215</v>
       </c>
       <c r="P287" t="n">
-        <v>3051</v>
+        <v>3080</v>
       </c>
       <c r="Q287" t="n">
         <v>3215</v>
@@ -19703,13 +19703,13 @@
         <v>664</v>
       </c>
       <c r="P291" t="n">
-        <v>684</v>
+        <v>734</v>
       </c>
       <c r="Q291" t="n">
-        <v>684</v>
+        <v>734</v>
       </c>
       <c r="R291" t="n">
-        <v>28.62</v>
+        <v>30.71</v>
       </c>
       <c r="S291" t="n">
         <v>8</v>
@@ -19913,7 +19913,7 @@
         <v>250</v>
       </c>
       <c r="P294" t="n">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="Q294" t="n">
         <v>874</v>
@@ -21033,13 +21033,13 @@
         <v>3754</v>
       </c>
       <c r="P310" t="n">
-        <v>4124</v>
+        <v>3696</v>
       </c>
       <c r="Q310" t="n">
-        <v>4124</v>
+        <v>3754</v>
       </c>
       <c r="R310" t="n">
-        <v>41.24</v>
+        <v>37.54</v>
       </c>
       <c r="S310" t="n">
         <v>8</v>
@@ -22475,13 +22475,13 @@
         <v>4717</v>
       </c>
       <c r="P333" t="n">
-        <v>4813</v>
+        <v>5115</v>
       </c>
       <c r="Q333" t="n">
-        <v>4879</v>
+        <v>5115</v>
       </c>
       <c r="R333" t="n">
-        <v>48.79</v>
+        <v>51.15</v>
       </c>
       <c r="S333" t="n">
         <v>8</v>
@@ -22825,7 +22825,7 @@
         <v>4083</v>
       </c>
       <c r="P338" t="n">
-        <v>4005</v>
+        <v>4013</v>
       </c>
       <c r="Q338" t="n">
         <v>4083</v>
@@ -23523,13 +23523,13 @@
         <v>6030</v>
       </c>
       <c r="P349" t="n">
-        <v>9101</v>
+        <v>8182</v>
       </c>
       <c r="Q349" t="n">
-        <v>9101</v>
+        <v>8182</v>
       </c>
       <c r="R349" t="n">
-        <v>90.66</v>
+        <v>81.5</v>
       </c>
       <c r="S349" t="n">
         <v>8</v>
@@ -23663,7 +23663,7 @@
         <v>2641</v>
       </c>
       <c r="P351" t="n">
-        <v>3225</v>
+        <v>3164</v>
       </c>
       <c r="Q351" t="n">
         <v>4698</v>
@@ -25273,13 +25273,13 @@
         <v>3531</v>
       </c>
       <c r="P374" t="n">
-        <v>5346</v>
+        <v>5191</v>
       </c>
       <c r="Q374" t="n">
-        <v>5346</v>
+        <v>5191</v>
       </c>
       <c r="R374" t="n">
-        <v>53.46</v>
+        <v>51.91</v>
       </c>
       <c r="S374" t="n">
         <v>8</v>
@@ -25483,13 +25483,13 @@
         <v>6423</v>
       </c>
       <c r="P377" t="n">
-        <v>4894</v>
+        <v>6448</v>
       </c>
       <c r="Q377" t="n">
-        <v>6423</v>
+        <v>6448</v>
       </c>
       <c r="R377" t="n">
-        <v>53.52</v>
+        <v>53.73</v>
       </c>
       <c r="S377" t="n">
         <v>8</v>
@@ -25553,13 +25553,13 @@
         <v>6570</v>
       </c>
       <c r="P378" t="n">
-        <v>7077</v>
+        <v>7173</v>
       </c>
       <c r="Q378" t="n">
-        <v>7077</v>
+        <v>7173</v>
       </c>
       <c r="R378" t="n">
-        <v>58.98</v>
+        <v>59.78</v>
       </c>
       <c r="S378" t="n">
         <v>8</v>
@@ -26253,13 +26253,13 @@
         <v>2537</v>
       </c>
       <c r="P388" t="n">
-        <v>2486</v>
+        <v>2905</v>
       </c>
       <c r="Q388" t="n">
-        <v>2537</v>
+        <v>2905</v>
       </c>
       <c r="R388" t="n">
-        <v>42.46</v>
+        <v>48.61</v>
       </c>
       <c r="S388" t="n">
         <v>8</v>
@@ -26323,7 +26323,7 @@
         <v>7403</v>
       </c>
       <c r="P389" t="n">
-        <v>6105</v>
+        <v>5725</v>
       </c>
       <c r="Q389" t="n">
         <v>7403</v>
@@ -26463,13 +26463,13 @@
         <v>172</v>
       </c>
       <c r="P391" t="n">
-        <v>1133</v>
+        <v>1020</v>
       </c>
       <c r="Q391" t="n">
-        <v>1133</v>
+        <v>1020</v>
       </c>
       <c r="R391" t="n">
-        <v>11.33</v>
+        <v>10.2</v>
       </c>
       <c r="S391" t="n">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>5981</v>
       </c>
       <c r="P393" t="n">
-        <v>5776</v>
+        <v>5627</v>
       </c>
       <c r="Q393" t="n">
         <v>5981</v>
@@ -27699,13 +27699,13 @@
         <v>3223</v>
       </c>
       <c r="P409" t="n">
-        <v>3299</v>
+        <v>3500</v>
       </c>
       <c r="Q409" t="n">
-        <v>3299</v>
+        <v>3500</v>
       </c>
       <c r="R409" t="n">
-        <v>32.99</v>
+        <v>35</v>
       </c>
       <c r="S409" t="n">
         <v>8</v>
@@ -28119,7 +28119,7 @@
         <v>3854</v>
       </c>
       <c r="P415" t="n">
-        <v>3609</v>
+        <v>3812</v>
       </c>
       <c r="Q415" t="n">
         <v>3854</v>
@@ -30359,13 +30359,13 @@
         <v>4704</v>
       </c>
       <c r="P447" t="n">
-        <v>5077</v>
+        <v>5708</v>
       </c>
       <c r="Q447" t="n">
-        <v>5077</v>
+        <v>5708</v>
       </c>
       <c r="R447" t="n">
-        <v>50.57</v>
+        <v>56.86</v>
       </c>
       <c r="S447" t="n">
         <v>8</v>
@@ -30499,13 +30499,13 @@
         <v>4114</v>
       </c>
       <c r="P449" t="n">
-        <v>5598</v>
+        <v>6442</v>
       </c>
       <c r="Q449" t="n">
-        <v>5598</v>
+        <v>6442</v>
       </c>
       <c r="R449" t="n">
-        <v>55.98</v>
+        <v>64.42</v>
       </c>
       <c r="S449" t="n">
         <v>8</v>
@@ -30849,13 +30849,13 @@
         <v>6391</v>
       </c>
       <c r="P454" t="n">
-        <v>7740</v>
+        <v>6249</v>
       </c>
       <c r="Q454" t="n">
-        <v>7740</v>
+        <v>6391</v>
       </c>
       <c r="R454" t="n">
-        <v>77.40000000000001</v>
+        <v>63.91</v>
       </c>
       <c r="S454" t="n">
         <v>8</v>
@@ -33229,7 +33229,7 @@
         <v>905</v>
       </c>
       <c r="P488" t="n">
-        <v>930</v>
+        <v>957</v>
       </c>
       <c r="Q488" t="n">
         <v>958</v>
@@ -33789,13 +33789,13 @@
         <v>5058</v>
       </c>
       <c r="P496" t="n">
-        <v>5311</v>
+        <v>6431</v>
       </c>
       <c r="Q496" t="n">
-        <v>5311</v>
+        <v>6431</v>
       </c>
       <c r="R496" t="n">
-        <v>52.9</v>
+        <v>64.06</v>
       </c>
       <c r="S496" t="n">
         <v>8</v>
@@ -33929,13 +33929,13 @@
         <v>4963</v>
       </c>
       <c r="P498" t="n">
-        <v>5443</v>
+        <v>6149</v>
       </c>
       <c r="Q498" t="n">
-        <v>5443</v>
+        <v>6149</v>
       </c>
       <c r="R498" t="n">
-        <v>41.87</v>
+        <v>47.3</v>
       </c>
       <c r="S498" t="n">
         <v>8</v>
@@ -34629,7 +34629,7 @@
         <v>7115</v>
       </c>
       <c r="P508" t="n">
-        <v>7358</v>
+        <v>7535</v>
       </c>
       <c r="Q508" t="n">
         <v>8169</v>
@@ -35049,7 +35049,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q514" t="n">
         <v>1</v>
@@ -35889,13 +35889,13 @@
         <v>4832</v>
       </c>
       <c r="P526" t="n">
-        <v>5604</v>
+        <v>5653</v>
       </c>
       <c r="Q526" t="n">
-        <v>5604</v>
+        <v>5653</v>
       </c>
       <c r="R526" t="n">
-        <v>62.27</v>
+        <v>62.81</v>
       </c>
       <c r="S526" t="n">
         <v>8</v>
@@ -36379,13 +36379,13 @@
         <v>665</v>
       </c>
       <c r="P533" t="n">
-        <v>919</v>
+        <v>876</v>
       </c>
       <c r="Q533" t="n">
-        <v>919</v>
+        <v>876</v>
       </c>
       <c r="R533" t="n">
-        <v>45.95</v>
+        <v>43.8</v>
       </c>
       <c r="S533" t="n">
         <v>8</v>
@@ -36495,7 +36495,7 @@
         <v>3366</v>
       </c>
       <c r="P535" t="n">
-        <v>3339</v>
+        <v>3485</v>
       </c>
       <c r="Q535" t="n">
         <v>4223</v>
@@ -36821,13 +36821,13 @@
         <v>4608</v>
       </c>
       <c r="P540" t="n">
-        <v>4605</v>
+        <v>4761</v>
       </c>
       <c r="Q540" t="n">
-        <v>4753</v>
+        <v>4761</v>
       </c>
       <c r="R540" t="n">
-        <v>39.61</v>
+        <v>39.68</v>
       </c>
       <c r="S540" t="n">
         <v>8</v>
@@ -36937,7 +36937,7 @@
         <v>435</v>
       </c>
       <c r="P542" t="n">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="Q542" t="n">
         <v>3755</v>
@@ -37007,7 +37007,7 @@
         <v>2804</v>
       </c>
       <c r="P543" t="n">
-        <v>824</v>
+        <v>711</v>
       </c>
       <c r="Q543" t="n">
         <v>5012</v>
@@ -37077,7 +37077,7 @@
         <v>5417</v>
       </c>
       <c r="P544" t="n">
-        <v>2663</v>
+        <v>2415</v>
       </c>
       <c r="Q544" t="n">
         <v>6510</v>
@@ -37147,7 +37147,7 @@
         <v>6861</v>
       </c>
       <c r="P545" t="n">
-        <v>2427</v>
+        <v>2154</v>
       </c>
       <c r="Q545" t="n">
         <v>6861</v>
@@ -37427,7 +37427,7 @@
         <v>3810</v>
       </c>
       <c r="P549" t="n">
-        <v>791</v>
+        <v>610</v>
       </c>
       <c r="Q549" t="n">
         <v>3847</v>
@@ -37683,13 +37683,13 @@
         <v>2857</v>
       </c>
       <c r="P553" t="n">
-        <v>2840</v>
+        <v>3039</v>
       </c>
       <c r="Q553" t="n">
-        <v>2857</v>
+        <v>3039</v>
       </c>
       <c r="R553" t="n">
-        <v>57.14</v>
+        <v>60.78</v>
       </c>
       <c r="S553" t="n">
         <v>8</v>
@@ -37753,7 +37753,7 @@
         <v>529</v>
       </c>
       <c r="P554" t="n">
-        <v>435</v>
+        <v>454</v>
       </c>
       <c r="Q554" t="n">
         <v>603</v>
@@ -37915,13 +37915,13 @@
         <v>1904</v>
       </c>
       <c r="P557" t="n">
-        <v>2338</v>
+        <v>3456</v>
       </c>
       <c r="Q557" t="n">
-        <v>2338</v>
+        <v>3456</v>
       </c>
       <c r="R557" t="n">
-        <v>11.69</v>
+        <v>17.28</v>
       </c>
       <c r="S557" t="n">
         <v>8</v>
@@ -38381,13 +38381,13 @@
         <v>3465</v>
       </c>
       <c r="P564" t="n">
-        <v>3466</v>
+        <v>3651</v>
       </c>
       <c r="Q564" t="n">
-        <v>3466</v>
+        <v>3651</v>
       </c>
       <c r="R564" t="n">
-        <v>57.77</v>
+        <v>60.85</v>
       </c>
       <c r="S564" t="n">
         <v>8</v>
@@ -38777,7 +38777,7 @@
         <v>3766</v>
       </c>
       <c r="P570" t="n">
-        <v>2623</v>
+        <v>3008</v>
       </c>
       <c r="Q570" t="n">
         <v>3836</v>
@@ -38847,13 +38847,13 @@
         <v>5101</v>
       </c>
       <c r="P571" t="n">
-        <v>6088</v>
+        <v>6670</v>
       </c>
       <c r="Q571" t="n">
-        <v>6088</v>
+        <v>6670</v>
       </c>
       <c r="R571" t="n">
-        <v>86.97</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="S571" t="n">
         <v>8</v>
@@ -39943,13 +39943,13 @@
         <v>2423</v>
       </c>
       <c r="P587" t="n">
-        <v>1970</v>
+        <v>3744</v>
       </c>
       <c r="Q587" t="n">
-        <v>3670</v>
+        <v>3744</v>
       </c>
       <c r="R587" t="n">
-        <v>36.7</v>
+        <v>37.44</v>
       </c>
       <c r="S587" t="n">
         <v>8</v>
@@ -40293,7 +40293,7 @@
         <v>398</v>
       </c>
       <c r="P592" t="n">
-        <v>349</v>
+        <v>167</v>
       </c>
       <c r="Q592" t="n">
         <v>398</v>
@@ -40853,13 +40853,13 @@
         <v>5124</v>
       </c>
       <c r="P600" t="n">
-        <v>7646</v>
+        <v>7268</v>
       </c>
       <c r="Q600" t="n">
-        <v>7646</v>
+        <v>7268</v>
       </c>
       <c r="R600" t="n">
-        <v>76.45999999999999</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="S600" t="n">
         <v>8</v>
@@ -41133,13 +41133,13 @@
         <v>6402</v>
       </c>
       <c r="P604" t="n">
-        <v>8600</v>
+        <v>7580</v>
       </c>
       <c r="Q604" t="n">
-        <v>8600</v>
+        <v>7580</v>
       </c>
       <c r="R604" t="n">
-        <v>66.15000000000001</v>
+        <v>58.31</v>
       </c>
       <c r="S604" t="n">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>3274</v>
       </c>
       <c r="P610" t="n">
-        <v>2933</v>
+        <v>2532</v>
       </c>
       <c r="Q610" t="n">
         <v>3274</v>
@@ -42485,7 +42485,7 @@
         <v>4097</v>
       </c>
       <c r="P624" t="n">
-        <v>3993</v>
+        <v>3527</v>
       </c>
       <c r="Q624" t="n">
         <v>5528</v>
@@ -43185,13 +43185,13 @@
         <v>447</v>
       </c>
       <c r="P634" t="n">
-        <v>334</v>
+        <v>687</v>
       </c>
       <c r="Q634" t="n">
-        <v>641</v>
+        <v>687</v>
       </c>
       <c r="R634" t="n">
-        <v>10.68</v>
+        <v>11.45</v>
       </c>
       <c r="S634" t="n">
         <v>8</v>
@@ -43535,13 +43535,13 @@
         <v>7734</v>
       </c>
       <c r="P639" t="n">
-        <v>7593</v>
+        <v>8908</v>
       </c>
       <c r="Q639" t="n">
-        <v>8193</v>
+        <v>8908</v>
       </c>
       <c r="R639" t="n">
-        <v>85.69</v>
+        <v>93.17</v>
       </c>
       <c r="S639" t="n">
         <v>8</v>
@@ -44305,13 +44305,13 @@
         <v>2379</v>
       </c>
       <c r="P650" t="n">
-        <v>2361</v>
+        <v>2390</v>
       </c>
       <c r="Q650" t="n">
-        <v>2379</v>
+        <v>2390</v>
       </c>
       <c r="R650" t="n">
-        <v>29.74</v>
+        <v>29.88</v>
       </c>
       <c r="S650" t="n">
         <v>8</v>
@@ -44515,7 +44515,7 @@
         <v>2204</v>
       </c>
       <c r="P653" t="n">
-        <v>2140</v>
+        <v>2164</v>
       </c>
       <c r="Q653" t="n">
         <v>2204</v>
@@ -45821,7 +45821,7 @@
         <v>4216</v>
       </c>
       <c r="P672" t="n">
-        <v>2632</v>
+        <v>3585</v>
       </c>
       <c r="Q672" t="n">
         <v>5639</v>
@@ -46031,13 +46031,13 @@
         <v>3710</v>
       </c>
       <c r="P675" t="n">
-        <v>3893</v>
+        <v>3955</v>
       </c>
       <c r="Q675" t="n">
-        <v>3893</v>
+        <v>3955</v>
       </c>
       <c r="R675" t="n">
-        <v>77.86</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="S675" t="n">
         <v>8</v>
@@ -46521,7 +46521,7 @@
         <v>4565</v>
       </c>
       <c r="P682" t="n">
-        <v>3615</v>
+        <v>4536</v>
       </c>
       <c r="Q682" t="n">
         <v>5228</v>
@@ -46893,13 +46893,13 @@
         <v>372</v>
       </c>
       <c r="P688" t="n">
-        <v>385</v>
+        <v>687</v>
       </c>
       <c r="Q688" t="n">
-        <v>385</v>
+        <v>687</v>
       </c>
       <c r="R688" t="n">
-        <v>8.949999999999999</v>
+        <v>15.98</v>
       </c>
       <c r="S688" t="n">
         <v>8</v>
@@ -47873,13 +47873,13 @@
         <v>2843</v>
       </c>
       <c r="P702" t="n">
-        <v>2632</v>
+        <v>2954</v>
       </c>
       <c r="Q702" t="n">
-        <v>2843</v>
+        <v>2954</v>
       </c>
       <c r="R702" t="n">
-        <v>40.61</v>
+        <v>42.2</v>
       </c>
       <c r="S702" t="n">
         <v>8</v>
@@ -48713,13 +48713,13 @@
         <v>9341</v>
       </c>
       <c r="P714" t="n">
-        <v>7740</v>
+        <v>9639</v>
       </c>
       <c r="Q714" t="n">
-        <v>9341</v>
+        <v>9639</v>
       </c>
       <c r="R714" t="n">
-        <v>87.3</v>
+        <v>90.08</v>
       </c>
       <c r="S714" t="n">
         <v>8</v>
@@ -48923,7 +48923,7 @@
         <v>1355</v>
       </c>
       <c r="P717" t="n">
-        <v>1276</v>
+        <v>1334</v>
       </c>
       <c r="Q717" t="n">
         <v>1486</v>
@@ -49273,7 +49273,7 @@
         <v>4643</v>
       </c>
       <c r="P722" t="n">
-        <v>4352</v>
+        <v>4422</v>
       </c>
       <c r="Q722" t="n">
         <v>4643</v>
@@ -49903,7 +49903,7 @@
         <v>6867</v>
       </c>
       <c r="P731" t="n">
-        <v>6286</v>
+        <v>6370</v>
       </c>
       <c r="Q731" t="n">
         <v>7742</v>
@@ -50603,13 +50603,13 @@
         <v>1267</v>
       </c>
       <c r="P741" t="n">
-        <v>1400</v>
+        <v>1746</v>
       </c>
       <c r="Q741" t="n">
-        <v>1610</v>
+        <v>1746</v>
       </c>
       <c r="R741" t="n">
-        <v>13.42</v>
+        <v>14.55</v>
       </c>
       <c r="S741" t="n">
         <v>8</v>
@@ -50673,7 +50673,7 @@
         <v>6356</v>
       </c>
       <c r="P742" t="n">
-        <v>7070</v>
+        <v>6822</v>
       </c>
       <c r="Q742" t="n">
         <v>11079</v>
@@ -50813,7 +50813,7 @@
         <v>3932</v>
       </c>
       <c r="P744" t="n">
-        <v>4043</v>
+        <v>4054</v>
       </c>
       <c r="Q744" t="n">
         <v>5457</v>
@@ -50883,7 +50883,7 @@
         <v>7046</v>
       </c>
       <c r="P745" t="n">
-        <v>6620</v>
+        <v>6912</v>
       </c>
       <c r="Q745" t="n">
         <v>7787</v>
@@ -50953,7 +50953,7 @@
         <v>2365</v>
       </c>
       <c r="P746" t="n">
-        <v>2986</v>
+        <v>2753</v>
       </c>
       <c r="Q746" t="n">
         <v>4293</v>
@@ -51023,7 +51023,7 @@
         <v>4170</v>
       </c>
       <c r="P747" t="n">
-        <v>3820</v>
+        <v>4002</v>
       </c>
       <c r="Q747" t="n">
         <v>5747</v>
@@ -51093,7 +51093,7 @@
         <v>5858</v>
       </c>
       <c r="P748" t="n">
-        <v>4788</v>
+        <v>4821</v>
       </c>
       <c r="Q748" t="n">
         <v>5858</v>
@@ -51163,7 +51163,7 @@
         <v>5114</v>
       </c>
       <c r="P749" t="n">
-        <v>2143</v>
+        <v>1917</v>
       </c>
       <c r="Q749" t="n">
         <v>5114</v>
@@ -51233,7 +51233,7 @@
         <v>1154</v>
       </c>
       <c r="P750" t="n">
-        <v>1089</v>
+        <v>910</v>
       </c>
       <c r="Q750" t="n">
         <v>1431</v>
@@ -54029,7 +54029,7 @@
         <v>1241</v>
       </c>
       <c r="P792" t="n">
-        <v>325</v>
+        <v>1699</v>
       </c>
       <c r="Q792" t="n">
         <v>1907</v>
@@ -54309,13 +54309,13 @@
         <v>3990</v>
       </c>
       <c r="P796" t="n">
-        <v>4057</v>
+        <v>4082</v>
       </c>
       <c r="Q796" t="n">
-        <v>4057</v>
+        <v>4082</v>
       </c>
       <c r="R796" t="n">
-        <v>40.57</v>
+        <v>40.82</v>
       </c>
       <c r="S796" t="n">
         <v>8</v>
@@ -55335,7 +55335,7 @@
         <v>128</v>
       </c>
       <c r="P811" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="Q811" t="n">
         <v>4173</v>
@@ -56077,13 +56077,13 @@
         <v>5628</v>
       </c>
       <c r="P824" t="n">
-        <v>5802</v>
+        <v>5870</v>
       </c>
       <c r="Q824" t="n">
-        <v>5802</v>
+        <v>5870</v>
       </c>
       <c r="R824" t="n">
-        <v>95.19</v>
+        <v>96.31</v>
       </c>
       <c r="S824" t="n">
         <v>8</v>
@@ -56287,13 +56287,13 @@
         <v>7717</v>
       </c>
       <c r="P827" t="n">
-        <v>7874</v>
+        <v>8001</v>
       </c>
       <c r="Q827" t="n">
-        <v>7907</v>
+        <v>8001</v>
       </c>
       <c r="R827" t="n">
-        <v>88.20999999999999</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="S827" t="n">
         <v>8</v>
@@ -56427,7 +56427,7 @@
         <v>7806</v>
       </c>
       <c r="P829" t="n">
-        <v>6618</v>
+        <v>7480</v>
       </c>
       <c r="Q829" t="n">
         <v>7806</v>
@@ -56497,7 +56497,7 @@
         <v>258</v>
       </c>
       <c r="P830" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q830" t="n">
         <v>3542</v>
@@ -56567,13 +56567,13 @@
         <v>7814</v>
       </c>
       <c r="P831" t="n">
-        <v>7948</v>
+        <v>8116</v>
       </c>
       <c r="Q831" t="n">
-        <v>7948</v>
+        <v>8116</v>
       </c>
       <c r="R831" t="n">
-        <v>55.58</v>
+        <v>56.76</v>
       </c>
       <c r="S831" t="n">
         <v>8</v>
@@ -56637,13 +56637,13 @@
         <v>1722</v>
       </c>
       <c r="P832" t="n">
-        <v>1642</v>
+        <v>1891</v>
       </c>
       <c r="Q832" t="n">
-        <v>1722</v>
+        <v>1891</v>
       </c>
       <c r="R832" t="n">
-        <v>19.13</v>
+        <v>21.01</v>
       </c>
       <c r="S832" t="n">
         <v>8</v>
@@ -58317,7 +58317,7 @@
         <v>10395</v>
       </c>
       <c r="P856" t="n">
-        <v>9232</v>
+        <v>9640</v>
       </c>
       <c r="Q856" t="n">
         <v>10395</v>

--- a/Valores_maximos_P_meses.xlsx
+++ b/Valores_maximos_P_meses.xlsx
@@ -653,13 +653,13 @@
         <v>2102</v>
       </c>
       <c r="P3" t="n">
-        <v>2107</v>
+        <v>2131</v>
       </c>
       <c r="Q3" t="n">
-        <v>2107</v>
+        <v>2131</v>
       </c>
       <c r="R3" t="n">
-        <v>33.71</v>
+        <v>34.1</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
@@ -1165,13 +1165,13 @@
         <v>1036</v>
       </c>
       <c r="P11" t="n">
-        <v>1366</v>
+        <v>1539</v>
       </c>
       <c r="Q11" t="n">
-        <v>1366</v>
+        <v>1539</v>
       </c>
       <c r="R11" t="n">
-        <v>45.53</v>
+        <v>51.3</v>
       </c>
       <c r="S11" t="n">
         <v>8</v>
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1377</v>
+        <v>1520</v>
       </c>
       <c r="Q15" t="n">
         <v>4925</v>
@@ -1515,7 +1515,7 @@
         <v>14925</v>
       </c>
       <c r="P16" t="n">
-        <v>15662</v>
+        <v>15851</v>
       </c>
       <c r="Q16" t="n">
         <v>28370</v>
@@ -2027,13 +2027,13 @@
         <v>9466</v>
       </c>
       <c r="P24" t="n">
-        <v>9373</v>
+        <v>9471</v>
       </c>
       <c r="Q24" t="n">
-        <v>9466</v>
+        <v>9471</v>
       </c>
       <c r="R24" t="n">
-        <v>75.73</v>
+        <v>75.77</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -2701,13 +2701,13 @@
         <v>2175</v>
       </c>
       <c r="P35" t="n">
-        <v>2251</v>
+        <v>2265</v>
       </c>
       <c r="Q35" t="n">
-        <v>2251</v>
+        <v>2265</v>
       </c>
       <c r="R35" t="n">
-        <v>75.03</v>
+        <v>75.5</v>
       </c>
       <c r="S35" t="n">
         <v>8</v>
@@ -3377,13 +3377,13 @@
         <v>3477</v>
       </c>
       <c r="P45" t="n">
-        <v>4333</v>
+        <v>4079</v>
       </c>
       <c r="Q45" t="n">
-        <v>4333</v>
+        <v>4079</v>
       </c>
       <c r="R45" t="n">
-        <v>28.89</v>
+        <v>27.19</v>
       </c>
       <c r="S45" t="n">
         <v>8</v>
@@ -4937,7 +4937,7 @@
         <v>12752</v>
       </c>
       <c r="P69" t="n">
-        <v>11260</v>
+        <v>11158</v>
       </c>
       <c r="Q69" t="n">
         <v>12752</v>
@@ -5007,13 +5007,13 @@
         <v>19630</v>
       </c>
       <c r="P70" t="n">
-        <v>23482</v>
+        <v>24431</v>
       </c>
       <c r="Q70" t="n">
-        <v>23482</v>
+        <v>24431</v>
       </c>
       <c r="R70" t="n">
-        <v>93.93000000000001</v>
+        <v>97.72</v>
       </c>
       <c r="S70" t="n">
         <v>8</v>
@@ -6965,7 +6965,7 @@
         <v>3522</v>
       </c>
       <c r="P99" t="n">
-        <v>3348</v>
+        <v>3414</v>
       </c>
       <c r="Q99" t="n">
         <v>3576</v>
@@ -7361,7 +7361,7 @@
         <v>27513</v>
       </c>
       <c r="P105" t="n">
-        <v>12812</v>
+        <v>12281</v>
       </c>
       <c r="Q105" t="n">
         <v>27513</v>
@@ -7431,7 +7431,7 @@
         <v>9607</v>
       </c>
       <c r="P106" t="n">
-        <v>3269</v>
+        <v>2863</v>
       </c>
       <c r="Q106" t="n">
         <v>9607</v>
@@ -9525,13 +9525,13 @@
         <v>22643</v>
       </c>
       <c r="P139" t="n">
-        <v>23453</v>
+        <v>23750</v>
       </c>
       <c r="Q139" t="n">
-        <v>23453</v>
+        <v>23750</v>
       </c>
       <c r="R139" t="n">
-        <v>93.81</v>
+        <v>95</v>
       </c>
       <c r="S139" t="n">
         <v>8</v>
@@ -9665,7 +9665,7 @@
         <v>4729</v>
       </c>
       <c r="P141" t="n">
-        <v>5067</v>
+        <v>5101</v>
       </c>
       <c r="Q141" t="n">
         <v>5336</v>
@@ -11871,7 +11871,7 @@
         <v>6068</v>
       </c>
       <c r="P175" t="n">
-        <v>2859</v>
+        <v>2762</v>
       </c>
       <c r="Q175" t="n">
         <v>6068</v>
@@ -14457,7 +14457,7 @@
         <v>13013</v>
       </c>
       <c r="P214" t="n">
-        <v>12581</v>
+        <v>12753</v>
       </c>
       <c r="Q214" t="n">
         <v>13013</v>
@@ -15715,7 +15715,7 @@
         <v>6622</v>
       </c>
       <c r="P233" t="n">
-        <v>5941</v>
+        <v>5991</v>
       </c>
       <c r="Q233" t="n">
         <v>6622</v>
@@ -15995,13 +15995,13 @@
         <v>1844</v>
       </c>
       <c r="P237" t="n">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="Q237" t="n">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="R237" t="n">
-        <v>46.39</v>
+        <v>46.44</v>
       </c>
       <c r="S237" t="n">
         <v>8</v>
@@ -16345,7 +16345,7 @@
         <v>7078</v>
       </c>
       <c r="P242" t="n">
-        <v>6131</v>
+        <v>5819</v>
       </c>
       <c r="Q242" t="n">
         <v>7078</v>
@@ -16415,7 +16415,7 @@
         <v>7330</v>
       </c>
       <c r="P243" t="n">
-        <v>5759</v>
+        <v>5618</v>
       </c>
       <c r="Q243" t="n">
         <v>7330</v>
@@ -16485,7 +16485,7 @@
         <v>3733</v>
       </c>
       <c r="P244" t="n">
-        <v>2660</v>
+        <v>2643</v>
       </c>
       <c r="Q244" t="n">
         <v>3733</v>
@@ -16555,7 +16555,7 @@
         <v>3899</v>
       </c>
       <c r="P245" t="n">
-        <v>2946</v>
+        <v>2850</v>
       </c>
       <c r="Q245" t="n">
         <v>3899</v>
@@ -16695,7 +16695,7 @@
         <v>4579</v>
       </c>
       <c r="P247" t="n">
-        <v>4327</v>
+        <v>4199</v>
       </c>
       <c r="Q247" t="n">
         <v>4579</v>
@@ -17605,7 +17605,7 @@
         <v>1054</v>
       </c>
       <c r="P260" t="n">
-        <v>1009</v>
+        <v>1038</v>
       </c>
       <c r="Q260" t="n">
         <v>1371</v>
@@ -17745,13 +17745,13 @@
         <v>4353</v>
       </c>
       <c r="P262" t="n">
-        <v>4488</v>
+        <v>4533</v>
       </c>
       <c r="Q262" t="n">
-        <v>4488</v>
+        <v>4533</v>
       </c>
       <c r="R262" t="n">
-        <v>89.41</v>
+        <v>90.31</v>
       </c>
       <c r="S262" t="n">
         <v>8</v>
@@ -17955,13 +17955,13 @@
         <v>6086</v>
       </c>
       <c r="P265" t="n">
-        <v>6309</v>
+        <v>6514</v>
       </c>
       <c r="Q265" t="n">
-        <v>6309</v>
+        <v>6514</v>
       </c>
       <c r="R265" t="n">
-        <v>78.86</v>
+        <v>81.42</v>
       </c>
       <c r="S265" t="n">
         <v>8</v>
@@ -18095,13 +18095,13 @@
         <v>2312</v>
       </c>
       <c r="P267" t="n">
-        <v>2398</v>
+        <v>2428</v>
       </c>
       <c r="Q267" t="n">
-        <v>2398</v>
+        <v>2428</v>
       </c>
       <c r="R267" t="n">
-        <v>59.95</v>
+        <v>60.7</v>
       </c>
       <c r="S267" t="n">
         <v>8</v>
@@ -18445,7 +18445,7 @@
         <v>4999</v>
       </c>
       <c r="P272" t="n">
-        <v>5018</v>
+        <v>5031</v>
       </c>
       <c r="Q272" t="n">
         <v>5324</v>
@@ -18515,7 +18515,7 @@
         <v>4413</v>
       </c>
       <c r="P273" t="n">
-        <v>4307</v>
+        <v>4400</v>
       </c>
       <c r="Q273" t="n">
         <v>4413</v>
@@ -18981,7 +18981,7 @@
         <v>84</v>
       </c>
       <c r="P280" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="Q280" t="n">
         <v>807</v>
@@ -19051,7 +19051,7 @@
         <v>886</v>
       </c>
       <c r="P281" t="n">
-        <v>914</v>
+        <v>829</v>
       </c>
       <c r="Q281" t="n">
         <v>2450</v>
@@ -19843,13 +19843,13 @@
         <v>2181</v>
       </c>
       <c r="P293" t="n">
-        <v>2249</v>
+        <v>2268</v>
       </c>
       <c r="Q293" t="n">
-        <v>2249</v>
+        <v>2268</v>
       </c>
       <c r="R293" t="n">
-        <v>74.97</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="S293" t="n">
         <v>8</v>
@@ -19913,7 +19913,7 @@
         <v>250</v>
       </c>
       <c r="P294" t="n">
-        <v>253</v>
+        <v>492</v>
       </c>
       <c r="Q294" t="n">
         <v>874</v>
@@ -22545,13 +22545,13 @@
         <v>5311</v>
       </c>
       <c r="P334" t="n">
-        <v>6185</v>
+        <v>6850</v>
       </c>
       <c r="Q334" t="n">
-        <v>6185</v>
+        <v>6850</v>
       </c>
       <c r="R334" t="n">
-        <v>51.54</v>
+        <v>57.08</v>
       </c>
       <c r="S334" t="n">
         <v>8</v>
@@ -23523,13 +23523,13 @@
         <v>6030</v>
       </c>
       <c r="P349" t="n">
-        <v>8182</v>
+        <v>7979</v>
       </c>
       <c r="Q349" t="n">
-        <v>8182</v>
+        <v>7979</v>
       </c>
       <c r="R349" t="n">
-        <v>81.5</v>
+        <v>79.48</v>
       </c>
       <c r="S349" t="n">
         <v>8</v>
@@ -23663,7 +23663,7 @@
         <v>2641</v>
       </c>
       <c r="P351" t="n">
-        <v>3164</v>
+        <v>2962</v>
       </c>
       <c r="Q351" t="n">
         <v>4698</v>
@@ -24363,13 +24363,13 @@
         <v>2223</v>
       </c>
       <c r="P361" t="n">
-        <v>2106</v>
+        <v>2702</v>
       </c>
       <c r="Q361" t="n">
-        <v>2223</v>
+        <v>2702</v>
       </c>
       <c r="R361" t="n">
-        <v>22.23</v>
+        <v>27.02</v>
       </c>
       <c r="S361" t="n">
         <v>8</v>
@@ -25273,13 +25273,13 @@
         <v>3531</v>
       </c>
       <c r="P374" t="n">
-        <v>5191</v>
+        <v>5100</v>
       </c>
       <c r="Q374" t="n">
-        <v>5191</v>
+        <v>5100</v>
       </c>
       <c r="R374" t="n">
-        <v>51.91</v>
+        <v>51</v>
       </c>
       <c r="S374" t="n">
         <v>8</v>
@@ -25623,7 +25623,7 @@
         <v>5910</v>
       </c>
       <c r="P379" t="n">
-        <v>5163</v>
+        <v>5369</v>
       </c>
       <c r="Q379" t="n">
         <v>5910</v>
@@ -26323,7 +26323,7 @@
         <v>7403</v>
       </c>
       <c r="P389" t="n">
-        <v>5725</v>
+        <v>5593</v>
       </c>
       <c r="Q389" t="n">
         <v>7403</v>
@@ -26393,13 +26393,13 @@
         <v>2485</v>
       </c>
       <c r="P390" t="n">
-        <v>2886</v>
+        <v>2971</v>
       </c>
       <c r="Q390" t="n">
-        <v>2886</v>
+        <v>2971</v>
       </c>
       <c r="R390" t="n">
-        <v>28.86</v>
+        <v>29.71</v>
       </c>
       <c r="S390" t="n">
         <v>8</v>
@@ -26463,13 +26463,13 @@
         <v>172</v>
       </c>
       <c r="P391" t="n">
-        <v>1020</v>
+        <v>698</v>
       </c>
       <c r="Q391" t="n">
-        <v>1020</v>
+        <v>698</v>
       </c>
       <c r="R391" t="n">
-        <v>10.2</v>
+        <v>6.98</v>
       </c>
       <c r="S391" t="n">
         <v>8</v>
@@ -26673,13 +26673,13 @@
         <v>1037</v>
       </c>
       <c r="P394" t="n">
-        <v>1486</v>
+        <v>1383</v>
       </c>
       <c r="Q394" t="n">
-        <v>1486</v>
+        <v>1383</v>
       </c>
       <c r="R394" t="n">
-        <v>14.86</v>
+        <v>13.83</v>
       </c>
       <c r="S394" t="n">
         <v>8</v>
@@ -28119,13 +28119,13 @@
         <v>3854</v>
       </c>
       <c r="P415" t="n">
-        <v>3812</v>
+        <v>4215</v>
       </c>
       <c r="Q415" t="n">
-        <v>3854</v>
+        <v>4215</v>
       </c>
       <c r="R415" t="n">
-        <v>38.54</v>
+        <v>42.15</v>
       </c>
       <c r="S415" t="n">
         <v>8</v>
@@ -30359,13 +30359,13 @@
         <v>4704</v>
       </c>
       <c r="P447" t="n">
-        <v>5708</v>
+        <v>5716</v>
       </c>
       <c r="Q447" t="n">
-        <v>5708</v>
+        <v>5716</v>
       </c>
       <c r="R447" t="n">
-        <v>56.86</v>
+        <v>56.94</v>
       </c>
       <c r="S447" t="n">
         <v>8</v>
@@ -30499,13 +30499,13 @@
         <v>4114</v>
       </c>
       <c r="P449" t="n">
-        <v>6442</v>
+        <v>6837</v>
       </c>
       <c r="Q449" t="n">
-        <v>6442</v>
+        <v>6837</v>
       </c>
       <c r="R449" t="n">
-        <v>64.42</v>
+        <v>68.37</v>
       </c>
       <c r="S449" t="n">
         <v>8</v>
@@ -31899,13 +31899,13 @@
         <v>2969</v>
       </c>
       <c r="P469" t="n">
-        <v>3423</v>
+        <v>5619</v>
       </c>
       <c r="Q469" t="n">
-        <v>3423</v>
+        <v>5619</v>
       </c>
       <c r="R469" t="n">
-        <v>42.79</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="S469" t="n">
         <v>8</v>
@@ -32109,13 +32109,13 @@
         <v>5733</v>
       </c>
       <c r="P472" t="n">
-        <v>6132</v>
+        <v>7796</v>
       </c>
       <c r="Q472" t="n">
-        <v>6132</v>
+        <v>7796</v>
       </c>
       <c r="R472" t="n">
-        <v>61.32</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="S472" t="n">
         <v>8</v>
@@ -34629,13 +34629,13 @@
         <v>7115</v>
       </c>
       <c r="P508" t="n">
-        <v>7535</v>
+        <v>8280</v>
       </c>
       <c r="Q508" t="n">
-        <v>8169</v>
+        <v>8280</v>
       </c>
       <c r="R508" t="n">
-        <v>81.69</v>
+        <v>82.8</v>
       </c>
       <c r="S508" t="n">
         <v>8</v>
@@ -35329,13 +35329,13 @@
         <v>4667</v>
       </c>
       <c r="P518" t="n">
-        <v>4666</v>
+        <v>4816</v>
       </c>
       <c r="Q518" t="n">
-        <v>4712</v>
+        <v>4816</v>
       </c>
       <c r="R518" t="n">
-        <v>47.12</v>
+        <v>48.16</v>
       </c>
       <c r="S518" t="n">
         <v>8</v>
@@ -37007,7 +37007,7 @@
         <v>2804</v>
       </c>
       <c r="P543" t="n">
-        <v>711</v>
+        <v>688</v>
       </c>
       <c r="Q543" t="n">
         <v>5012</v>
@@ -37077,7 +37077,7 @@
         <v>5417</v>
       </c>
       <c r="P544" t="n">
-        <v>2415</v>
+        <v>2274</v>
       </c>
       <c r="Q544" t="n">
         <v>6510</v>
@@ -37287,7 +37287,7 @@
         <v>6600</v>
       </c>
       <c r="P547" t="n">
-        <v>5751</v>
+        <v>5188</v>
       </c>
       <c r="Q547" t="n">
         <v>8472</v>
@@ -37357,7 +37357,7 @@
         <v>3233</v>
       </c>
       <c r="P548" t="n">
-        <v>2219</v>
+        <v>742</v>
       </c>
       <c r="Q548" t="n">
         <v>3752</v>
@@ -37753,7 +37753,7 @@
         <v>529</v>
       </c>
       <c r="P554" t="n">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="Q554" t="n">
         <v>603</v>
@@ -37915,13 +37915,13 @@
         <v>1904</v>
       </c>
       <c r="P557" t="n">
-        <v>3456</v>
+        <v>3563</v>
       </c>
       <c r="Q557" t="n">
-        <v>3456</v>
+        <v>3563</v>
       </c>
       <c r="R557" t="n">
-        <v>17.28</v>
+        <v>17.82</v>
       </c>
       <c r="S557" t="n">
         <v>8</v>
@@ -38777,7 +38777,7 @@
         <v>3766</v>
       </c>
       <c r="P570" t="n">
-        <v>3008</v>
+        <v>2695</v>
       </c>
       <c r="Q570" t="n">
         <v>3836</v>
@@ -38987,13 +38987,13 @@
         <v>4368</v>
       </c>
       <c r="P573" t="n">
-        <v>4456</v>
+        <v>4606</v>
       </c>
       <c r="Q573" t="n">
-        <v>4456</v>
+        <v>4606</v>
       </c>
       <c r="R573" t="n">
-        <v>67.55</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="S573" t="n">
         <v>8</v>
@@ -40293,7 +40293,7 @@
         <v>398</v>
       </c>
       <c r="P592" t="n">
-        <v>167</v>
+        <v>92</v>
       </c>
       <c r="Q592" t="n">
         <v>398</v>
@@ -41553,7 +41553,7 @@
         <v>3274</v>
       </c>
       <c r="P610" t="n">
-        <v>2532</v>
+        <v>2933</v>
       </c>
       <c r="Q610" t="n">
         <v>3274</v>
@@ -43185,13 +43185,13 @@
         <v>447</v>
       </c>
       <c r="P634" t="n">
-        <v>687</v>
+        <v>942</v>
       </c>
       <c r="Q634" t="n">
-        <v>687</v>
+        <v>942</v>
       </c>
       <c r="R634" t="n">
-        <v>11.45</v>
+        <v>15.7</v>
       </c>
       <c r="S634" t="n">
         <v>8</v>
@@ -43465,7 +43465,7 @@
         <v>7248</v>
       </c>
       <c r="P638" t="n">
-        <v>4823</v>
+        <v>4412</v>
       </c>
       <c r="Q638" t="n">
         <v>9088</v>
@@ -44445,7 +44445,7 @@
         <v>2179</v>
       </c>
       <c r="P652" t="n">
-        <v>2151</v>
+        <v>2780</v>
       </c>
       <c r="Q652" t="n">
         <v>2801</v>
@@ -45891,13 +45891,13 @@
         <v>2439</v>
       </c>
       <c r="P673" t="n">
-        <v>3098</v>
+        <v>3083</v>
       </c>
       <c r="Q673" t="n">
-        <v>3098</v>
+        <v>3083</v>
       </c>
       <c r="R673" t="n">
-        <v>25.82</v>
+        <v>25.69</v>
       </c>
       <c r="S673" t="n">
         <v>8</v>
@@ -46893,13 +46893,13 @@
         <v>372</v>
       </c>
       <c r="P688" t="n">
-        <v>687</v>
+        <v>932</v>
       </c>
       <c r="Q688" t="n">
-        <v>687</v>
+        <v>932</v>
       </c>
       <c r="R688" t="n">
-        <v>15.98</v>
+        <v>21.67</v>
       </c>
       <c r="S688" t="n">
         <v>8</v>
@@ -47803,13 +47803,13 @@
         <v>266</v>
       </c>
       <c r="P701" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="Q701" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="R701" t="n">
-        <v>6.9</v>
+        <v>7.02</v>
       </c>
       <c r="S701" t="n">
         <v>8</v>
@@ -48013,7 +48013,7 @@
         <v>400</v>
       </c>
       <c r="P704" t="n">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="Q704" t="n">
         <v>410</v>
@@ -48083,7 +48083,7 @@
         <v>3176</v>
       </c>
       <c r="P705" t="n">
-        <v>1030</v>
+        <v>1082</v>
       </c>
       <c r="Q705" t="n">
         <v>3176</v>
@@ -48503,7 +48503,7 @@
         <v>4</v>
       </c>
       <c r="P711" t="n">
-        <v>-56</v>
+        <v>-50</v>
       </c>
       <c r="Q711" t="n">
         <v>4528</v>
@@ -48923,13 +48923,13 @@
         <v>1355</v>
       </c>
       <c r="P717" t="n">
-        <v>1334</v>
+        <v>1627</v>
       </c>
       <c r="Q717" t="n">
-        <v>1486</v>
+        <v>1627</v>
       </c>
       <c r="R717" t="n">
-        <v>14.8</v>
+        <v>16.21</v>
       </c>
       <c r="S717" t="n">
         <v>8</v>
@@ -49903,7 +49903,7 @@
         <v>6867</v>
       </c>
       <c r="P731" t="n">
-        <v>6370</v>
+        <v>6562</v>
       </c>
       <c r="Q731" t="n">
         <v>7742</v>
@@ -50533,7 +50533,7 @@
         <v>8830</v>
       </c>
       <c r="P740" t="n">
-        <v>6506</v>
+        <v>5581</v>
       </c>
       <c r="Q740" t="n">
         <v>8830</v>
@@ -51163,7 +51163,7 @@
         <v>5114</v>
       </c>
       <c r="P749" t="n">
-        <v>1917</v>
+        <v>1882</v>
       </c>
       <c r="Q749" t="n">
         <v>5114</v>
@@ -51233,7 +51233,7 @@
         <v>1154</v>
       </c>
       <c r="P750" t="n">
-        <v>910</v>
+        <v>877</v>
       </c>
       <c r="Q750" t="n">
         <v>1431</v>
@@ -51443,13 +51443,13 @@
         <v>1934</v>
       </c>
       <c r="P753" t="n">
-        <v>3412</v>
+        <v>3352</v>
       </c>
       <c r="Q753" t="n">
-        <v>3412</v>
+        <v>3352</v>
       </c>
       <c r="R753" t="n">
-        <v>42.65</v>
+        <v>41.9</v>
       </c>
       <c r="S753" t="n">
         <v>8</v>
@@ -56427,13 +56427,13 @@
         <v>7806</v>
       </c>
       <c r="P829" t="n">
-        <v>7480</v>
+        <v>9400</v>
       </c>
       <c r="Q829" t="n">
-        <v>7806</v>
+        <v>9400</v>
       </c>
       <c r="R829" t="n">
-        <v>65.05</v>
+        <v>78.33</v>
       </c>
       <c r="S829" t="n">
         <v>8</v>
@@ -56637,13 +56637,13 @@
         <v>1722</v>
       </c>
       <c r="P832" t="n">
-        <v>1891</v>
+        <v>1749</v>
       </c>
       <c r="Q832" t="n">
-        <v>1891</v>
+        <v>1749</v>
       </c>
       <c r="R832" t="n">
-        <v>21.01</v>
+        <v>19.43</v>
       </c>
       <c r="S832" t="n">
         <v>8</v>
@@ -59085,7 +59085,7 @@
         <v>5274</v>
       </c>
       <c r="P868" t="n">
-        <v>3737</v>
+        <v>3760</v>
       </c>
       <c r="Q868" t="n">
         <v>8343</v>

--- a/Valores_maximos_P_meses.xlsx
+++ b/Valores_maximos_P_meses.xlsx
@@ -810,7 +810,7 @@
         <v>11139</v>
       </c>
       <c r="Q5" t="n">
-        <v>9872</v>
+        <v>10367</v>
       </c>
       <c r="R5" t="n">
         <v>11929</v>
@@ -977,7 +977,7 @@
         <v>24350</v>
       </c>
       <c r="Q8" t="n">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="R8" t="n">
         <v>26168</v>
@@ -1050,7 +1050,7 @@
         <v>6171</v>
       </c>
       <c r="Q9" t="n">
-        <v>6004</v>
+        <v>6108</v>
       </c>
       <c r="R9" t="n">
         <v>6171</v>
@@ -1123,13 +1123,13 @@
         <v>20934</v>
       </c>
       <c r="Q10" t="n">
-        <v>20975</v>
+        <v>21564</v>
       </c>
       <c r="R10" t="n">
-        <v>20975</v>
+        <v>21564</v>
       </c>
       <c r="S10" t="n">
-        <v>83.90000000000001</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="T10" t="n">
         <v>2</v>
@@ -1754,7 +1754,7 @@
         <v>2938</v>
       </c>
       <c r="Q19" t="n">
-        <v>2622</v>
+        <v>2652</v>
       </c>
       <c r="R19" t="n">
         <v>3131</v>
@@ -2359,7 +2359,7 @@
         <v>12085</v>
       </c>
       <c r="Q28" t="n">
-        <v>11114</v>
+        <v>11209</v>
       </c>
       <c r="R28" t="n">
         <v>12217</v>
@@ -2865,7 +2865,7 @@
         <v>9554</v>
       </c>
       <c r="Q36" t="n">
-        <v>8794</v>
+        <v>8848</v>
       </c>
       <c r="R36" t="n">
         <v>9554</v>
@@ -5457,7 +5457,7 @@
         <v>26971</v>
       </c>
       <c r="Q74" t="n">
-        <v>26898</v>
+        <v>26948</v>
       </c>
       <c r="R74" t="n">
         <v>26971</v>
@@ -6333,7 +6333,7 @@
         <v>976</v>
       </c>
       <c r="Q86" t="n">
-        <v>930</v>
+        <v>993</v>
       </c>
       <c r="R86" t="n">
         <v>1173</v>
@@ -7715,7 +7715,7 @@
         <v>2863</v>
       </c>
       <c r="Q106" t="n">
-        <v>4241</v>
+        <v>3958</v>
       </c>
       <c r="R106" t="n">
         <v>9607</v>
@@ -8315,7 +8315,7 @@
         <v>19937</v>
       </c>
       <c r="Q116" t="n">
-        <v>16831</v>
+        <v>19536</v>
       </c>
       <c r="R116" t="n">
         <v>20122</v>
@@ -8727,7 +8727,7 @@
         <v>17861</v>
       </c>
       <c r="Q122" t="n">
-        <v>11327</v>
+        <v>14119</v>
       </c>
       <c r="R122" t="n">
         <v>17861</v>
@@ -8946,13 +8946,13 @@
         <v>28173</v>
       </c>
       <c r="Q125" t="n">
-        <v>28277</v>
+        <v>32272</v>
       </c>
       <c r="R125" t="n">
-        <v>28277</v>
+        <v>32272</v>
       </c>
       <c r="S125" t="n">
-        <v>113.11</v>
+        <v>129.09</v>
       </c>
       <c r="T125" t="n">
         <v>2</v>
@@ -10182,7 +10182,7 @@
         <v>16445</v>
       </c>
       <c r="Q143" t="n">
-        <v>12146</v>
+        <v>13555</v>
       </c>
       <c r="R143" t="n">
         <v>19796</v>
@@ -10852,7 +10852,7 @@
         <v>22480</v>
       </c>
       <c r="Q153" t="n">
-        <v>19242</v>
+        <v>20730</v>
       </c>
       <c r="R153" t="n">
         <v>31853</v>
@@ -11676,7 +11676,7 @@
         <v>20680</v>
       </c>
       <c r="Q165" t="n">
-        <v>12216</v>
+        <v>12422</v>
       </c>
       <c r="R165" t="n">
         <v>23412</v>
@@ -12474,7 +12474,7 @@
         <v>16659</v>
       </c>
       <c r="Q177" t="n">
-        <v>12791</v>
+        <v>15249</v>
       </c>
       <c r="R177" t="n">
         <v>19578</v>
@@ -12766,7 +12766,7 @@
         <v>23700</v>
       </c>
       <c r="Q181" t="n">
-        <v>22076</v>
+        <v>22215</v>
       </c>
       <c r="R181" t="n">
         <v>23700</v>
@@ -13131,7 +13131,7 @@
         <v>17525</v>
       </c>
       <c r="Q186" t="n">
-        <v>11415</v>
+        <v>13736</v>
       </c>
       <c r="R186" t="n">
         <v>23208</v>
@@ -13277,7 +13277,7 @@
         <v>27216</v>
       </c>
       <c r="Q188" t="n">
-        <v>9436</v>
+        <v>14435</v>
       </c>
       <c r="R188" t="n">
         <v>27359</v>
@@ -13496,7 +13496,7 @@
         <v>2677</v>
       </c>
       <c r="Q191" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R191" t="n">
         <v>2708</v>
@@ -13642,7 +13642,7 @@
         <v>11823</v>
       </c>
       <c r="Q193" t="n">
-        <v>8018</v>
+        <v>8046</v>
       </c>
       <c r="R193" t="n">
         <v>11823</v>
@@ -14821,7 +14821,7 @@
         <v>2828</v>
       </c>
       <c r="Q212" t="n">
-        <v>2504</v>
+        <v>2815</v>
       </c>
       <c r="R212" t="n">
         <v>2828</v>
@@ -15791,7 +15791,7 @@
         <v>23717</v>
       </c>
       <c r="Q226" t="n">
-        <v>21958</v>
+        <v>22271</v>
       </c>
       <c r="R226" t="n">
         <v>27054</v>
@@ -16203,7 +16203,7 @@
         <v>7722</v>
       </c>
       <c r="Q232" t="n">
-        <v>7026</v>
+        <v>7335</v>
       </c>
       <c r="R232" t="n">
         <v>7776</v>
@@ -16349,7 +16349,7 @@
         <v>8965</v>
       </c>
       <c r="Q234" t="n">
-        <v>7973</v>
+        <v>8398</v>
       </c>
       <c r="R234" t="n">
         <v>8965</v>
@@ -17444,13 +17444,13 @@
         <v>6193</v>
       </c>
       <c r="Q249" t="n">
-        <v>6065</v>
+        <v>6350</v>
       </c>
       <c r="R249" t="n">
-        <v>6287</v>
+        <v>6350</v>
       </c>
       <c r="S249" t="n">
-        <v>62.87</v>
+        <v>63.5</v>
       </c>
       <c r="T249" t="n">
         <v>2</v>
@@ -17955,7 +17955,7 @@
         <v>1175</v>
       </c>
       <c r="Q256" t="n">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="R256" t="n">
         <v>1251</v>
@@ -18101,7 +18101,7 @@
         <v>5437</v>
       </c>
       <c r="Q258" t="n">
-        <v>5234</v>
+        <v>5236</v>
       </c>
       <c r="R258" t="n">
         <v>5648</v>
@@ -18174,7 +18174,7 @@
         <v>5481</v>
       </c>
       <c r="Q259" t="n">
-        <v>5218</v>
+        <v>5268</v>
       </c>
       <c r="R259" t="n">
         <v>5793</v>
@@ -18393,7 +18393,7 @@
         <v>4533</v>
       </c>
       <c r="Q262" t="n">
-        <v>4236</v>
+        <v>4296</v>
       </c>
       <c r="R262" t="n">
         <v>4533</v>
@@ -18539,7 +18539,7 @@
         <v>3376</v>
       </c>
       <c r="Q264" t="n">
-        <v>3144</v>
+        <v>3197</v>
       </c>
       <c r="R264" t="n">
         <v>3376</v>
@@ -19681,7 +19681,7 @@
         <v>54</v>
       </c>
       <c r="Q280" t="n">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="R280" t="n">
         <v>807</v>
@@ -19827,7 +19827,7 @@
         <v>5717</v>
       </c>
       <c r="Q282" t="n">
-        <v>5086</v>
+        <v>5315</v>
       </c>
       <c r="R282" t="n">
         <v>5717</v>
@@ -19900,7 +19900,7 @@
         <v>4256</v>
       </c>
       <c r="Q283" t="n">
-        <v>3850</v>
+        <v>4060</v>
       </c>
       <c r="R283" t="n">
         <v>4502</v>
@@ -20046,7 +20046,7 @@
         <v>3724</v>
       </c>
       <c r="Q285" t="n">
-        <v>1867</v>
+        <v>2216</v>
       </c>
       <c r="R285" t="n">
         <v>4980</v>
@@ -20192,7 +20192,7 @@
         <v>3080</v>
       </c>
       <c r="Q287" t="n">
-        <v>3003</v>
+        <v>3070</v>
       </c>
       <c r="R287" t="n">
         <v>3215</v>
@@ -20359,7 +20359,7 @@
         <v>4744</v>
       </c>
       <c r="Q290" t="n">
-        <v>4576</v>
+        <v>4800</v>
       </c>
       <c r="R290" t="n">
         <v>4824</v>
@@ -20943,7 +20943,7 @@
         <v>1813</v>
       </c>
       <c r="Q298" t="n">
-        <v>1615</v>
+        <v>1631</v>
       </c>
       <c r="R298" t="n">
         <v>1847</v>
@@ -21016,7 +21016,7 @@
         <v>4602</v>
       </c>
       <c r="Q299" t="n">
-        <v>4178</v>
+        <v>4265</v>
       </c>
       <c r="R299" t="n">
         <v>4617</v>
@@ -21381,7 +21381,7 @@
         <v>648</v>
       </c>
       <c r="Q304" t="n">
-        <v>596</v>
+        <v>607</v>
       </c>
       <c r="R304" t="n">
         <v>648</v>
@@ -22257,13 +22257,13 @@
         <v>4815</v>
       </c>
       <c r="Q316" t="n">
-        <v>4709</v>
+        <v>4912</v>
       </c>
       <c r="R316" t="n">
-        <v>4815</v>
+        <v>4912</v>
       </c>
       <c r="S316" t="n">
-        <v>60.19</v>
+        <v>61.4</v>
       </c>
       <c r="T316" t="n">
         <v>2</v>
@@ -22977,7 +22977,7 @@
         <v>0</v>
       </c>
       <c r="Q328" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="R328" t="n">
         <v>384</v>
@@ -23535,13 +23535,13 @@
         <v>9284</v>
       </c>
       <c r="Q336" t="n">
-        <v>9656</v>
+        <v>9689</v>
       </c>
       <c r="R336" t="n">
-        <v>9656</v>
+        <v>9689</v>
       </c>
       <c r="S336" t="n">
-        <v>89.41</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="T336" t="n">
         <v>2</v>
@@ -23608,7 +23608,7 @@
         <v>7764</v>
       </c>
       <c r="Q337" t="n">
-        <v>7299</v>
+        <v>7583</v>
       </c>
       <c r="R337" t="n">
         <v>7764</v>
@@ -25136,7 +25136,7 @@
         <v>4644</v>
       </c>
       <c r="Q359" t="n">
-        <v>4327</v>
+        <v>4330</v>
       </c>
       <c r="R359" t="n">
         <v>4644</v>
@@ -25355,7 +25355,7 @@
         <v>8091</v>
       </c>
       <c r="Q362" t="n">
-        <v>7822</v>
+        <v>7960</v>
       </c>
       <c r="R362" t="n">
         <v>8091</v>
@@ -25428,7 +25428,7 @@
         <v>9345</v>
       </c>
       <c r="Q363" t="n">
-        <v>8799</v>
+        <v>9007</v>
       </c>
       <c r="R363" t="n">
         <v>9345</v>
@@ -27034,7 +27034,7 @@
         <v>3227</v>
       </c>
       <c r="Q385" t="n">
-        <v>2986</v>
+        <v>3061</v>
       </c>
       <c r="R385" t="n">
         <v>3436</v>
@@ -27472,7 +27472,7 @@
         <v>698</v>
       </c>
       <c r="Q391" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="R391" t="n">
         <v>698</v>
@@ -28541,7 +28541,7 @@
         <v>1469</v>
       </c>
       <c r="Q406" t="n">
-        <v>1200</v>
+        <v>1213</v>
       </c>
       <c r="R406" t="n">
         <v>1469</v>
@@ -28833,7 +28833,7 @@
         <v>4196</v>
       </c>
       <c r="Q410" t="n">
-        <v>4147</v>
+        <v>4198</v>
       </c>
       <c r="R410" t="n">
         <v>4295</v>
@@ -28906,7 +28906,7 @@
         <v>3711</v>
       </c>
       <c r="Q411" t="n">
-        <v>3553</v>
+        <v>3610</v>
       </c>
       <c r="R411" t="n">
         <v>3711</v>
@@ -28979,7 +28979,7 @@
         <v>9272</v>
       </c>
       <c r="Q412" t="n">
-        <v>7408</v>
+        <v>7543</v>
       </c>
       <c r="R412" t="n">
         <v>9317</v>
@@ -29125,7 +29125,7 @@
         <v>7063</v>
       </c>
       <c r="Q414" t="n">
-        <v>7021</v>
+        <v>7057</v>
       </c>
       <c r="R414" t="n">
         <v>7501</v>
@@ -29344,7 +29344,7 @@
         <v>6227</v>
       </c>
       <c r="Q417" t="n">
-        <v>5917</v>
+        <v>6223</v>
       </c>
       <c r="R417" t="n">
         <v>6227</v>
@@ -29417,7 +29417,7 @@
         <v>3535</v>
       </c>
       <c r="Q418" t="n">
-        <v>3323</v>
+        <v>3360</v>
       </c>
       <c r="R418" t="n">
         <v>3545</v>
@@ -30293,13 +30293,13 @@
         <v>5641</v>
       </c>
       <c r="Q430" t="n">
-        <v>5562</v>
+        <v>5738</v>
       </c>
       <c r="R430" t="n">
-        <v>5641</v>
+        <v>5738</v>
       </c>
       <c r="S430" t="n">
-        <v>56.19</v>
+        <v>57.16</v>
       </c>
       <c r="T430" t="n">
         <v>2</v>
@@ -31169,13 +31169,13 @@
         <v>334</v>
       </c>
       <c r="Q442" t="n">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="R442" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="S442" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="T442" t="n">
         <v>2</v>
@@ -31607,7 +31607,7 @@
         <v>9289</v>
       </c>
       <c r="Q448" t="n">
-        <v>8939</v>
+        <v>9148</v>
       </c>
       <c r="R448" t="n">
         <v>9289</v>
@@ -32556,7 +32556,7 @@
         <v>4367</v>
       </c>
       <c r="Q461" t="n">
-        <v>2997</v>
+        <v>3019</v>
       </c>
       <c r="R461" t="n">
         <v>5366</v>
@@ -32629,13 +32629,13 @@
         <v>586</v>
       </c>
       <c r="Q462" t="n">
-        <v>550</v>
+        <v>608</v>
       </c>
       <c r="R462" t="n">
-        <v>586</v>
+        <v>608</v>
       </c>
       <c r="S462" t="n">
-        <v>29.3</v>
+        <v>30.4</v>
       </c>
       <c r="T462" t="n">
         <v>2</v>
@@ -32848,7 +32848,7 @@
         <v>5447</v>
       </c>
       <c r="Q465" t="n">
-        <v>4522</v>
+        <v>4534</v>
       </c>
       <c r="R465" t="n">
         <v>6268</v>
@@ -33286,7 +33286,7 @@
         <v>4033</v>
       </c>
       <c r="Q471" t="n">
-        <v>3766</v>
+        <v>3841</v>
       </c>
       <c r="R471" t="n">
         <v>4731</v>
@@ -34454,7 +34454,7 @@
         <v>944</v>
       </c>
       <c r="Q487" t="n">
-        <v>885</v>
+        <v>911</v>
       </c>
       <c r="R487" t="n">
         <v>965</v>
@@ -37082,7 +37082,7 @@
         <v>3353</v>
       </c>
       <c r="Q523" t="n">
-        <v>3061</v>
+        <v>3073</v>
       </c>
       <c r="R523" t="n">
         <v>3596</v>
@@ -38391,7 +38391,7 @@
         <v>113</v>
       </c>
       <c r="Q542" t="n">
-        <v>190</v>
+        <v>149</v>
       </c>
       <c r="R542" t="n">
         <v>3755</v>
@@ -38610,7 +38610,7 @@
         <v>2154</v>
       </c>
       <c r="Q545" t="n">
-        <v>1084</v>
+        <v>942</v>
       </c>
       <c r="R545" t="n">
         <v>6861</v>
@@ -38902,7 +38902,7 @@
         <v>610</v>
       </c>
       <c r="Q549" t="n">
-        <v>1505</v>
+        <v>1399</v>
       </c>
       <c r="R549" t="n">
         <v>3847</v>
@@ -38975,7 +38975,7 @@
         <v>1699</v>
       </c>
       <c r="Q550" t="n">
-        <v>1616</v>
+        <v>1652</v>
       </c>
       <c r="R550" t="n">
         <v>1837</v>
@@ -39408,7 +39408,7 @@
         <v>3687</v>
       </c>
       <c r="Q557" t="n">
-        <v>2311</v>
+        <v>3655</v>
       </c>
       <c r="R557" t="n">
         <v>3687</v>
@@ -40305,7 +40305,7 @@
         <v>2695</v>
       </c>
       <c r="Q570" t="n">
-        <v>2790</v>
+        <v>3363</v>
       </c>
       <c r="R570" t="n">
         <v>3836</v>
@@ -40378,7 +40378,7 @@
         <v>6670</v>
       </c>
       <c r="Q571" t="n">
-        <v>5212</v>
+        <v>5382</v>
       </c>
       <c r="R571" t="n">
         <v>6670</v>
@@ -41374,7 +41374,7 @@
         <v>3804</v>
       </c>
       <c r="Q585" t="n">
-        <v>2547</v>
+        <v>2570</v>
       </c>
       <c r="R585" t="n">
         <v>5542</v>
@@ -41447,7 +41447,7 @@
         <v>3230</v>
       </c>
       <c r="Q586" t="n">
-        <v>2576</v>
+        <v>3057</v>
       </c>
       <c r="R586" t="n">
         <v>3230</v>
@@ -41520,7 +41520,7 @@
         <v>3744</v>
       </c>
       <c r="Q587" t="n">
-        <v>3472</v>
+        <v>3741</v>
       </c>
       <c r="R587" t="n">
         <v>3744</v>
@@ -41739,7 +41739,7 @@
         <v>4968</v>
       </c>
       <c r="Q590" t="n">
-        <v>3079</v>
+        <v>3529</v>
       </c>
       <c r="R590" t="n">
         <v>4968</v>
@@ -41812,7 +41812,7 @@
         <v>6869</v>
       </c>
       <c r="Q591" t="n">
-        <v>4851</v>
+        <v>6152</v>
       </c>
       <c r="R591" t="n">
         <v>6869</v>
@@ -42250,7 +42250,7 @@
         <v>8368</v>
       </c>
       <c r="Q597" t="n">
-        <v>7808</v>
+        <v>8168</v>
       </c>
       <c r="R597" t="n">
         <v>8368</v>
@@ -42469,7 +42469,7 @@
         <v>7268</v>
       </c>
       <c r="Q600" t="n">
-        <v>5147</v>
+        <v>5181</v>
       </c>
       <c r="R600" t="n">
         <v>7268</v>
@@ -43199,7 +43199,7 @@
         <v>2933</v>
       </c>
       <c r="Q610" t="n">
-        <v>2686</v>
+        <v>2327</v>
       </c>
       <c r="R610" t="n">
         <v>3274</v>
@@ -44169,7 +44169,7 @@
         <v>3527</v>
       </c>
       <c r="Q624" t="n">
-        <v>952</v>
+        <v>1322</v>
       </c>
       <c r="R624" t="n">
         <v>5528</v>
@@ -44242,7 +44242,7 @@
         <v>8231</v>
       </c>
       <c r="Q625" t="n">
-        <v>3770</v>
+        <v>4914</v>
       </c>
       <c r="R625" t="n">
         <v>8231</v>
@@ -44461,13 +44461,13 @@
         <v>4430</v>
       </c>
       <c r="Q628" t="n">
-        <v>4341</v>
+        <v>6326</v>
       </c>
       <c r="R628" t="n">
-        <v>5342</v>
+        <v>6326</v>
       </c>
       <c r="S628" t="n">
-        <v>66.77</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="T628" t="n">
         <v>2</v>
@@ -44607,13 +44607,13 @@
         <v>1500</v>
       </c>
       <c r="Q630" t="n">
-        <v>1749</v>
+        <v>1833</v>
       </c>
       <c r="R630" t="n">
-        <v>1749</v>
+        <v>1833</v>
       </c>
       <c r="S630" t="n">
-        <v>19.43</v>
+        <v>20.37</v>
       </c>
       <c r="T630" t="n">
         <v>2</v>
@@ -44680,7 +44680,7 @@
         <v>3312</v>
       </c>
       <c r="Q631" t="n">
-        <v>0</v>
+        <v>1812</v>
       </c>
       <c r="R631" t="n">
         <v>3312</v>
@@ -44826,7 +44826,7 @@
         <v>2582</v>
       </c>
       <c r="Q633" t="n">
-        <v>0</v>
+        <v>2328</v>
       </c>
       <c r="R633" t="n">
         <v>2582</v>
@@ -45118,7 +45118,7 @@
         <v>2479</v>
       </c>
       <c r="Q637" t="n">
-        <v>2099</v>
+        <v>2252</v>
       </c>
       <c r="R637" t="n">
         <v>2816</v>
@@ -45191,7 +45191,7 @@
         <v>4412</v>
       </c>
       <c r="Q638" t="n">
-        <v>3462</v>
+        <v>3797</v>
       </c>
       <c r="R638" t="n">
         <v>9088</v>
@@ -45264,7 +45264,7 @@
         <v>8908</v>
       </c>
       <c r="Q639" t="n">
-        <v>4929</v>
+        <v>6274</v>
       </c>
       <c r="R639" t="n">
         <v>8908</v>
@@ -45775,7 +45775,7 @@
         <v>3858</v>
       </c>
       <c r="Q646" t="n">
-        <v>3599</v>
+        <v>3714</v>
       </c>
       <c r="R646" t="n">
         <v>5433</v>
@@ -45848,7 +45848,7 @@
         <v>6421</v>
       </c>
       <c r="Q647" t="n">
-        <v>6248</v>
+        <v>6334</v>
       </c>
       <c r="R647" t="n">
         <v>6540</v>
@@ -45994,13 +45994,13 @@
         <v>5887</v>
       </c>
       <c r="Q649" t="n">
-        <v>6030</v>
+        <v>7490</v>
       </c>
       <c r="R649" t="n">
-        <v>6820</v>
+        <v>7490</v>
       </c>
       <c r="S649" t="n">
-        <v>56.83</v>
+        <v>62.42</v>
       </c>
       <c r="T649" t="n">
         <v>2</v>
@@ -46771,7 +46771,7 @@
         <v>6978</v>
       </c>
       <c r="Q660" t="n">
-        <v>6718</v>
+        <v>8634</v>
       </c>
       <c r="R660" t="n">
         <v>10585</v>
@@ -46844,7 +46844,7 @@
         <v>9582</v>
       </c>
       <c r="Q661" t="n">
-        <v>7059</v>
+        <v>7270</v>
       </c>
       <c r="R661" t="n">
         <v>11193</v>
@@ -46990,7 +46990,7 @@
         <v>1438</v>
       </c>
       <c r="Q663" t="n">
-        <v>1504</v>
+        <v>1298</v>
       </c>
       <c r="R663" t="n">
         <v>8614</v>
@@ -47939,7 +47939,7 @@
         <v>2665</v>
       </c>
       <c r="Q676" t="n">
-        <v>1343</v>
+        <v>1376</v>
       </c>
       <c r="R676" t="n">
         <v>2895</v>
@@ -48377,7 +48377,7 @@
         <v>4536</v>
       </c>
       <c r="Q682" t="n">
-        <v>3571</v>
+        <v>3573</v>
       </c>
       <c r="R682" t="n">
         <v>5228</v>
@@ -49639,7 +49639,7 @@
         <v>2664</v>
       </c>
       <c r="Q700" t="n">
-        <v>2853</v>
+        <v>2921</v>
       </c>
       <c r="R700" t="n">
         <v>3510</v>
@@ -50077,7 +50077,7 @@
         <v>1272</v>
       </c>
       <c r="Q706" t="n">
-        <v>665</v>
+        <v>1065</v>
       </c>
       <c r="R706" t="n">
         <v>1318</v>
@@ -50150,7 +50150,7 @@
         <v>1002</v>
       </c>
       <c r="Q707" t="n">
-        <v>311</v>
+        <v>388</v>
       </c>
       <c r="R707" t="n">
         <v>1777</v>
@@ -50515,7 +50515,7 @@
         <v>4896</v>
       </c>
       <c r="Q712" t="n">
-        <v>4410</v>
+        <v>4484</v>
       </c>
       <c r="R712" t="n">
         <v>4896</v>
@@ -50661,7 +50661,7 @@
         <v>9639</v>
       </c>
       <c r="Q714" t="n">
-        <v>5908</v>
+        <v>8190</v>
       </c>
       <c r="R714" t="n">
         <v>9639</v>
@@ -50734,7 +50734,7 @@
         <v>6619</v>
       </c>
       <c r="Q715" t="n">
-        <v>4458</v>
+        <v>4943</v>
       </c>
       <c r="R715" t="n">
         <v>6709</v>
@@ -51537,7 +51537,7 @@
         <v>4343</v>
       </c>
       <c r="Q726" t="n">
-        <v>3860</v>
+        <v>3908</v>
       </c>
       <c r="R726" t="n">
         <v>5849</v>
@@ -51902,7 +51902,7 @@
         <v>6562</v>
       </c>
       <c r="Q731" t="n">
-        <v>6137</v>
+        <v>6172</v>
       </c>
       <c r="R731" t="n">
         <v>7742</v>
@@ -52486,7 +52486,7 @@
         <v>2885</v>
       </c>
       <c r="Q739" t="n">
-        <v>842</v>
+        <v>889</v>
       </c>
       <c r="R739" t="n">
         <v>2885</v>
@@ -52559,7 +52559,7 @@
         <v>5581</v>
       </c>
       <c r="Q740" t="n">
-        <v>3559</v>
+        <v>3593</v>
       </c>
       <c r="R740" t="n">
         <v>8830</v>
@@ -52632,7 +52632,7 @@
         <v>1746</v>
       </c>
       <c r="Q741" t="n">
-        <v>1228</v>
+        <v>1510</v>
       </c>
       <c r="R741" t="n">
         <v>1746</v>
@@ -52705,7 +52705,7 @@
         <v>6822</v>
       </c>
       <c r="Q742" t="n">
-        <v>3927</v>
+        <v>6238</v>
       </c>
       <c r="R742" t="n">
         <v>11079</v>
@@ -53143,7 +53143,7 @@
         <v>4821</v>
       </c>
       <c r="Q748" t="n">
-        <v>3171</v>
+        <v>5728</v>
       </c>
       <c r="R748" t="n">
         <v>5858</v>
@@ -55375,13 +55375,13 @@
         <v>1036</v>
       </c>
       <c r="Q780" t="n">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="R780" t="n">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="S780" t="n">
-        <v>26.52</v>
+        <v>26.72</v>
       </c>
       <c r="T780" t="n">
         <v>2</v>
@@ -55667,7 +55667,7 @@
         <v>5739</v>
       </c>
       <c r="Q784" t="n">
-        <v>4204</v>
+        <v>4213</v>
       </c>
       <c r="R784" t="n">
         <v>5739</v>
@@ -57560,7 +57560,7 @@
         <v>156</v>
       </c>
       <c r="Q811" t="n">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="R811" t="n">
         <v>4173</v>
@@ -58765,7 +58765,7 @@
         <v>7</v>
       </c>
       <c r="Q830" t="n">
-        <v>-242</v>
+        <v>0</v>
       </c>
       <c r="R830" t="n">
         <v>3542</v>
@@ -58911,7 +58911,7 @@
         <v>1749</v>
       </c>
       <c r="Q832" t="n">
-        <v>1617</v>
+        <v>1629</v>
       </c>
       <c r="R832" t="n">
         <v>1749</v>
@@ -59714,7 +59714,7 @@
         <v>6196</v>
       </c>
       <c r="Q843" t="n">
-        <v>6089</v>
+        <v>6123</v>
       </c>
       <c r="R843" t="n">
         <v>6196</v>
@@ -60809,7 +60809,7 @@
         <v>7741</v>
       </c>
       <c r="Q858" t="n">
-        <v>6829</v>
+        <v>7254</v>
       </c>
       <c r="R858" t="n">
         <v>7741</v>
@@ -61169,7 +61169,7 @@
         <v>4927</v>
       </c>
       <c r="Q864" t="n">
-        <v>3963</v>
+        <v>4587</v>
       </c>
       <c r="R864" t="n">
         <v>6268</v>
@@ -61242,7 +61242,7 @@
         <v>5966</v>
       </c>
       <c r="Q865" t="n">
-        <v>4198</v>
+        <v>4352</v>
       </c>
       <c r="R865" t="n">
         <v>5966</v>
@@ -61388,7 +61388,7 @@
         <v>6263</v>
       </c>
       <c r="Q867" t="n">
-        <v>5944</v>
+        <v>6026</v>
       </c>
       <c r="R867" t="n">
         <v>6309</v>
@@ -61534,7 +61534,7 @@
         <v>5201</v>
       </c>
       <c r="Q869" t="n">
-        <v>4056</v>
+        <v>4354</v>
       </c>
       <c r="R869" t="n">
         <v>8644</v>
@@ -61607,7 +61607,7 @@
         <v>10949</v>
       </c>
       <c r="Q870" t="n">
-        <v>7272</v>
+        <v>9567</v>
       </c>
       <c r="R870" t="n">
         <v>12918</v>
@@ -61680,7 +61680,7 @@
         <v>5310</v>
       </c>
       <c r="Q871" t="n">
-        <v>4444</v>
+        <v>4475</v>
       </c>
       <c r="R871" t="n">
         <v>5310</v>

--- a/Valores_maximos_P_meses.xlsx
+++ b/Valores_maximos_P_meses.xlsx
@@ -10076,7 +10076,7 @@
         <v>13.8</v>
       </c>
       <c r="F142" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="G142" t="n">
         <v>2357</v>
@@ -10115,7 +10115,7 @@
         <v>3089</v>
       </c>
       <c r="S142" t="n">
-        <v>102.97</v>
+        <v>61.78</v>
       </c>
       <c r="T142" t="n">
         <v>2</v>

--- a/Valores_maximos_P_meses.xlsx
+++ b/Valores_maximos_P_meses.xlsx
@@ -1900,7 +1900,7 @@
         <v>740</v>
       </c>
       <c r="Q21" t="n">
-        <v>688</v>
+        <v>708</v>
       </c>
       <c r="R21" t="n">
         <v>740</v>
@@ -2020,7 +2020,7 @@
         <v>1594</v>
       </c>
       <c r="Q23" t="n">
-        <v>1539</v>
+        <v>1552</v>
       </c>
       <c r="R23" t="n">
         <v>1594</v>
@@ -2719,7 +2719,7 @@
         <v>1987</v>
       </c>
       <c r="Q34" t="n">
-        <v>1707</v>
+        <v>1731</v>
       </c>
       <c r="R34" t="n">
         <v>1987</v>
@@ -2792,13 +2792,13 @@
         <v>2265</v>
       </c>
       <c r="Q35" t="n">
-        <v>2268</v>
+        <v>2280</v>
       </c>
       <c r="R35" t="n">
-        <v>2268</v>
+        <v>2280</v>
       </c>
       <c r="S35" t="n">
-        <v>75.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="T35" t="n">
         <v>2</v>
@@ -2865,13 +2865,13 @@
         <v>9554</v>
       </c>
       <c r="Q36" t="n">
-        <v>8848</v>
+        <v>9628</v>
       </c>
       <c r="R36" t="n">
-        <v>9554</v>
+        <v>9628</v>
       </c>
       <c r="S36" t="n">
-        <v>38.22</v>
+        <v>38.51</v>
       </c>
       <c r="T36" t="n">
         <v>2</v>
@@ -3715,13 +3715,13 @@
         <v>677</v>
       </c>
       <c r="Q48" t="n">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="R48" t="n">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="S48" t="n">
-        <v>68.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="T48" t="n">
         <v>2</v>
@@ -4174,7 +4174,7 @@
         <v>17663</v>
       </c>
       <c r="Q55" t="n">
-        <v>16763</v>
+        <v>17116</v>
       </c>
       <c r="R55" t="n">
         <v>17663</v>
@@ -4513,7 +4513,7 @@
         <v>26213</v>
       </c>
       <c r="Q60" t="n">
-        <v>23780</v>
+        <v>24718</v>
       </c>
       <c r="R60" t="n">
         <v>26404</v>
@@ -4586,7 +4586,7 @@
         <v>20399</v>
       </c>
       <c r="Q61" t="n">
-        <v>16066</v>
+        <v>16097</v>
       </c>
       <c r="R61" t="n">
         <v>20399</v>
@@ -4659,7 +4659,7 @@
         <v>39390</v>
       </c>
       <c r="Q62" t="n">
-        <v>37160</v>
+        <v>38393</v>
       </c>
       <c r="R62" t="n">
         <v>39390</v>
@@ -5337,7 +5337,7 @@
         <v>27366</v>
       </c>
       <c r="Q72" t="n">
-        <v>25978</v>
+        <v>26086</v>
       </c>
       <c r="R72" t="n">
         <v>27366</v>
@@ -5457,13 +5457,13 @@
         <v>26971</v>
       </c>
       <c r="Q74" t="n">
-        <v>26948</v>
+        <v>27176</v>
       </c>
       <c r="R74" t="n">
-        <v>26971</v>
+        <v>27176</v>
       </c>
       <c r="S74" t="n">
-        <v>59.94</v>
+        <v>60.39</v>
       </c>
       <c r="T74" t="n">
         <v>2</v>
@@ -5676,13 +5676,13 @@
         <v>24841</v>
       </c>
       <c r="Q77" t="n">
-        <v>25397</v>
+        <v>25549</v>
       </c>
       <c r="R77" t="n">
-        <v>25397</v>
+        <v>25549</v>
       </c>
       <c r="S77" t="n">
-        <v>56.44</v>
+        <v>56.78</v>
       </c>
       <c r="T77" t="n">
         <v>2</v>
@@ -6552,7 +6552,7 @@
         <v>14332</v>
       </c>
       <c r="Q89" t="n">
-        <v>7068</v>
+        <v>7739</v>
       </c>
       <c r="R89" t="n">
         <v>16869</v>
@@ -6625,7 +6625,7 @@
         <v>23928</v>
       </c>
       <c r="Q90" t="n">
-        <v>22577</v>
+        <v>23343</v>
       </c>
       <c r="R90" t="n">
         <v>23928</v>
@@ -6771,7 +6771,7 @@
         <v>40517</v>
       </c>
       <c r="Q92" t="n">
-        <v>37741</v>
+        <v>38101</v>
       </c>
       <c r="R92" t="n">
         <v>40517</v>
@@ -7715,7 +7715,7 @@
         <v>2863</v>
       </c>
       <c r="Q106" t="n">
-        <v>3958</v>
+        <v>3847</v>
       </c>
       <c r="R106" t="n">
         <v>9607</v>
@@ -8800,7 +8800,7 @@
         <v>12850</v>
       </c>
       <c r="Q123" t="n">
-        <v>2246</v>
+        <v>2545</v>
       </c>
       <c r="R123" t="n">
         <v>12850</v>
@@ -9019,13 +9019,13 @@
         <v>20047</v>
       </c>
       <c r="Q126" t="n">
-        <v>21417</v>
+        <v>21422</v>
       </c>
       <c r="R126" t="n">
-        <v>21417</v>
+        <v>21422</v>
       </c>
       <c r="S126" t="n">
-        <v>85.67</v>
+        <v>85.69</v>
       </c>
       <c r="T126" t="n">
         <v>2</v>
@@ -9092,7 +9092,7 @@
         <v>24895</v>
       </c>
       <c r="Q127" t="n">
-        <v>23162</v>
+        <v>23247</v>
       </c>
       <c r="R127" t="n">
         <v>24895</v>
@@ -9890,13 +9890,13 @@
         <v>23750</v>
       </c>
       <c r="Q139" t="n">
-        <v>23556</v>
+        <v>25303</v>
       </c>
       <c r="R139" t="n">
-        <v>23750</v>
+        <v>25303</v>
       </c>
       <c r="S139" t="n">
-        <v>95</v>
+        <v>101.21</v>
       </c>
       <c r="T139" t="n">
         <v>2</v>
@@ -10036,13 +10036,13 @@
         <v>5101</v>
       </c>
       <c r="Q141" t="n">
-        <v>5360</v>
+        <v>5683</v>
       </c>
       <c r="R141" t="n">
-        <v>5360</v>
+        <v>5683</v>
       </c>
       <c r="S141" t="n">
-        <v>57.17</v>
+        <v>60.62</v>
       </c>
       <c r="T141" t="n">
         <v>2</v>
@@ -10521,7 +10521,7 @@
         <v>14975</v>
       </c>
       <c r="Q148" t="n">
-        <v>14114</v>
+        <v>14848</v>
       </c>
       <c r="R148" t="n">
         <v>14975</v>
@@ -10732,7 +10732,7 @@
         <v>4144</v>
       </c>
       <c r="Q151" t="n">
-        <v>3913</v>
+        <v>4166</v>
       </c>
       <c r="R151" t="n">
         <v>4768</v>
@@ -11337,7 +11337,7 @@
         <v>19135</v>
       </c>
       <c r="Q160" t="n">
-        <v>18930</v>
+        <v>18940</v>
       </c>
       <c r="R160" t="n">
         <v>19135</v>
@@ -11410,7 +11410,7 @@
         <v>20845</v>
       </c>
       <c r="Q161" t="n">
-        <v>19983</v>
+        <v>20165</v>
       </c>
       <c r="R161" t="n">
         <v>20845</v>
@@ -11676,7 +11676,7 @@
         <v>20680</v>
       </c>
       <c r="Q165" t="n">
-        <v>12422</v>
+        <v>16930</v>
       </c>
       <c r="R165" t="n">
         <v>23412</v>
@@ -11895,7 +11895,7 @@
         <v>3495</v>
       </c>
       <c r="Q168" t="n">
-        <v>3266</v>
+        <v>3424</v>
       </c>
       <c r="R168" t="n">
         <v>3495</v>
@@ -12015,7 +12015,7 @@
         <v>4860</v>
       </c>
       <c r="Q170" t="n">
-        <v>3982</v>
+        <v>4044</v>
       </c>
       <c r="R170" t="n">
         <v>5470</v>
@@ -12088,13 +12088,13 @@
         <v>3311</v>
       </c>
       <c r="Q171" t="n">
-        <v>3302</v>
+        <v>3354</v>
       </c>
       <c r="R171" t="n">
-        <v>3311</v>
+        <v>3354</v>
       </c>
       <c r="S171" t="n">
-        <v>66.22</v>
+        <v>67.08</v>
       </c>
       <c r="T171" t="n">
         <v>2</v>
@@ -12401,7 +12401,7 @@
         <v>21881</v>
       </c>
       <c r="Q176" t="n">
-        <v>17081</v>
+        <v>18267</v>
       </c>
       <c r="R176" t="n">
         <v>22662</v>
@@ -12547,7 +12547,7 @@
         <v>25738</v>
       </c>
       <c r="Q178" t="n">
-        <v>24951</v>
+        <v>25344</v>
       </c>
       <c r="R178" t="n">
         <v>26402</v>
@@ -12620,7 +12620,7 @@
         <v>23599</v>
       </c>
       <c r="Q179" t="n">
-        <v>22662</v>
+        <v>23125</v>
       </c>
       <c r="R179" t="n">
         <v>23792</v>
@@ -13131,7 +13131,7 @@
         <v>17525</v>
       </c>
       <c r="Q186" t="n">
-        <v>13736</v>
+        <v>13751</v>
       </c>
       <c r="R186" t="n">
         <v>23208</v>
@@ -13204,7 +13204,7 @@
         <v>16892</v>
       </c>
       <c r="Q187" t="n">
-        <v>11208</v>
+        <v>11335</v>
       </c>
       <c r="R187" t="n">
         <v>16892</v>
@@ -13277,7 +13277,7 @@
         <v>27216</v>
       </c>
       <c r="Q188" t="n">
-        <v>14435</v>
+        <v>15513</v>
       </c>
       <c r="R188" t="n">
         <v>27359</v>
@@ -13642,7 +13642,7 @@
         <v>11823</v>
       </c>
       <c r="Q193" t="n">
-        <v>8046</v>
+        <v>8631</v>
       </c>
       <c r="R193" t="n">
         <v>11823</v>
@@ -15452,7 +15452,7 @@
         <v>5045</v>
       </c>
       <c r="Q221" t="n">
-        <v>4949</v>
+        <v>5009</v>
       </c>
       <c r="R221" t="n">
         <v>5442</v>
@@ -15525,7 +15525,7 @@
         <v>9049</v>
       </c>
       <c r="Q222" t="n">
-        <v>6973</v>
+        <v>7065</v>
       </c>
       <c r="R222" t="n">
         <v>9049</v>
@@ -15864,13 +15864,13 @@
         <v>2106</v>
       </c>
       <c r="Q227" t="n">
-        <v>2148</v>
+        <v>2198</v>
       </c>
       <c r="R227" t="n">
-        <v>2148</v>
+        <v>2198</v>
       </c>
       <c r="S227" t="n">
-        <v>42.96</v>
+        <v>43.96</v>
       </c>
       <c r="T227" t="n">
         <v>2</v>
@@ -16010,13 +16010,13 @@
         <v>29745</v>
       </c>
       <c r="Q229" t="n">
-        <v>30085</v>
+        <v>30147</v>
       </c>
       <c r="R229" t="n">
-        <v>30085</v>
+        <v>30147</v>
       </c>
       <c r="S229" t="n">
-        <v>100.28</v>
+        <v>100.49</v>
       </c>
       <c r="T229" t="n">
         <v>2</v>
@@ -16276,7 +16276,7 @@
         <v>5991</v>
       </c>
       <c r="Q233" t="n">
-        <v>5789</v>
+        <v>6108</v>
       </c>
       <c r="R233" t="n">
         <v>6622</v>
@@ -17590,7 +17590,7 @@
         <v>2466</v>
       </c>
       <c r="Q251" t="n">
-        <v>2485</v>
+        <v>2525</v>
       </c>
       <c r="R251" t="n">
         <v>2618</v>
@@ -17882,7 +17882,7 @@
         <v>2428</v>
       </c>
       <c r="Q255" t="n">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="R255" t="n">
         <v>2428</v>
@@ -17955,7 +17955,7 @@
         <v>1175</v>
       </c>
       <c r="Q256" t="n">
-        <v>864</v>
+        <v>920</v>
       </c>
       <c r="R256" t="n">
         <v>1251</v>
@@ -18101,7 +18101,7 @@
         <v>5437</v>
       </c>
       <c r="Q258" t="n">
-        <v>5236</v>
+        <v>5282</v>
       </c>
       <c r="R258" t="n">
         <v>5648</v>
@@ -18393,13 +18393,13 @@
         <v>4533</v>
       </c>
       <c r="Q262" t="n">
-        <v>4296</v>
+        <v>4590</v>
       </c>
       <c r="R262" t="n">
-        <v>4533</v>
+        <v>4590</v>
       </c>
       <c r="S262" t="n">
-        <v>90.31</v>
+        <v>91.44</v>
       </c>
       <c r="T262" t="n">
         <v>2</v>
@@ -18466,13 +18466,13 @@
         <v>4998</v>
       </c>
       <c r="Q263" t="n">
-        <v>4918</v>
+        <v>5154</v>
       </c>
       <c r="R263" t="n">
-        <v>4998</v>
+        <v>5154</v>
       </c>
       <c r="S263" t="n">
-        <v>69.42</v>
+        <v>71.58</v>
       </c>
       <c r="T263" t="n">
         <v>2</v>
@@ -18539,13 +18539,13 @@
         <v>3376</v>
       </c>
       <c r="Q264" t="n">
-        <v>3197</v>
+        <v>3440</v>
       </c>
       <c r="R264" t="n">
-        <v>3376</v>
+        <v>3440</v>
       </c>
       <c r="S264" t="n">
-        <v>67.26000000000001</v>
+        <v>68.53</v>
       </c>
       <c r="T264" t="n">
         <v>2</v>
@@ -18612,7 +18612,7 @@
         <v>6514</v>
       </c>
       <c r="Q265" t="n">
-        <v>5988</v>
+        <v>6180</v>
       </c>
       <c r="R265" t="n">
         <v>6514</v>
@@ -18758,13 +18758,13 @@
         <v>2428</v>
       </c>
       <c r="Q267" t="n">
-        <v>2432</v>
+        <v>2445</v>
       </c>
       <c r="R267" t="n">
-        <v>2432</v>
+        <v>2445</v>
       </c>
       <c r="S267" t="n">
-        <v>60.8</v>
+        <v>61.12</v>
       </c>
       <c r="T267" t="n">
         <v>2</v>
@@ -18831,7 +18831,7 @@
         <v>808</v>
       </c>
       <c r="Q268" t="n">
-        <v>681</v>
+        <v>711</v>
       </c>
       <c r="R268" t="n">
         <v>808</v>
@@ -19050,7 +19050,7 @@
         <v>743</v>
       </c>
       <c r="Q271" t="n">
-        <v>692</v>
+        <v>712</v>
       </c>
       <c r="R271" t="n">
         <v>743</v>
@@ -20046,7 +20046,7 @@
         <v>3724</v>
       </c>
       <c r="Q285" t="n">
-        <v>2216</v>
+        <v>2376</v>
       </c>
       <c r="R285" t="n">
         <v>4980</v>
@@ -20359,13 +20359,13 @@
         <v>4744</v>
       </c>
       <c r="Q290" t="n">
-        <v>4800</v>
+        <v>4920</v>
       </c>
       <c r="R290" t="n">
-        <v>4824</v>
+        <v>4920</v>
       </c>
       <c r="S290" t="n">
-        <v>241.2</v>
+        <v>246</v>
       </c>
       <c r="T290" t="n">
         <v>2</v>
@@ -20578,13 +20578,13 @@
         <v>2268</v>
       </c>
       <c r="Q293" t="n">
-        <v>2271</v>
+        <v>2277</v>
       </c>
       <c r="R293" t="n">
-        <v>2271</v>
+        <v>2277</v>
       </c>
       <c r="S293" t="n">
-        <v>75.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="T293" t="n">
         <v>2</v>
@@ -20651,13 +20651,13 @@
         <v>492</v>
       </c>
       <c r="Q294" t="n">
-        <v>979</v>
+        <v>1017</v>
       </c>
       <c r="R294" t="n">
-        <v>979</v>
+        <v>1017</v>
       </c>
       <c r="S294" t="n">
-        <v>48.95</v>
+        <v>50.85</v>
       </c>
       <c r="T294" t="n">
         <v>2</v>
@@ -20943,7 +20943,7 @@
         <v>1813</v>
       </c>
       <c r="Q298" t="n">
-        <v>1631</v>
+        <v>1769</v>
       </c>
       <c r="R298" t="n">
         <v>1847</v>
@@ -21016,7 +21016,7 @@
         <v>4602</v>
       </c>
       <c r="Q299" t="n">
-        <v>4265</v>
+        <v>4524</v>
       </c>
       <c r="R299" t="n">
         <v>4617</v>
@@ -21162,7 +21162,7 @@
         <v>2416</v>
       </c>
       <c r="Q301" t="n">
-        <v>2118</v>
+        <v>2203</v>
       </c>
       <c r="R301" t="n">
         <v>2440</v>
@@ -21235,7 +21235,7 @@
         <v>4070</v>
       </c>
       <c r="Q302" t="n">
-        <v>3699</v>
+        <v>4004</v>
       </c>
       <c r="R302" t="n">
         <v>4070</v>
@@ -21600,13 +21600,13 @@
         <v>5754</v>
       </c>
       <c r="Q307" t="n">
-        <v>5486</v>
+        <v>5833</v>
       </c>
       <c r="R307" t="n">
-        <v>5754</v>
+        <v>5833</v>
       </c>
       <c r="S307" t="n">
-        <v>57.54</v>
+        <v>58.33</v>
       </c>
       <c r="T307" t="n">
         <v>2</v>
@@ -21819,7 +21819,7 @@
         <v>3696</v>
       </c>
       <c r="Q310" t="n">
-        <v>3555</v>
+        <v>3714</v>
       </c>
       <c r="R310" t="n">
         <v>3754</v>
@@ -22904,13 +22904,13 @@
         <v>4827</v>
       </c>
       <c r="Q327" t="n">
-        <v>4736</v>
+        <v>4877</v>
       </c>
       <c r="R327" t="n">
-        <v>4827</v>
+        <v>4877</v>
       </c>
       <c r="S327" t="n">
-        <v>68.95999999999999</v>
+        <v>69.67</v>
       </c>
       <c r="T327" t="n">
         <v>2</v>
@@ -23097,13 +23097,13 @@
         <v>7890</v>
       </c>
       <c r="Q330" t="n">
-        <v>7837</v>
+        <v>8203</v>
       </c>
       <c r="R330" t="n">
-        <v>7890</v>
+        <v>8203</v>
       </c>
       <c r="S330" t="n">
-        <v>109.58</v>
+        <v>113.93</v>
       </c>
       <c r="T330" t="n">
         <v>2</v>
@@ -23170,13 +23170,13 @@
         <v>8524</v>
       </c>
       <c r="Q331" t="n">
-        <v>8703</v>
+        <v>8787</v>
       </c>
       <c r="R331" t="n">
-        <v>8703</v>
+        <v>8787</v>
       </c>
       <c r="S331" t="n">
-        <v>90.66</v>
+        <v>91.53</v>
       </c>
       <c r="T331" t="n">
         <v>2</v>
@@ -23243,7 +23243,7 @@
         <v>14357</v>
       </c>
       <c r="Q332" t="n">
-        <v>13979</v>
+        <v>14100</v>
       </c>
       <c r="R332" t="n">
         <v>14357</v>
@@ -23389,7 +23389,7 @@
         <v>6850</v>
       </c>
       <c r="Q334" t="n">
-        <v>5242</v>
+        <v>5294</v>
       </c>
       <c r="R334" t="n">
         <v>6850</v>
@@ -23754,7 +23754,7 @@
         <v>3339</v>
       </c>
       <c r="Q339" t="n">
-        <v>3296</v>
+        <v>3360</v>
       </c>
       <c r="R339" t="n">
         <v>4937</v>
@@ -23827,7 +23827,7 @@
         <v>4047</v>
       </c>
       <c r="Q340" t="n">
-        <v>3898</v>
+        <v>3974</v>
       </c>
       <c r="R340" t="n">
         <v>6174</v>
@@ -23900,7 +23900,7 @@
         <v>1075</v>
       </c>
       <c r="Q341" t="n">
-        <v>1045</v>
+        <v>1063</v>
       </c>
       <c r="R341" t="n">
         <v>1078</v>
@@ -23973,7 +23973,7 @@
         <v>4272</v>
       </c>
       <c r="Q342" t="n">
-        <v>4255</v>
+        <v>4262</v>
       </c>
       <c r="R342" t="n">
         <v>4419</v>
@@ -24406,7 +24406,7 @@
         <v>7979</v>
       </c>
       <c r="Q349" t="n">
-        <v>3637</v>
+        <v>3672</v>
       </c>
       <c r="R349" t="n">
         <v>7979</v>
@@ -24479,7 +24479,7 @@
         <v>3753</v>
       </c>
       <c r="Q350" t="n">
-        <v>3200</v>
+        <v>3262</v>
       </c>
       <c r="R350" t="n">
         <v>3782</v>
@@ -24625,7 +24625,7 @@
         <v>1936</v>
       </c>
       <c r="Q352" t="n">
-        <v>1732</v>
+        <v>1781</v>
       </c>
       <c r="R352" t="n">
         <v>1936</v>
@@ -24698,7 +24698,7 @@
         <v>4023</v>
       </c>
       <c r="Q353" t="n">
-        <v>3888</v>
+        <v>3984</v>
       </c>
       <c r="R353" t="n">
         <v>4023</v>
@@ -24771,7 +24771,7 @@
         <v>5756</v>
       </c>
       <c r="Q354" t="n">
-        <v>5432</v>
+        <v>5460</v>
       </c>
       <c r="R354" t="n">
         <v>5756</v>
@@ -24917,7 +24917,7 @@
         <v>5202</v>
       </c>
       <c r="Q356" t="n">
-        <v>4993</v>
+        <v>5017</v>
       </c>
       <c r="R356" t="n">
         <v>5516</v>
@@ -25136,7 +25136,7 @@
         <v>4644</v>
       </c>
       <c r="Q359" t="n">
-        <v>4330</v>
+        <v>4398</v>
       </c>
       <c r="R359" t="n">
         <v>4644</v>
@@ -25501,7 +25501,7 @@
         <v>2644</v>
       </c>
       <c r="Q364" t="n">
-        <v>2548</v>
+        <v>2563</v>
       </c>
       <c r="R364" t="n">
         <v>2644</v>
@@ -25574,7 +25574,7 @@
         <v>7437</v>
       </c>
       <c r="Q365" t="n">
-        <v>6222</v>
+        <v>6587</v>
       </c>
       <c r="R365" t="n">
         <v>7802</v>
@@ -25647,7 +25647,7 @@
         <v>6490</v>
       </c>
       <c r="Q366" t="n">
-        <v>6102</v>
+        <v>6432</v>
       </c>
       <c r="R366" t="n">
         <v>6493</v>
@@ -25866,7 +25866,7 @@
         <v>5884</v>
       </c>
       <c r="Q369" t="n">
-        <v>5524</v>
+        <v>5619</v>
       </c>
       <c r="R369" t="n">
         <v>5884</v>
@@ -25939,7 +25939,7 @@
         <v>7971</v>
       </c>
       <c r="Q370" t="n">
-        <v>7747</v>
+        <v>7830</v>
       </c>
       <c r="R370" t="n">
         <v>7971</v>
@@ -26012,7 +26012,7 @@
         <v>7339</v>
       </c>
       <c r="Q371" t="n">
-        <v>6744</v>
+        <v>6862</v>
       </c>
       <c r="R371" t="n">
         <v>7339</v>
@@ -26085,7 +26085,7 @@
         <v>6777</v>
       </c>
       <c r="Q372" t="n">
-        <v>6745</v>
+        <v>6751</v>
       </c>
       <c r="R372" t="n">
         <v>6777</v>
@@ -26888,7 +26888,7 @@
         <v>3917</v>
       </c>
       <c r="Q383" t="n">
-        <v>3574</v>
+        <v>3585</v>
       </c>
       <c r="R383" t="n">
         <v>4682</v>
@@ -27472,7 +27472,7 @@
         <v>698</v>
       </c>
       <c r="Q391" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="R391" t="n">
         <v>698</v>
@@ -27618,7 +27618,7 @@
         <v>5627</v>
       </c>
       <c r="Q393" t="n">
-        <v>4615</v>
+        <v>4765</v>
       </c>
       <c r="R393" t="n">
         <v>5981</v>
@@ -27764,7 +27764,7 @@
         <v>6782</v>
       </c>
       <c r="Q395" t="n">
-        <v>6365</v>
+        <v>6623</v>
       </c>
       <c r="R395" t="n">
         <v>9811</v>
@@ -27837,7 +27837,7 @@
         <v>3961</v>
       </c>
       <c r="Q396" t="n">
-        <v>3717</v>
+        <v>3889</v>
       </c>
       <c r="R396" t="n">
         <v>3961</v>
@@ -28322,7 +28322,7 @@
         <v>2285</v>
       </c>
       <c r="Q403" t="n">
-        <v>2104</v>
+        <v>2139</v>
       </c>
       <c r="R403" t="n">
         <v>3611</v>
@@ -28833,13 +28833,13 @@
         <v>4196</v>
       </c>
       <c r="Q410" t="n">
-        <v>4198</v>
+        <v>4316</v>
       </c>
       <c r="R410" t="n">
-        <v>4295</v>
+        <v>4316</v>
       </c>
       <c r="S410" t="n">
-        <v>42.95</v>
+        <v>43.16</v>
       </c>
       <c r="T410" t="n">
         <v>2</v>
@@ -28906,7 +28906,7 @@
         <v>3711</v>
       </c>
       <c r="Q411" t="n">
-        <v>3610</v>
+        <v>3674</v>
       </c>
       <c r="R411" t="n">
         <v>3711</v>
@@ -28979,7 +28979,7 @@
         <v>9272</v>
       </c>
       <c r="Q412" t="n">
-        <v>7543</v>
+        <v>7712</v>
       </c>
       <c r="R412" t="n">
         <v>9317</v>
@@ -29271,7 +29271,7 @@
         <v>4548</v>
       </c>
       <c r="Q416" t="n">
-        <v>4367</v>
+        <v>4453</v>
       </c>
       <c r="R416" t="n">
         <v>4548</v>
@@ -29417,7 +29417,7 @@
         <v>3535</v>
       </c>
       <c r="Q418" t="n">
-        <v>3360</v>
+        <v>3442</v>
       </c>
       <c r="R418" t="n">
         <v>3545</v>
@@ -29709,7 +29709,7 @@
         <v>8253</v>
       </c>
       <c r="Q422" t="n">
-        <v>7716</v>
+        <v>7768</v>
       </c>
       <c r="R422" t="n">
         <v>8253</v>
@@ -29928,7 +29928,7 @@
         <v>2990</v>
       </c>
       <c r="Q425" t="n">
-        <v>2770</v>
+        <v>3351</v>
       </c>
       <c r="R425" t="n">
         <v>3581</v>
@@ -30001,7 +30001,7 @@
         <v>4726</v>
       </c>
       <c r="Q426" t="n">
-        <v>4434</v>
+        <v>4477</v>
       </c>
       <c r="R426" t="n">
         <v>4726</v>
@@ -30220,7 +30220,7 @@
         <v>3500</v>
       </c>
       <c r="Q429" t="n">
-        <v>3065</v>
+        <v>3077</v>
       </c>
       <c r="R429" t="n">
         <v>5420</v>
@@ -30293,13 +30293,13 @@
         <v>5641</v>
       </c>
       <c r="Q430" t="n">
-        <v>5738</v>
+        <v>5823</v>
       </c>
       <c r="R430" t="n">
-        <v>5738</v>
+        <v>5823</v>
       </c>
       <c r="S430" t="n">
-        <v>57.16</v>
+        <v>58</v>
       </c>
       <c r="T430" t="n">
         <v>2</v>
@@ -30585,7 +30585,7 @@
         <v>4166</v>
       </c>
       <c r="Q434" t="n">
-        <v>4012</v>
+        <v>4057</v>
       </c>
       <c r="R434" t="n">
         <v>4396</v>
@@ -30804,7 +30804,7 @@
         <v>7100</v>
       </c>
       <c r="Q437" t="n">
-        <v>6740</v>
+        <v>6797</v>
       </c>
       <c r="R437" t="n">
         <v>7100</v>
@@ -30950,7 +30950,7 @@
         <v>2775</v>
       </c>
       <c r="Q439" t="n">
-        <v>2652</v>
+        <v>2698</v>
       </c>
       <c r="R439" t="n">
         <v>2775</v>
@@ -31388,7 +31388,7 @@
         <v>1656</v>
       </c>
       <c r="Q445" t="n">
-        <v>1484</v>
+        <v>1489</v>
       </c>
       <c r="R445" t="n">
         <v>3108</v>
@@ -31534,7 +31534,7 @@
         <v>5716</v>
       </c>
       <c r="Q447" t="n">
-        <v>5552</v>
+        <v>5714</v>
       </c>
       <c r="R447" t="n">
         <v>5716</v>
@@ -31607,7 +31607,7 @@
         <v>9289</v>
       </c>
       <c r="Q448" t="n">
-        <v>9148</v>
+        <v>9256</v>
       </c>
       <c r="R448" t="n">
         <v>9289</v>
@@ -31753,7 +31753,7 @@
         <v>7745</v>
       </c>
       <c r="Q450" t="n">
-        <v>7418</v>
+        <v>7698</v>
       </c>
       <c r="R450" t="n">
         <v>7745</v>
@@ -31826,7 +31826,7 @@
         <v>8708</v>
       </c>
       <c r="Q451" t="n">
-        <v>8343</v>
+        <v>8388</v>
       </c>
       <c r="R451" t="n">
         <v>8708</v>
@@ -33286,7 +33286,7 @@
         <v>4033</v>
       </c>
       <c r="Q471" t="n">
-        <v>3841</v>
+        <v>3943</v>
       </c>
       <c r="R471" t="n">
         <v>4731</v>
@@ -33432,7 +33432,7 @@
         <v>5262</v>
       </c>
       <c r="Q473" t="n">
-        <v>3948</v>
+        <v>3992</v>
       </c>
       <c r="R473" t="n">
         <v>5505</v>
@@ -33505,7 +33505,7 @@
         <v>4452</v>
       </c>
       <c r="Q474" t="n">
-        <v>4123</v>
+        <v>4202</v>
       </c>
       <c r="R474" t="n">
         <v>4452</v>
@@ -33870,7 +33870,7 @@
         <v>6473</v>
       </c>
       <c r="Q479" t="n">
-        <v>5949</v>
+        <v>6067</v>
       </c>
       <c r="R479" t="n">
         <v>8776</v>
@@ -34089,13 +34089,13 @@
         <v>3841</v>
       </c>
       <c r="Q482" t="n">
-        <v>3879</v>
+        <v>3926</v>
       </c>
       <c r="R482" t="n">
-        <v>3879</v>
+        <v>3926</v>
       </c>
       <c r="S482" t="n">
-        <v>38.79</v>
+        <v>39.26</v>
       </c>
       <c r="T482" t="n">
         <v>2</v>
@@ -34162,7 +34162,7 @@
         <v>7786</v>
       </c>
       <c r="Q483" t="n">
-        <v>7486</v>
+        <v>7528</v>
       </c>
       <c r="R483" t="n">
         <v>7838</v>
@@ -34381,13 +34381,13 @@
         <v>3675</v>
       </c>
       <c r="Q486" t="n">
-        <v>3758</v>
+        <v>3763</v>
       </c>
       <c r="R486" t="n">
-        <v>3758</v>
+        <v>3763</v>
       </c>
       <c r="S486" t="n">
-        <v>52.19</v>
+        <v>52.26</v>
       </c>
       <c r="T486" t="n">
         <v>2</v>
@@ -34892,7 +34892,7 @@
         <v>4744</v>
       </c>
       <c r="Q493" t="n">
-        <v>4691</v>
+        <v>4716</v>
       </c>
       <c r="R493" t="n">
         <v>4744</v>
@@ -35111,7 +35111,7 @@
         <v>6431</v>
       </c>
       <c r="Q496" t="n">
-        <v>4975</v>
+        <v>4999</v>
       </c>
       <c r="R496" t="n">
         <v>6431</v>
@@ -35403,13 +35403,13 @@
         <v>3848</v>
       </c>
       <c r="Q500" t="n">
-        <v>4499</v>
+        <v>4670</v>
       </c>
       <c r="R500" t="n">
-        <v>4499</v>
+        <v>4670</v>
       </c>
       <c r="S500" t="n">
-        <v>44.99</v>
+        <v>46.7</v>
       </c>
       <c r="T500" t="n">
         <v>2</v>
@@ -37374,7 +37374,7 @@
         <v>4437</v>
       </c>
       <c r="Q527" t="n">
-        <v>3558</v>
+        <v>4004</v>
       </c>
       <c r="R527" t="n">
         <v>4805</v>
@@ -38610,7 +38610,7 @@
         <v>2154</v>
       </c>
       <c r="Q545" t="n">
-        <v>942</v>
+        <v>878</v>
       </c>
       <c r="R545" t="n">
         <v>6861</v>
@@ -38902,7 +38902,7 @@
         <v>610</v>
       </c>
       <c r="Q549" t="n">
-        <v>1399</v>
+        <v>1285</v>
       </c>
       <c r="R549" t="n">
         <v>3847</v>
@@ -40305,7 +40305,7 @@
         <v>2695</v>
       </c>
       <c r="Q570" t="n">
-        <v>3363</v>
+        <v>2790</v>
       </c>
       <c r="R570" t="n">
         <v>3836</v>
@@ -41374,7 +41374,7 @@
         <v>3804</v>
       </c>
       <c r="Q585" t="n">
-        <v>2570</v>
+        <v>2734</v>
       </c>
       <c r="R585" t="n">
         <v>5542</v>
@@ -41812,7 +41812,7 @@
         <v>6869</v>
       </c>
       <c r="Q591" t="n">
-        <v>6152</v>
+        <v>6543</v>
       </c>
       <c r="R591" t="n">
         <v>6869</v>
@@ -43199,7 +43199,7 @@
         <v>2933</v>
       </c>
       <c r="Q610" t="n">
-        <v>2327</v>
+        <v>2090</v>
       </c>
       <c r="R610" t="n">
         <v>3274</v>
@@ -43903,7 +43903,7 @@
         <v>6767</v>
       </c>
       <c r="Q620" t="n">
-        <v>5644</v>
+        <v>6066</v>
       </c>
       <c r="R620" t="n">
         <v>6767</v>
@@ -44169,7 +44169,7 @@
         <v>3527</v>
       </c>
       <c r="Q624" t="n">
-        <v>1322</v>
+        <v>3279</v>
       </c>
       <c r="R624" t="n">
         <v>5528</v>
@@ -44242,7 +44242,7 @@
         <v>8231</v>
       </c>
       <c r="Q625" t="n">
-        <v>4914</v>
+        <v>4039</v>
       </c>
       <c r="R625" t="n">
         <v>8231</v>
@@ -44315,13 +44315,13 @@
         <v>5022</v>
       </c>
       <c r="Q626" t="n">
-        <v>4846</v>
+        <v>5035</v>
       </c>
       <c r="R626" t="n">
-        <v>5022</v>
+        <v>5035</v>
       </c>
       <c r="S626" t="n">
-        <v>55.8</v>
+        <v>55.94</v>
       </c>
       <c r="T626" t="n">
         <v>2</v>
@@ -44534,7 +44534,7 @@
         <v>4367</v>
       </c>
       <c r="Q629" t="n">
-        <v>4206</v>
+        <v>4361</v>
       </c>
       <c r="R629" t="n">
         <v>4488</v>
@@ -44607,13 +44607,13 @@
         <v>1500</v>
       </c>
       <c r="Q630" t="n">
-        <v>1833</v>
+        <v>2040</v>
       </c>
       <c r="R630" t="n">
-        <v>1833</v>
+        <v>2040</v>
       </c>
       <c r="S630" t="n">
-        <v>20.37</v>
+        <v>22.67</v>
       </c>
       <c r="T630" t="n">
         <v>2</v>
@@ -44680,7 +44680,7 @@
         <v>3312</v>
       </c>
       <c r="Q631" t="n">
-        <v>1812</v>
+        <v>2277</v>
       </c>
       <c r="R631" t="n">
         <v>3312</v>
@@ -44826,13 +44826,13 @@
         <v>2582</v>
       </c>
       <c r="Q633" t="n">
-        <v>2328</v>
+        <v>2699</v>
       </c>
       <c r="R633" t="n">
-        <v>2582</v>
+        <v>2699</v>
       </c>
       <c r="S633" t="n">
-        <v>28.69</v>
+        <v>29.99</v>
       </c>
       <c r="T633" t="n">
         <v>2</v>
@@ -44899,13 +44899,13 @@
         <v>942</v>
       </c>
       <c r="Q634" t="n">
-        <v>1030</v>
+        <v>1073</v>
       </c>
       <c r="R634" t="n">
-        <v>1030</v>
+        <v>1073</v>
       </c>
       <c r="S634" t="n">
-        <v>17.17</v>
+        <v>17.88</v>
       </c>
       <c r="T634" t="n">
         <v>2</v>
@@ -44972,7 +44972,7 @@
         <v>4721</v>
       </c>
       <c r="Q635" t="n">
-        <v>4420</v>
+        <v>4638</v>
       </c>
       <c r="R635" t="n">
         <v>5135</v>
@@ -45118,7 +45118,7 @@
         <v>2479</v>
       </c>
       <c r="Q637" t="n">
-        <v>2252</v>
+        <v>2369</v>
       </c>
       <c r="R637" t="n">
         <v>2816</v>
@@ -45191,7 +45191,7 @@
         <v>4412</v>
       </c>
       <c r="Q638" t="n">
-        <v>3797</v>
+        <v>4557</v>
       </c>
       <c r="R638" t="n">
         <v>9088</v>
@@ -45775,7 +45775,7 @@
         <v>3858</v>
       </c>
       <c r="Q646" t="n">
-        <v>3714</v>
+        <v>3860</v>
       </c>
       <c r="R646" t="n">
         <v>5433</v>
@@ -45848,7 +45848,7 @@
         <v>6421</v>
       </c>
       <c r="Q647" t="n">
-        <v>6334</v>
+        <v>6526</v>
       </c>
       <c r="R647" t="n">
         <v>6540</v>
@@ -46140,7 +46140,7 @@
         <v>7406</v>
       </c>
       <c r="Q651" t="n">
-        <v>7041</v>
+        <v>7145</v>
       </c>
       <c r="R651" t="n">
         <v>7406</v>
@@ -46286,13 +46286,13 @@
         <v>2164</v>
       </c>
       <c r="Q653" t="n">
-        <v>2053</v>
+        <v>2223</v>
       </c>
       <c r="R653" t="n">
-        <v>2204</v>
+        <v>2223</v>
       </c>
       <c r="S653" t="n">
-        <v>36.73</v>
+        <v>37.05</v>
       </c>
       <c r="T653" t="n">
         <v>2</v>
@@ -46359,7 +46359,7 @@
         <v>2146</v>
       </c>
       <c r="Q654" t="n">
-        <v>1855</v>
+        <v>1921</v>
       </c>
       <c r="R654" t="n">
         <v>2377</v>
@@ -46698,7 +46698,7 @@
         <v>3212</v>
       </c>
       <c r="Q659" t="n">
-        <v>1173</v>
+        <v>1868</v>
       </c>
       <c r="R659" t="n">
         <v>9224</v>
@@ -47647,7 +47647,7 @@
         <v>3585</v>
       </c>
       <c r="Q672" t="n">
-        <v>2426</v>
+        <v>2189</v>
       </c>
       <c r="R672" t="n">
         <v>5639</v>
@@ -48158,7 +48158,7 @@
         <v>4790</v>
       </c>
       <c r="Q679" t="n">
-        <v>4665</v>
+        <v>4725</v>
       </c>
       <c r="R679" t="n">
         <v>4790</v>
@@ -48304,7 +48304,7 @@
         <v>8165</v>
       </c>
       <c r="Q681" t="n">
-        <v>8228</v>
+        <v>8528</v>
       </c>
       <c r="R681" t="n">
         <v>9371</v>
@@ -48377,7 +48377,7 @@
         <v>4536</v>
       </c>
       <c r="Q682" t="n">
-        <v>3573</v>
+        <v>3648</v>
       </c>
       <c r="R682" t="n">
         <v>5228</v>
@@ -48523,7 +48523,7 @@
         <v>901</v>
       </c>
       <c r="Q684" t="n">
-        <v>0</v>
+        <v>3388</v>
       </c>
       <c r="R684" t="n">
         <v>13027</v>
@@ -48836,7 +48836,7 @@
         <v>2543</v>
       </c>
       <c r="Q689" t="n">
-        <v>2465</v>
+        <v>2471</v>
       </c>
       <c r="R689" t="n">
         <v>2550</v>
@@ -49201,7 +49201,7 @@
         <v>6140</v>
       </c>
       <c r="Q694" t="n">
-        <v>5887</v>
+        <v>6081</v>
       </c>
       <c r="R694" t="n">
         <v>7839</v>
@@ -49639,7 +49639,7 @@
         <v>2664</v>
       </c>
       <c r="Q700" t="n">
-        <v>2921</v>
+        <v>2968</v>
       </c>
       <c r="R700" t="n">
         <v>3510</v>
@@ -49785,13 +49785,13 @@
         <v>2954</v>
       </c>
       <c r="Q702" t="n">
-        <v>2941</v>
+        <v>2987</v>
       </c>
       <c r="R702" t="n">
-        <v>2954</v>
+        <v>2987</v>
       </c>
       <c r="S702" t="n">
-        <v>42.2</v>
+        <v>42.67</v>
       </c>
       <c r="T702" t="n">
         <v>2</v>
@@ -50004,7 +50004,7 @@
         <v>1082</v>
       </c>
       <c r="Q705" t="n">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="R705" t="n">
         <v>3176</v>
@@ -50077,7 +50077,7 @@
         <v>1272</v>
       </c>
       <c r="Q706" t="n">
-        <v>1065</v>
+        <v>1238</v>
       </c>
       <c r="R706" t="n">
         <v>1318</v>
@@ -50515,7 +50515,7 @@
         <v>4896</v>
       </c>
       <c r="Q712" t="n">
-        <v>4484</v>
+        <v>4503</v>
       </c>
       <c r="R712" t="n">
         <v>4896</v>
@@ -50588,7 +50588,7 @@
         <v>8051</v>
       </c>
       <c r="Q713" t="n">
-        <v>7551</v>
+        <v>7585</v>
       </c>
       <c r="R713" t="n">
         <v>8051</v>
@@ -50734,7 +50734,7 @@
         <v>6619</v>
       </c>
       <c r="Q715" t="n">
-        <v>4943</v>
+        <v>5108</v>
       </c>
       <c r="R715" t="n">
         <v>6709</v>
@@ -51099,7 +51099,7 @@
         <v>6118</v>
       </c>
       <c r="Q720" t="n">
-        <v>3658</v>
+        <v>3725</v>
       </c>
       <c r="R720" t="n">
         <v>6120</v>
@@ -51318,7 +51318,7 @@
         <v>8469</v>
       </c>
       <c r="Q723" t="n">
-        <v>8261</v>
+        <v>8389</v>
       </c>
       <c r="R723" t="n">
         <v>8594</v>
@@ -51391,7 +51391,7 @@
         <v>8987</v>
       </c>
       <c r="Q724" t="n">
-        <v>8619</v>
+        <v>8671</v>
       </c>
       <c r="R724" t="n">
         <v>9239</v>
@@ -51610,7 +51610,7 @@
         <v>4900</v>
       </c>
       <c r="Q727" t="n">
-        <v>4734</v>
+        <v>4829</v>
       </c>
       <c r="R727" t="n">
         <v>6905</v>
@@ -51829,7 +51829,7 @@
         <v>6618</v>
       </c>
       <c r="Q730" t="n">
-        <v>6342</v>
+        <v>6478</v>
       </c>
       <c r="R730" t="n">
         <v>6640</v>
@@ -51975,7 +51975,7 @@
         <v>5351</v>
       </c>
       <c r="Q732" t="n">
-        <v>5097</v>
+        <v>5132</v>
       </c>
       <c r="R732" t="n">
         <v>7052</v>
@@ -52194,7 +52194,7 @@
         <v>7496</v>
       </c>
       <c r="Q735" t="n">
-        <v>6949</v>
+        <v>7124</v>
       </c>
       <c r="R735" t="n">
         <v>7628</v>
@@ -52267,7 +52267,7 @@
         <v>7604</v>
       </c>
       <c r="Q736" t="n">
-        <v>7174</v>
+        <v>7349</v>
       </c>
       <c r="R736" t="n">
         <v>7604</v>
@@ -52413,7 +52413,7 @@
         <v>5821</v>
       </c>
       <c r="Q738" t="n">
-        <v>5724</v>
+        <v>5756</v>
       </c>
       <c r="R738" t="n">
         <v>5821</v>
@@ -52632,13 +52632,13 @@
         <v>1746</v>
       </c>
       <c r="Q741" t="n">
-        <v>1510</v>
+        <v>1973</v>
       </c>
       <c r="R741" t="n">
-        <v>1746</v>
+        <v>1973</v>
       </c>
       <c r="S741" t="n">
-        <v>14.55</v>
+        <v>16.44</v>
       </c>
       <c r="T741" t="n">
         <v>2</v>
@@ -52851,7 +52851,7 @@
         <v>4054</v>
       </c>
       <c r="Q744" t="n">
-        <v>3973</v>
+        <v>4214</v>
       </c>
       <c r="R744" t="n">
         <v>5457</v>
@@ -53581,7 +53581,7 @@
         <v>3713</v>
       </c>
       <c r="Q754" t="n">
-        <v>2131</v>
+        <v>2317</v>
       </c>
       <c r="R754" t="n">
         <v>3723</v>
@@ -53847,7 +53847,7 @@
         <v>4835</v>
       </c>
       <c r="Q758" t="n">
-        <v>2919</v>
+        <v>3240</v>
       </c>
       <c r="R758" t="n">
         <v>5661</v>
@@ -55667,7 +55667,7 @@
         <v>5739</v>
       </c>
       <c r="Q784" t="n">
-        <v>4213</v>
+        <v>4358</v>
       </c>
       <c r="R784" t="n">
         <v>5739</v>
@@ -55740,7 +55740,7 @@
         <v>4506</v>
       </c>
       <c r="Q785" t="n">
-        <v>4401</v>
+        <v>4436</v>
       </c>
       <c r="R785" t="n">
         <v>4507</v>
@@ -55886,7 +55886,7 @@
         <v>12292</v>
       </c>
       <c r="Q787" t="n">
-        <v>11789</v>
+        <v>12166</v>
       </c>
       <c r="R787" t="n">
         <v>12292</v>
@@ -57367,13 +57367,13 @@
         <v>5579</v>
       </c>
       <c r="Q808" t="n">
-        <v>5568</v>
+        <v>5678</v>
       </c>
       <c r="R808" t="n">
-        <v>5579</v>
+        <v>5678</v>
       </c>
       <c r="S808" t="n">
-        <v>77.48999999999999</v>
+        <v>78.86</v>
       </c>
       <c r="T808" t="n">
         <v>2</v>
@@ -57753,7 +57753,7 @@
         <v>5053</v>
       </c>
       <c r="Q814" t="n">
-        <v>4955</v>
+        <v>5004</v>
       </c>
       <c r="R814" t="n">
         <v>9982</v>
@@ -58765,7 +58765,7 @@
         <v>7</v>
       </c>
       <c r="Q830" t="n">
-        <v>0</v>
+        <v>-242</v>
       </c>
       <c r="R830" t="n">
         <v>3542</v>
@@ -58984,7 +58984,7 @@
         <v>1093</v>
       </c>
       <c r="Q833" t="n">
-        <v>1084</v>
+        <v>1129</v>
       </c>
       <c r="R833" t="n">
         <v>1510</v>
@@ -59130,13 +59130,13 @@
         <v>2095</v>
       </c>
       <c r="Q835" t="n">
-        <v>2138</v>
+        <v>2189</v>
       </c>
       <c r="R835" t="n">
-        <v>2138</v>
+        <v>2189</v>
       </c>
       <c r="S835" t="n">
-        <v>71.27</v>
+        <v>72.97</v>
       </c>
       <c r="T835" t="n">
         <v>2</v>
@@ -59203,13 +59203,13 @@
         <v>3616</v>
       </c>
       <c r="Q836" t="n">
-        <v>3679</v>
+        <v>3861</v>
       </c>
       <c r="R836" t="n">
-        <v>3679</v>
+        <v>3861</v>
       </c>
       <c r="S836" t="n">
-        <v>36.79</v>
+        <v>38.61</v>
       </c>
       <c r="T836" t="n">
         <v>2</v>
@@ -59276,7 +59276,7 @@
         <v>7020</v>
       </c>
       <c r="Q837" t="n">
-        <v>6811</v>
+        <v>6833</v>
       </c>
       <c r="R837" t="n">
         <v>7020</v>
@@ -59568,7 +59568,7 @@
         <v>4716</v>
       </c>
       <c r="Q841" t="n">
-        <v>4632</v>
+        <v>4643</v>
       </c>
       <c r="R841" t="n">
         <v>5470</v>
@@ -59641,7 +59641,7 @@
         <v>7005</v>
       </c>
       <c r="Q842" t="n">
-        <v>6160</v>
+        <v>6337</v>
       </c>
       <c r="R842" t="n">
         <v>7005</v>
@@ -59714,13 +59714,13 @@
         <v>6196</v>
       </c>
       <c r="Q843" t="n">
-        <v>6123</v>
+        <v>6280</v>
       </c>
       <c r="R843" t="n">
-        <v>6196</v>
+        <v>6280</v>
       </c>
       <c r="S843" t="n">
-        <v>61.72</v>
+        <v>62.56</v>
       </c>
       <c r="T843" t="n">
         <v>2</v>
@@ -59787,13 +59787,13 @@
         <v>1623</v>
       </c>
       <c r="Q844" t="n">
-        <v>1592</v>
+        <v>1653</v>
       </c>
       <c r="R844" t="n">
-        <v>1623</v>
+        <v>1653</v>
       </c>
       <c r="S844" t="n">
-        <v>16.17</v>
+        <v>16.47</v>
       </c>
       <c r="T844" t="n">
         <v>2</v>
@@ -59933,7 +59933,7 @@
         <v>293</v>
       </c>
       <c r="Q846" t="n">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="R846" t="n">
         <v>1355</v>
@@ -60006,7 +60006,7 @@
         <v>1782</v>
       </c>
       <c r="Q847" t="n">
-        <v>696</v>
+        <v>762</v>
       </c>
       <c r="R847" t="n">
         <v>1782</v>
@@ -60079,13 +60079,13 @@
         <v>2171</v>
       </c>
       <c r="Q848" t="n">
-        <v>2171</v>
+        <v>2253</v>
       </c>
       <c r="R848" t="n">
-        <v>2171</v>
+        <v>2253</v>
       </c>
       <c r="S848" t="n">
-        <v>25.23</v>
+        <v>26.18</v>
       </c>
       <c r="T848" t="n">
         <v>2</v>
@@ -60152,13 +60152,13 @@
         <v>4169</v>
       </c>
       <c r="Q849" t="n">
-        <v>4191</v>
+        <v>4348</v>
       </c>
       <c r="R849" t="n">
-        <v>4278</v>
+        <v>4348</v>
       </c>
       <c r="S849" t="n">
-        <v>49.72</v>
+        <v>50.53</v>
       </c>
       <c r="T849" t="n">
         <v>2</v>
@@ -60298,7 +60298,7 @@
         <v>238</v>
       </c>
       <c r="Q851" t="n">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="R851" t="n">
         <v>571</v>
@@ -60444,7 +60444,7 @@
         <v>2578</v>
       </c>
       <c r="Q853" t="n">
-        <v>2513</v>
+        <v>2537</v>
       </c>
       <c r="R853" t="n">
         <v>2599</v>
@@ -60929,7 +60929,7 @@
         <v>12764</v>
       </c>
       <c r="Q860" t="n">
-        <v>1109</v>
+        <v>1258</v>
       </c>
       <c r="R860" t="n">
         <v>12764</v>
@@ -61242,7 +61242,7 @@
         <v>5966</v>
       </c>
       <c r="Q865" t="n">
-        <v>4352</v>
+        <v>4454</v>
       </c>
       <c r="R865" t="n">
         <v>5966</v>
@@ -61534,7 +61534,7 @@
         <v>5201</v>
       </c>
       <c r="Q869" t="n">
-        <v>4354</v>
+        <v>5244</v>
       </c>
       <c r="R869" t="n">
         <v>8644</v>
